--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043E2811-2544-E341-B252-F395DC083D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D8E467-8C17-DB4A-BB45-22538D1B5223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2331,6 +2331,9 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2340,15 +2343,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2356,6 +2350,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12729,9 +12729,9 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>164.07</v>
-    <v>2.2280000000000002</v>
-    <v>3.9338000000000002</v>
-    <v>2.0169000000000003E-2</v>
+    <v>2.2233999999999998</v>
+    <v>5.71</v>
+    <v>2.9276E-2</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12739,23 +12739,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>200.09</v>
+    <v>202</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46234.719659200782</v>
+    <v>46234.999993483594</v>
     <v>0</v>
     <v>194.95</v>
-    <v>4815165960000</v>
+    <v>4858150000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>198.49</v>
-    <v>30.470700000000001</v>
+    <v>198.44049999999999</v>
+    <v>30.742899999999999</v>
     <v>195.04</v>
-    <v>198.97380000000001</v>
+    <v>200.75</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>61716561</v>
+    <v>565032</v>
     <v>134310928</v>
     <v>1998</v>
   </rv>
@@ -12793,19 +12793,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.14</v>
+    <v>47.47</v>
     <v>39.47</v>
-    <v>0.41</v>
-    <v>8.8710000000000004E-3</v>
+    <v>0.82</v>
+    <v>1.7585E-2</v>
     <v>US</v>
-    <v>46.86</v>
+    <v>47.47</v>
     <v>Index</v>
     <v>6</v>
-    <v>46.51</v>
+    <v>46.82</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.69</v>
-    <v>46.22</v>
+    <v>46.84</v>
     <v>46.63</v>
+    <v>47.45</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13587,18 +13587,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="238" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="238"/>
-      <c r="E2" s="237" t="s">
+      <c r="C2" s="239"/>
+      <c r="E2" s="238" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="238"/>
-      <c r="H2" s="237" t="s">
+      <c r="F2" s="239"/>
+      <c r="H2" s="238" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="238"/>
+      <c r="I2" s="239"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>4836058.2090000007</v>
+        <v>4879228.75</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13637,7 +13637,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>4763956.2090000007</v>
+        <v>4807126.75</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>198.97380000000001</v>
+        <v>200.75</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>30.470719754977033</v>
+        <v>30.742725880551305</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13702,14 +13702,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>3.9338000000000002</v>
+        <v>5.71</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>19.19910237878268</v>
+        <v>19.370488991719629</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13733,7 +13733,7 @@
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.3208364157223067E-2</v>
+        <v>2.3003020713058389E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.4988718448402843</v>
+        <v>0.48561009554611095</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13750,14 +13750,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.0169000000000003E-2</v>
+        <v>2.9276E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.2818391165067962E-2</v>
+        <v>3.2528019925280198E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>9.3679600290352896E-3</v>
+        <v>9.2850739986314428E-3</v>
       </c>
       <c r="H10" s="185" t="s">
         <v>409</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>2.0103149258847143E-4</v>
+        <v>1.9925280199252802E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2280000000000002</v>
+        <v>2.2233999999999998</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.4909249823713193E-2</v>
+        <v>1.4777335454911803E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13866,10 +13866,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="239" t="s">
+      <c r="B17" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="239"/>
+      <c r="C17" s="240"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13942,14 +13942,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="239" t="s">
+      <c r="B25" s="240" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="239"/>
-      <c r="E25" s="237" t="s">
+      <c r="C25" s="240"/>
+      <c r="E25" s="238" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="238"/>
+      <c r="F25" s="239"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.63</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.7450000000000006E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,15 +13998,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="240" t="s">
+      <c r="B33" s="237" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="240"/>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14025,24 +14025,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="240"/>
-      <c r="C39" s="240"/>
-      <c r="D39" s="240"/>
-      <c r="E39" s="240"/>
-      <c r="F39" s="240"/>
-      <c r="G39" s="240"/>
-      <c r="H39" s="240"/>
+      <c r="B39" s="237"/>
+      <c r="C39" s="237"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="240" t="s">
+      <c r="B42" s="237" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="240"/>
-      <c r="D42" s="240"/>
-      <c r="E42" s="240"/>
-      <c r="F42" s="240"/>
-      <c r="G42" s="240"/>
-      <c r="H42" s="240"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14057,24 +14057,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="240"/>
-      <c r="C49" s="240"/>
-      <c r="D49" s="240"/>
-      <c r="E49" s="240"/>
-      <c r="F49" s="240"/>
-      <c r="G49" s="240"/>
-      <c r="H49" s="240"/>
+      <c r="B49" s="237"/>
+      <c r="C49" s="237"/>
+      <c r="D49" s="237"/>
+      <c r="E49" s="237"/>
+      <c r="F49" s="237"/>
+      <c r="G49" s="237"/>
+      <c r="H49" s="237"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="240" t="s">
+      <c r="B52" s="237" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="240"/>
-      <c r="D52" s="240"/>
-      <c r="E52" s="240"/>
-      <c r="F52" s="240"/>
-      <c r="G52" s="240"/>
-      <c r="H52" s="240"/>
+      <c r="C52" s="237"/>
+      <c r="D52" s="237"/>
+      <c r="E52" s="237"/>
+      <c r="F52" s="237"/>
+      <c r="G52" s="237"/>
+      <c r="H52" s="237"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14089,28 +14089,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="240"/>
-      <c r="C59" s="240"/>
-      <c r="D59" s="240"/>
-      <c r="E59" s="240"/>
-      <c r="F59" s="240"/>
-      <c r="G59" s="240"/>
-      <c r="H59" s="240"/>
+      <c r="B59" s="237"/>
+      <c r="C59" s="237"/>
+      <c r="D59" s="237"/>
+      <c r="E59" s="237"/>
+      <c r="F59" s="237"/>
+      <c r="G59" s="237"/>
+      <c r="H59" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14180,36 +14180,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="240" t="s">
+      <c r="S2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240" t="s">
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
+      <c r="AA2" s="237" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15405,35 +15405,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="P2" s="240" t="s">
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
+      <c r="P2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="240"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240" t="s">
+      <c r="Q2" s="237"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="237"/>
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16664,20 +16664,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -18070,12 +18070,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18083,6 +18077,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18120,20 +18120,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="S2" s="251"/>
       <c r="T2" s="251"/>
       <c r="U2" s="251"/>
@@ -19142,16 +19142,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19214,10 +19214,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="237"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>198.97380000000001</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>4836058.2090000007</v>
+        <v>4879228.75</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.7450000000000006E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2280000000000002</v>
+        <v>2.2233999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19302,10 +19302,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="237" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="240"/>
+      <c r="C15" s="237"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.7483642647110032E-3</v>
+        <v>1.732921858164847E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99825163573528897</v>
+        <v>0.99826707814183513</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14689000000000002</v>
+        <v>0.147503</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14670362436938184</v>
+        <v>0.14731720824882055</v>
       </c>
     </row>
   </sheetData>
@@ -19394,20 +19394,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -19693,10 +19693,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="240" t="s">
+      <c r="B13" s="237" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="240"/>
+      <c r="C13" s="237"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19716,10 +19716,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="240" t="s">
+      <c r="B18" s="237" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="240"/>
+      <c r="C18" s="237"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19833,20 +19833,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20778,10 +20778,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="237" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="240"/>
+      <c r="C37" s="237"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20874,10 +20874,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="240" t="s">
+      <c r="B49" s="237" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="240"/>
+      <c r="C49" s="237"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -20933,10 +20933,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="240" t="s">
+      <c r="B57" s="237" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="240"/>
+      <c r="C57" s="237"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21076,10 +21076,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="237"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>198.97380000000001</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.4988718448402843</v>
+        <v>0.48561009554611095</v>
       </c>
     </row>
   </sheetData>
@@ -21198,20 +21198,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21574,10 +21574,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="240" t="s">
+      <c r="B20" s="237" t="s">
         <v>404</v>
       </c>
-      <c r="C20" s="240"/>
+      <c r="C20" s="237"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21678,20 +21678,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -21971,7 +21971,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>198.97380000000001</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22037,7 +22037,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>4815165.96</v>
+        <v>4858150</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4743063.96</v>
+        <v>4786048</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22590,17 +22590,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>198.97380000000001</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29185,7 +29185,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>198.97380000000001</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30687,7 +30687,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>30.470719754977033</v>
+        <v>30.742725880551305</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30724,7 +30724,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>19.19910237878268</v>
+        <v>19.370488991719629</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30785,7 +30785,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.633280947849848</v>
+        <v>24.85317740466763</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4836058.2090000007</v>
+        <v>4879228.75</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30907,7 +30907,7 @@
       </c>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4763956.2090000007</v>
+        <v>4807126.75</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30944,7 +30944,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>18.79339388380653</v>
+        <v>18.963697922214202</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30981,7 +30981,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>29.355493169424165</v>
+        <v>29.621509997843301</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31116,7 +31116,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="98">AC155/AC159</f>
-        <v>43.087914047952111</v>
+        <v>43.472551386797583</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31153,7 +31153,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>37.565873371689747</v>
+        <v>37.906291924137719</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31190,7 +31190,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="101">AC159/AC155</f>
-        <v>2.3208364157223067E-2</v>
+        <v>2.3003020713058389E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31227,7 +31227,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.2818391165067962E-2</v>
+        <v>3.2528019925280198E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31264,7 +31264,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>2.0103149258847143E-4</v>
+        <v>1.9925280199252802E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31301,7 +31301,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.3679600290352896E-3</v>
+        <v>9.2850739986314428E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31338,7 +31338,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.5691569456044963E-3</v>
+        <v>9.4844907609629905E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31841,7 +31841,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.4909249823713193E-2</v>
+        <v>1.4777335454911803E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -33006,15 +33006,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="240"/>
-      <c r="E4" s="240" t="s">
+      <c r="C4" s="237"/>
+      <c r="E4" s="237" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33022,7 +33022,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>198.97380000000001</v>
+        <v>200.75</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -33038,7 +33038,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4836058.2090000007</v>
+        <v>4879228.75</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33058,7 +33058,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4763956.2090000007</v>
+        <v>4807126.75</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33078,7 +33078,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>30.470719754977033</v>
+        <v>30.742725880551305</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33098,7 +33098,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.19910237878268</v>
+        <v>19.370488991719629</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33118,7 +33118,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.633280947849848</v>
+        <v>24.85317740466763</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.79339388380653</v>
+        <v>18.963697922214202</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33147,18 +33147,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>29.355493169424165</v>
+        <v>29.621509997843301</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="240"/>
-      <c r="E15" s="240" t="s">
+      <c r="C15" s="237"/>
+      <c r="E15" s="237" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="240"/>
+      <c r="F15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33209,14 +33209,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="240" t="s">
+      <c r="B21" s="237" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="240"/>
-      <c r="E21" s="240" t="s">
+      <c r="C21" s="237"/>
+      <c r="E21" s="237" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="240"/>
+      <c r="F21" s="237"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33285,14 +33285,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="240" t="s">
+      <c r="B29" s="237" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="240"/>
-      <c r="E29" s="240" t="s">
+      <c r="C29" s="237"/>
+      <c r="E29" s="237" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="240"/>
+      <c r="F29" s="237"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33368,14 +33368,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="237" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="240"/>
-      <c r="E37" s="240" t="s">
+      <c r="C37" s="237"/>
+      <c r="E37" s="237" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="240"/>
+      <c r="F37" s="237"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33383,7 +33383,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.2818391165067962E-2</v>
+        <v>3.2528019925280198E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.3208364157223067E-2</v>
+        <v>2.3003020713058389E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33415,7 +33415,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>2.0103149258847143E-4</v>
+        <v>1.9925280199252802E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33431,7 +33431,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.3679600290352896E-3</v>
+        <v>9.2850739986314428E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33440,18 +33440,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.5691569456044963E-3</v>
+        <v>9.4844907609629905E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="240" t="s">
+      <c r="B45" s="237" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="240"/>
-      <c r="E45" s="240" t="s">
+      <c r="C45" s="237"/>
+      <c r="E45" s="237" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="240"/>
+      <c r="F45" s="237"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33484,18 +33484,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.4909249823713193E-2</v>
+        <v>1.4777335454911803E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="240" t="s">
+      <c r="B51" s="237" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="240"/>
-      <c r="E51" s="240" t="s">
+      <c r="C51" s="237"/>
+      <c r="E51" s="237" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="240"/>
+      <c r="F51" s="237"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33664,7 +33664,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>198.97380000000001</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33693,7 +33693,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4836058.2090000007</v>
+        <v>4879228.75</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33722,7 +33722,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4763956.2090000007</v>
+        <v>4807126.75</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33751,7 +33751,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>30.470719754977033</v>
+        <v>30.742725880551305</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33780,7 +33780,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.19910237878268</v>
+        <v>19.370488991719629</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33809,7 +33809,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.633280947849848</v>
+        <v>24.85317740466763</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33838,7 +33838,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.79339388380653</v>
+        <v>18.963697922214202</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>29.355493169424165</v>
+        <v>29.621509997843301</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.2818391165067962E-2</v>
+        <v>3.2528019925280198E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34669,7 +34669,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.3208364157223067E-2</v>
+        <v>2.3003020713058389E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34698,7 +34698,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>2.0103149258847143E-4</v>
+        <v>1.9925280199252802E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34727,7 +34727,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.3679600290352896E-3</v>
+        <v>9.2850739986314428E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34756,7 +34756,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.5691569456044963E-3</v>
+        <v>9.4844907609629905E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34992,7 +34992,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.4909249823713193E-2</v>
+        <v>1.4777335454911803E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35504,14 +35504,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="241" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35578,19 +35578,19 @@
       <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="241">
+      <c r="C7" s="244">
         <f>Statement!AA88</f>
         <v>0.19798317847549429</v>
       </c>
-      <c r="D7" s="242"/>
-      <c r="F7" s="241">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.85227633788752211</v>
       </c>
-      <c r="G7" s="242"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="208" t="s">
@@ -35617,19 +35617,19 @@
       <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="241">
+      <c r="C9" s="244">
         <f>Statement!AA89</f>
         <v>0.20100974521545145</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="F9" s="241">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17615269633206854</v>
       </c>
-      <c r="G9" s="242"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="208" t="s">
@@ -35656,19 +35656,19 @@
       <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="241">
+      <c r="C11" s="244">
         <f>Statement!AA90</f>
         <v>0.19697414518622902</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="F11" s="241">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.293272836358182</v>
       </c>
-      <c r="G11" s="242"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="208" t="s">
@@ -35695,19 +35695,19 @@
       <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="241">
+      <c r="C13" s="244">
         <f>Statement!AA93</f>
         <v>0.12172505151604357</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="F13" s="241">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.51510934393638175</v>
       </c>
-      <c r="G13" s="242"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
@@ -35734,19 +35734,19 @@
       <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="241">
+      <c r="C15" s="244">
         <f>Statement!AA94</f>
         <v>0.20851486489537011</v>
       </c>
-      <c r="D15" s="242"/>
-      <c r="F15" s="241">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.4741658193918108</v>
       </c>
-      <c r="G15" s="242"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="208" t="s">
@@ -35773,19 +35773,19 @@
       <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="241">
+      <c r="C17" s="244">
         <f>Statement!AA96</f>
         <v>0.35756517690875234</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="F17" s="241">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1063115845539282</v>
       </c>
-      <c r="G17" s="242"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
@@ -35812,22 +35812,22 @@
       <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="241">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.6781270464963983E-3</v>
       </c>
-      <c r="D19" s="242"/>
-      <c r="F19" s="241">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-8.9390922758116297E-3</v>
       </c>
-      <c r="G19" s="242"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="208" t="s">
@@ -35854,22 +35854,22 @@
       <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="241">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.35795454545454553</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="F21" s="241">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.1447368421052633</v>
       </c>
-      <c r="G21" s="242"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35917,22 +35917,22 @@
       <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="241">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="F25" s="241">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.1517699869310756</v>
       </c>
-      <c r="G25" s="242"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="224" t="s">
@@ -35959,22 +35959,22 @@
       <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="241">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.31147368421052629</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="F27" s="241">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.73741458652907543</v>
       </c>
-      <c r="G27" s="242"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36001,22 +36001,22 @@
       <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="241">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.20752960811374652</v>
       </c>
-      <c r="D29" s="242"/>
-      <c r="F29" s="241">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.92385968500715898</v>
       </c>
-      <c r="G29" s="242"/>
+      <c r="G29" s="245"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36043,43 +36043,25 @@
       <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="241">
+      <c r="C31" s="244">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="F31" s="241">
+      <c r="D31" s="245"/>
+      <c r="F31" s="244">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.28666666666666668</v>
       </c>
-      <c r="G31" s="242"/>
+      <c r="G31" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -36088,6 +36070,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E42AD0-FBCA-C646-BCFF-58984A9B193E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454D0BD5-2DE6-1C4F-A25E-9807A9378ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2316,9 +2316,6 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2328,6 +2325,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2335,12 +2341,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12487,7 +12487,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -12713,12 +12713,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>164.07</v>
-    <v>2.2185999999999999</v>
-    <v>1.91</v>
-    <v>8.3610000000000004E-3</v>
-    <v>-0.36</v>
-    <v>-1.5629999999999999E-3</v>
+    <v>164.27</v>
+    <v>2.222</v>
+    <v>-7.0000000000000007E-2</v>
+    <v>-3.2059999999999999E-4</v>
+    <v>-4.9000000000000002E-2</v>
+    <v>-2.2450000000000001E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12726,25 +12726,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>234.76</v>
+    <v>222</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46269.90036100625</v>
+    <v>46276.999988356249</v>
     <v>0</v>
-    <v>229.63</v>
-    <v>5551676000000</v>
+    <v>218.15</v>
+    <v>5260789000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>231.09</v>
-    <v>29.120100000000001</v>
-    <v>228.45</v>
-    <v>230.36</v>
-    <v>230</v>
+    <v>221.23500000000001</v>
+    <v>27.603000000000002</v>
+    <v>218.36</v>
+    <v>218.29</v>
+    <v>218.24100000000001</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>134506744</v>
-    <v>128965491</v>
+    <v>89060140</v>
+    <v>124388051</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12766,19 +12766,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>48.12</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>0.22</v>
+    <v>4.62E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>48.12</v>
     <v>Index</v>
     <v>3</v>
-    <v>47.32</v>
+    <v>47.48</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
+    <v>47.54</v>
     <v>47.62</v>
+    <v>47.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13000,9 +13000,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13573,18 +13573,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="238" t="s">
+      <c r="B2" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="239"/>
-      <c r="E2" s="238" t="s">
+      <c r="C2" s="238"/>
+      <c r="E2" s="237" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="H2" s="238" t="s">
+      <c r="F2" s="238"/>
+      <c r="H2" s="237" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="239"/>
+      <c r="I2" s="238"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>5573560.2000000002</v>
+        <v>5281526.55</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>5507457.2000000002</v>
+        <v>5215423.55</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>230.36</v>
+        <v>218.29</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13664,14 +13664,14 @@
       </c>
       <c r="C6" s="209" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>230</v>
+        <v>218.24100000000001</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>29.122629582806574</v>
+        <v>27.59671302149178</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13688,14 +13688,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.91</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>18.550629569361881</v>
+        <v>17.578646156867531</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13712,14 +13712,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.36</v>
+        <v>-4.9000000000000002E-2</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.148788130071691E-2</v>
+        <v>2.2676019682226156E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.44836512970638454</v>
+        <v>0.52845018681186851</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13736,14 +13736,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>8.3610000000000004E-3</v>
+        <v>-3.2059999999999999E-4</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.433755860392429E-2</v>
+        <v>3.6236199551055934E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13752,14 +13752,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.5629999999999999E-3</v>
+        <v>-2.2450000000000001E-4</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>9.924536205781001E-3</v>
+        <v>1.0473297724878426E-2</v>
       </c>
       <c r="H10" s="185" t="s">
         <v>406</v>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>1.2154888001389131E-3</v>
+        <v>1.2826973292409181E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>164.07</v>
+        <v>164.27</v>
       </c>
       <c r="E12" s="186" t="s">
         <v>94</v>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2185999999999999</v>
+        <v>2.222</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>128965491</v>
+        <v>124388051</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.1860103350099278E-2</v>
+        <v>1.2515888990466214E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13852,10 +13852,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="240" t="s">
+      <c r="B17" s="239" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="240"/>
+      <c r="C17" s="239"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13928,14 +13928,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="240" t="s">
+      <c r="B25" s="239" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="240"/>
-      <c r="E25" s="238" t="s">
+      <c r="C25" s="239"/>
+      <c r="E25" s="237" t="s">
         <v>339</v>
       </c>
-      <c r="F25" s="239"/>
+      <c r="F25" s="238"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13984,15 +13984,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="240" t="s">
         <v>334</v>
       </c>
-      <c r="C33" s="237"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14011,24 +14011,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="237"/>
-      <c r="C39" s="237"/>
-      <c r="D39" s="237"/>
-      <c r="E39" s="237"/>
-      <c r="F39" s="237"/>
-      <c r="G39" s="237"/>
-      <c r="H39" s="237"/>
+      <c r="B39" s="240"/>
+      <c r="C39" s="240"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="240"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="237" t="s">
+      <c r="B42" s="240" t="s">
         <v>337</v>
       </c>
-      <c r="C42" s="237"/>
-      <c r="D42" s="237"/>
-      <c r="E42" s="237"/>
-      <c r="F42" s="237"/>
-      <c r="G42" s="237"/>
-      <c r="H42" s="237"/>
+      <c r="C42" s="240"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
+      <c r="G42" s="240"/>
+      <c r="H42" s="240"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14075,24 +14075,24 @@
       </c>
     </row>
     <row r="51" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="237"/>
-      <c r="C51" s="237"/>
-      <c r="D51" s="237"/>
-      <c r="E51" s="237"/>
-      <c r="F51" s="237"/>
-      <c r="G51" s="237"/>
-      <c r="H51" s="237"/>
+      <c r="B51" s="240"/>
+      <c r="C51" s="240"/>
+      <c r="D51" s="240"/>
+      <c r="E51" s="240"/>
+      <c r="F51" s="240"/>
+      <c r="G51" s="240"/>
+      <c r="H51" s="240"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="237" t="s">
+      <c r="B54" s="240" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="237"/>
-      <c r="D54" s="237"/>
-      <c r="E54" s="237"/>
-      <c r="F54" s="237"/>
-      <c r="G54" s="237"/>
-      <c r="H54" s="237"/>
+      <c r="C54" s="240"/>
+      <c r="D54" s="240"/>
+      <c r="E54" s="240"/>
+      <c r="F54" s="240"/>
+      <c r="G54" s="240"/>
+      <c r="H54" s="240"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="41" t="s">
@@ -14107,28 +14107,28 @@
       </c>
     </row>
     <row r="61" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="237"/>
-      <c r="C61" s="237"/>
-      <c r="D61" s="237"/>
-      <c r="E61" s="237"/>
-      <c r="F61" s="237"/>
-      <c r="G61" s="237"/>
-      <c r="H61" s="237"/>
+      <c r="B61" s="240"/>
+      <c r="C61" s="240"/>
+      <c r="D61" s="240"/>
+      <c r="E61" s="240"/>
+      <c r="F61" s="240"/>
+      <c r="G61" s="240"/>
+      <c r="H61" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B51:H51"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B51:H51"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14198,36 +14198,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="237" t="s">
+      <c r="S2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
-      <c r="AA2" s="237" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15423,35 +15423,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="P2" s="237" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="237"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="237"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16682,20 +16682,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -18088,6 +18088,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18095,12 +18101,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18138,20 +18138,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="S2" s="251"/>
       <c r="T2" s="251"/>
       <c r="U2" s="251"/>
@@ -19160,16 +19160,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19232,10 +19232,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>230.36</v>
+        <v>218.29</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5573560.2000000002</v>
+        <v>5281526.55</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2185999999999999</v>
+        <v>2.222</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="C11" s="136">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19320,10 +19320,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="240" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="237"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.9331248755311872E-3</v>
+        <v>6.2591342346936946E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99406687512446879</v>
+        <v>0.99374086576530629</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.147457</v>
+        <v>0.14560799999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14681647763781228</v>
+        <v>0.1449438557846251</v>
       </c>
     </row>
   </sheetData>
@@ -19412,20 +19412,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -19711,10 +19711,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="240" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="237"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19734,10 +19734,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="240" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="237"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19851,20 +19851,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20796,10 +20796,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="240" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="237"/>
+      <c r="C37" s="240"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20892,10 +20892,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="237" t="s">
+      <c r="B49" s="240" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="237"/>
+      <c r="C49" s="240"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -20951,10 +20951,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="237" t="s">
+      <c r="B57" s="240" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="237"/>
+      <c r="C57" s="240"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21094,10 +21094,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>230.36</v>
+        <v>218.29</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.44836512970638454</v>
+        <v>0.52845018681186851</v>
       </c>
     </row>
   </sheetData>
@@ -21216,20 +21216,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21592,10 +21592,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="240" t="s">
         <v>401</v>
       </c>
-      <c r="C20" s="237"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21696,20 +21696,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>230.36</v>
+        <v>218.29</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>5551676</v>
+        <v>5260789</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>5485573</v>
+        <v>5194686</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22608,17 +22608,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29193,7 +29193,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>230.36</v>
+        <v>218.29</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>230.36</v>
+        <v>218.29</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30766,7 +30766,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>29.122629582806574</v>
+        <v>27.59671302149178</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30803,7 +30803,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.550629569361881</v>
+        <v>17.578646156867531</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30864,7 +30864,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.244820598819135</v>
+        <v>22.974482933305385</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30925,7 +30925,7 @@
       </c>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5573560.2000000002</v>
+        <v>5281526.55</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5507457.2000000002</v>
+        <v>5215423.55</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31023,7 +31023,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>18.178286227303783</v>
+        <v>17.214380184111246</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31060,7 +31060,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>27.874709356763624</v>
+        <v>26.396649188425894</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31195,7 +31195,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>46.537859456931969</v>
+        <v>44.099450168665037</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31232,7 +31232,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>39.877336348315488</v>
+        <v>37.762835288538525</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31269,7 +31269,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.148788130071691E-2</v>
+        <v>2.2676019682226156E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31306,7 +31306,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.433755860392429E-2</v>
+        <v>3.6236199551055934E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31343,7 +31343,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.2154888001389131E-3</v>
+        <v>1.2826973292409181E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31380,7 +31380,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.924536205781001E-3</v>
+        <v>1.0473297724878426E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31417,7 +31417,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1140276191867454E-2</v>
+        <v>1.1756260128996228E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31920,7 +31920,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.1860103350099278E-2</v>
+        <v>1.2515888990466214E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -33106,15 +33106,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="E4" s="237" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33122,7 +33122,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>230.36</v>
+        <v>218.29</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -33138,7 +33138,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5573560.2000000002</v>
+        <v>5281526.55</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>5507457.2000000002</v>
+        <v>5215423.55</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33178,7 +33178,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>29.122629582806574</v>
+        <v>27.59671302149178</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>18.550629569361881</v>
+        <v>17.578646156867531</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33218,7 +33218,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.244820598819135</v>
+        <v>22.974482933305385</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33238,7 +33238,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.178286227303783</v>
+        <v>17.214380184111246</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33247,18 +33247,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>27.874709356763624</v>
+        <v>26.396649188425894</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="237"/>
-      <c r="E15" s="237" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="237"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33309,14 +33309,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="240" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="237"/>
-      <c r="E21" s="237" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="237"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33385,14 +33385,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="237" t="s">
+      <c r="B29" s="240" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="237"/>
-      <c r="E29" s="237" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="237"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33468,14 +33468,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="240" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="237"/>
-      <c r="E37" s="237" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="237"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33483,7 +33483,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.433755860392429E-2</v>
+        <v>3.6236199551055934E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33499,7 +33499,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.148788130071691E-2</v>
+        <v>2.2676019682226156E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33515,7 +33515,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.2154888001389131E-3</v>
+        <v>1.2826973292409181E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33531,7 +33531,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.924536205781001E-3</v>
+        <v>1.0473297724878426E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33540,18 +33540,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>1.1140276191867454E-2</v>
+        <v>1.1756260128996228E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="237" t="s">
+      <c r="B45" s="240" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="237"/>
-      <c r="E45" s="237" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="237"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33584,18 +33584,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.1860103350099278E-2</v>
+        <v>1.2515888990466214E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="237" t="s">
+      <c r="B51" s="240" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="237"/>
-      <c r="E51" s="237" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="237"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33764,7 +33764,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>230.36</v>
+        <v>218.29</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5573560.2000000002</v>
+        <v>5281526.55</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>5507457.2000000002</v>
+        <v>5215423.55</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33851,7 +33851,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>29.122629582806574</v>
+        <v>27.59671302149178</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33880,7 +33880,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>18.550629569361881</v>
+        <v>17.578646156867531</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33909,7 +33909,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.244820598819135</v>
+        <v>22.974482933305385</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33938,7 +33938,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.178286227303783</v>
+        <v>17.214380184111246</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33967,7 +33967,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>27.874709356763624</v>
+        <v>26.396649188425894</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34740,7 +34740,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.433755860392429E-2</v>
+        <v>3.6236199551055934E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.148788130071691E-2</v>
+        <v>2.2676019682226156E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34798,7 +34798,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.2154888001389131E-3</v>
+        <v>1.2826973292409181E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34827,7 +34827,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.924536205781001E-3</v>
+        <v>1.0473297724878426E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34856,7 +34856,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>1.1140276191867454E-2</v>
+        <v>1.1756260128996228E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35092,7 +35092,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.1860103350099278E-2</v>
+        <v>1.2515888990466214E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35604,14 +35604,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35678,19 +35678,19 @@
       <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="241">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="242"/>
+      <c r="F7" s="241">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="208" t="s">
@@ -35717,19 +35717,19 @@
       <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="241">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="242"/>
+      <c r="F9" s="241">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="242"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="208" t="s">
@@ -35756,19 +35756,19 @@
       <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="241">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="242"/>
+      <c r="F11" s="241">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="242"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="208" t="s">
@@ -35795,19 +35795,19 @@
       <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="241">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="242"/>
+      <c r="F13" s="241">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="242"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
@@ -35834,19 +35834,19 @@
       <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="241">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="242"/>
+      <c r="F15" s="241">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="208" t="s">
@@ -35873,19 +35873,19 @@
       <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="241">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="242"/>
+      <c r="F17" s="241">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="242"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
@@ -35912,22 +35912,22 @@
       <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="241">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="242"/>
+      <c r="F19" s="241">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="242"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="208" t="s">
@@ -35954,22 +35954,22 @@
       <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="241">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="242"/>
+      <c r="F21" s="241">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="242"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36017,22 +36017,22 @@
       <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="241">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="242"/>
+      <c r="F25" s="241">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="242"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="224" t="s">
@@ -36059,22 +36059,22 @@
       <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="241">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="242"/>
+      <c r="F27" s="241">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="242"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36101,22 +36101,22 @@
       <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="241">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="242"/>
+      <c r="F29" s="241">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="242"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36143,25 +36143,43 @@
       <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="244">
+      <c r="C31" s="241">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="245"/>
-      <c r="F31" s="244">
+      <c r="D31" s="242"/>
+      <c r="F31" s="241">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="245"/>
+      <c r="G31" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -36170,24 +36188,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454D0BD5-2DE6-1C4F-A25E-9807A9378ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ED4094-7786-8144-A094-8E98E9598FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,12 +161,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2316,6 +2346,9 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2325,15 +2358,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2341,6 +2365,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12695,7 +12725,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12714,11 +12744,9 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>164.27</v>
-    <v>2.222</v>
-    <v>-7.0000000000000007E-2</v>
-    <v>-3.2059999999999999E-4</v>
-    <v>-4.9000000000000002E-2</v>
-    <v>-2.2450000000000001E-4</v>
+    <v>2.2185000000000001</v>
+    <v>2.0600999999999998</v>
+    <v>9.0600000000000003E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12726,35 +12754,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>222</v>
+    <v>229.98</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46276.999988356249</v>
+    <v>46287.767407418753</v>
     <v>0</v>
-    <v>218.15</v>
-    <v>5260789000000</v>
+    <v>226.5</v>
+    <v>5529506410000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>221.23500000000001</v>
-    <v>27.603000000000002</v>
-    <v>218.36</v>
-    <v>218.29</v>
-    <v>218.24100000000001</v>
+    <v>226.94</v>
+    <v>29.003799999999998</v>
+    <v>227.38</v>
+    <v>229.4401</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>89060140</v>
-    <v>124388051</v>
+    <v>55208372</v>
+    <v>127595005</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12766,30 +12808,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.12</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.62E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>48.12</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>3</v>
-    <v>47.48</v>
+    <v>6</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.54</v>
-    <v>47.62</v>
-    <v>47.84</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12811,8 +12853,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12833,7 +12873,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12843,6 +12882,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12878,7 +12922,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12889,16 +12933,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12992,19 +13033,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13076,9 +13111,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13086,9 +13118,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13573,18 +13602,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="238" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="238"/>
-      <c r="E2" s="237" t="s">
+      <c r="C2" s="239"/>
+      <c r="E2" s="238" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="238"/>
-      <c r="H2" s="237" t="s">
+      <c r="F2" s="239"/>
+      <c r="H2" s="238" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="238"/>
+      <c r="I2" s="239"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13599,7 +13628,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>5281526.55</v>
+        <v>5551303.2194999997</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13623,7 +13652,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>5215423.55</v>
+        <v>5485200.2194999997</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13640,7 +13669,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>218.29</v>
+        <v>229.4401</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13662,16 +13691,16 @@
       <c r="B6" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="209" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>218.24100000000001</v>
+      <c r="C6" s="209" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>27.59671302149178</v>
+        <v>29.006333754740833</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13688,14 +13717,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-7.0000000000000007E-2</v>
+        <v>2.0600999999999998</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>17.578646156867531</v>
+        <v>18.476551065538057</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13710,16 +13739,16 @@
       <c r="B8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-4.9000000000000002E-2</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.2676019682226156E-2</v>
+        <v>2.1574033207068632E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13727,7 +13756,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.52845018681186851</v>
+        <v>0.45417209667866587</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13736,30 +13765,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.2059999999999999E-4</v>
+        <v>9.0600000000000003E-3</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.6236199551055934E-2</v>
+        <v>3.4475229046709792E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.2450000000000001E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.0473297724878426E-2</v>
+        <v>9.9643268999783027E-3</v>
       </c>
       <c r="H10" s="185" t="s">
         <v>406</v>
@@ -13782,7 +13811,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>1.2826973292409181E-3</v>
+        <v>1.2203620901490193E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13807,7 +13836,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.222</v>
+        <v>2.2185000000000001</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13823,7 +13852,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>124388051</v>
+        <v>127595005</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13839,7 +13868,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.2515888990466214E-2</v>
+        <v>1.1907654362637E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13852,10 +13881,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="239" t="s">
+      <c r="B17" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="239"/>
+      <c r="C17" s="240"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13928,14 +13957,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="239" t="s">
+      <c r="B25" s="240" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="239"/>
-      <c r="E25" s="237" t="s">
+      <c r="C25" s="240"/>
+      <c r="E25" s="238" t="s">
         <v>339</v>
       </c>
-      <c r="F25" s="238"/>
+      <c r="F25" s="239"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13944,12 +13973,12 @@
       <c r="C26" s="171">
         <v>0.21</v>
       </c>
-      <c r="E26" s="186" t="e" vm="2">
+      <c r="E26" s="186" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.84</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13964,7 +13993,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13984,15 +14013,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="240" t="s">
+      <c r="B33" s="237" t="s">
         <v>334</v>
       </c>
-      <c r="C33" s="240"/>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14011,24 +14040,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="240"/>
-      <c r="C39" s="240"/>
-      <c r="D39" s="240"/>
-      <c r="E39" s="240"/>
-      <c r="F39" s="240"/>
-      <c r="G39" s="240"/>
-      <c r="H39" s="240"/>
+      <c r="B39" s="237"/>
+      <c r="C39" s="237"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="240" t="s">
+      <c r="B42" s="237" t="s">
         <v>337</v>
       </c>
-      <c r="C42" s="240"/>
-      <c r="D42" s="240"/>
-      <c r="E42" s="240"/>
-      <c r="F42" s="240"/>
-      <c r="G42" s="240"/>
-      <c r="H42" s="240"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14075,24 +14104,24 @@
       </c>
     </row>
     <row r="51" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="240"/>
-      <c r="C51" s="240"/>
-      <c r="D51" s="240"/>
-      <c r="E51" s="240"/>
-      <c r="F51" s="240"/>
-      <c r="G51" s="240"/>
-      <c r="H51" s="240"/>
+      <c r="B51" s="237"/>
+      <c r="C51" s="237"/>
+      <c r="D51" s="237"/>
+      <c r="E51" s="237"/>
+      <c r="F51" s="237"/>
+      <c r="G51" s="237"/>
+      <c r="H51" s="237"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="240" t="s">
+      <c r="B54" s="237" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="240"/>
-      <c r="D54" s="240"/>
-      <c r="E54" s="240"/>
-      <c r="F54" s="240"/>
-      <c r="G54" s="240"/>
-      <c r="H54" s="240"/>
+      <c r="C54" s="237"/>
+      <c r="D54" s="237"/>
+      <c r="E54" s="237"/>
+      <c r="F54" s="237"/>
+      <c r="G54" s="237"/>
+      <c r="H54" s="237"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="41" t="s">
@@ -14107,28 +14136,28 @@
       </c>
     </row>
     <row r="61" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="240"/>
-      <c r="C61" s="240"/>
-      <c r="D61" s="240"/>
-      <c r="E61" s="240"/>
-      <c r="F61" s="240"/>
-      <c r="G61" s="240"/>
-      <c r="H61" s="240"/>
+      <c r="B61" s="237"/>
+      <c r="C61" s="237"/>
+      <c r="D61" s="237"/>
+      <c r="E61" s="237"/>
+      <c r="F61" s="237"/>
+      <c r="G61" s="237"/>
+      <c r="H61" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B54:H54"/>
     <mergeCell ref="B61:H61"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B51:H51"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14198,36 +14227,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="240" t="s">
+      <c r="S2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240" t="s">
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
+      <c r="AA2" s="237" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15423,35 +15452,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="P2" s="240" t="s">
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
+      <c r="P2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="240"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240" t="s">
+      <c r="Q2" s="237"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="237"/>
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16682,20 +16711,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -18088,12 +18117,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18101,6 +18124,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18138,20 +18167,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="S2" s="251"/>
       <c r="T2" s="251"/>
       <c r="U2" s="251"/>
@@ -19160,16 +19189,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19232,10 +19261,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="237"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19252,7 +19281,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>218.29</v>
+        <v>229.4401</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19261,7 +19290,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5281526.55</v>
+        <v>5551303.2194999997</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19279,7 +19308,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19288,7 +19317,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.222</v>
+        <v>2.2185000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19320,10 +19349,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="237" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="240"/>
+      <c r="C15" s="237"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19331,7 +19360,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.2591342346936946E-3</v>
+        <v>5.9567710046180408E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19340,7 +19369,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99374086576530629</v>
+        <v>0.994043228995382</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19358,7 +19387,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14560799999999999</v>
+        <v>0.14724400000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19367,7 +19396,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1449438557846251</v>
+        <v>0.14660219366487845</v>
       </c>
     </row>
   </sheetData>
@@ -19412,20 +19441,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -19711,10 +19740,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="240" t="s">
+      <c r="B13" s="237" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="240"/>
+      <c r="C13" s="237"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19734,10 +19763,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="240" t="s">
+      <c r="B18" s="237" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="240"/>
+      <c r="C18" s="237"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19851,20 +19880,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20796,10 +20825,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="237" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="240"/>
+      <c r="C37" s="237"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20892,10 +20921,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="240" t="s">
+      <c r="B49" s="237" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="240"/>
+      <c r="C49" s="237"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -20951,10 +20980,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="240" t="s">
+      <c r="B57" s="237" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="240"/>
+      <c r="C57" s="237"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21094,10 +21123,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="237"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21151,7 +21180,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>218.29</v>
+        <v>229.4401</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21160,7 +21189,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.52845018681186851</v>
+        <v>0.45417209667866587</v>
       </c>
     </row>
   </sheetData>
@@ -21216,20 +21245,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21592,10 +21621,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="240" t="s">
+      <c r="B20" s="237" t="s">
         <v>401</v>
       </c>
-      <c r="C20" s="240"/>
+      <c r="C20" s="237"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21696,20 +21725,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -21989,7 +22018,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>218.29</v>
+        <v>229.4401</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22055,7 +22084,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>5260789</v>
+        <v>5529506.4100000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22082,7 +22111,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>5194686</v>
+        <v>5463403.4100000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22608,17 +22637,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29193,7 +29222,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>218.29</v>
+        <v>229.4401</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29264,7 +29293,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>218.29</v>
+        <v>229.4401</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30766,7 +30795,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>27.59671302149178</v>
+        <v>29.006333754740833</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30803,7 +30832,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>17.578646156867531</v>
+        <v>18.476551065538057</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30864,7 +30893,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>22.974482933305385</v>
+        <v>24.148003397617302</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30925,7 +30954,7 @@
       </c>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5281526.55</v>
+        <v>5551303.2194999997</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30986,7 +31015,7 @@
       </c>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5215423.55</v>
+        <v>5485200.2194999997</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31023,7 +31052,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>17.214380184111246</v>
+        <v>18.104823330109681</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31060,7 +31089,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>26.396649188425894</v>
+        <v>27.762060844016823</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31195,7 +31224,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>44.099450168665037</v>
+        <v>46.35201913346247</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31232,7 +31261,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>37.762835288538525</v>
+        <v>39.716182286601416</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31269,7 +31298,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.2676019682226156E-2</v>
+        <v>2.1574033207068632E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31306,7 +31335,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.6236199551055934E-2</v>
+        <v>3.4475229046709792E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31343,7 +31372,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.2826973292409181E-3</v>
+        <v>1.2203620901490193E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31380,7 +31409,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>1.0473297724878426E-2</v>
+        <v>9.9643268999783027E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31417,7 +31446,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1756260128996228E-2</v>
+        <v>1.1184941183161037E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31920,7 +31949,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.2515888990466214E-2</v>
+        <v>1.1907654362637E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -33106,15 +33135,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="240"/>
-      <c r="E4" s="240" t="s">
+      <c r="C4" s="237"/>
+      <c r="E4" s="237" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33122,7 +33151,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>218.29</v>
+        <v>229.4401</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -33138,7 +33167,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5281526.55</v>
+        <v>5551303.2194999997</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33158,7 +33187,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>5215423.55</v>
+        <v>5485200.2194999997</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33178,7 +33207,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>27.59671302149178</v>
+        <v>29.006333754740833</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33198,7 +33227,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>17.578646156867531</v>
+        <v>18.476551065538057</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33218,7 +33247,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>22.974482933305385</v>
+        <v>24.148003397617302</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33238,7 +33267,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>17.214380184111246</v>
+        <v>18.104823330109681</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33247,18 +33276,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>26.396649188425894</v>
+        <v>27.762060844016823</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="240"/>
-      <c r="E15" s="240" t="s">
+      <c r="C15" s="237"/>
+      <c r="E15" s="237" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="240"/>
+      <c r="F15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33309,14 +33338,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="240" t="s">
+      <c r="B21" s="237" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="240"/>
-      <c r="E21" s="240" t="s">
+      <c r="C21" s="237"/>
+      <c r="E21" s="237" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="240"/>
+      <c r="F21" s="237"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33385,14 +33414,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="240" t="s">
+      <c r="B29" s="237" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="240"/>
-      <c r="E29" s="240" t="s">
+      <c r="C29" s="237"/>
+      <c r="E29" s="237" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="240"/>
+      <c r="F29" s="237"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33468,14 +33497,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="237" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="240"/>
-      <c r="E37" s="240" t="s">
+      <c r="C37" s="237"/>
+      <c r="E37" s="237" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="240"/>
+      <c r="F37" s="237"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33483,7 +33512,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.6236199551055934E-2</v>
+        <v>3.4475229046709792E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33499,7 +33528,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.2676019682226156E-2</v>
+        <v>2.1574033207068632E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33515,7 +33544,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.2826973292409181E-3</v>
+        <v>1.2203620901490193E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33531,7 +33560,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>1.0473297724878426E-2</v>
+        <v>9.9643268999783027E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33540,18 +33569,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>1.1756260128996228E-2</v>
+        <v>1.1184941183161037E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="240" t="s">
+      <c r="B45" s="237" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="240"/>
-      <c r="E45" s="240" t="s">
+      <c r="C45" s="237"/>
+      <c r="E45" s="237" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="240"/>
+      <c r="F45" s="237"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33584,18 +33613,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.2515888990466214E-2</v>
+        <v>1.1907654362637E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="240" t="s">
+      <c r="B51" s="237" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="240"/>
-      <c r="E51" s="240" t="s">
+      <c r="C51" s="237"/>
+      <c r="E51" s="237" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="240"/>
+      <c r="F51" s="237"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33764,7 +33793,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>218.29</v>
+        <v>229.4401</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33793,7 +33822,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5281526.55</v>
+        <v>5551303.2194999997</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33822,7 +33851,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>5215423.55</v>
+        <v>5485200.2194999997</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33851,7 +33880,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>27.59671302149178</v>
+        <v>29.006333754740833</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33880,7 +33909,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>17.578646156867531</v>
+        <v>18.476551065538057</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33909,7 +33938,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>22.974482933305385</v>
+        <v>24.148003397617302</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33938,7 +33967,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>17.214380184111246</v>
+        <v>18.104823330109681</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33967,7 +33996,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>26.396649188425894</v>
+        <v>27.762060844016823</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34740,7 +34769,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.6236199551055934E-2</v>
+        <v>3.4475229046709792E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34769,7 +34798,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.2676019682226156E-2</v>
+        <v>2.1574033207068632E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34798,7 +34827,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.2826973292409181E-3</v>
+        <v>1.2203620901490193E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34827,7 +34856,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>1.0473297724878426E-2</v>
+        <v>9.9643268999783027E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34856,7 +34885,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>1.1756260128996228E-2</v>
+        <v>1.1184941183161037E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35092,7 +35121,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.2515888990466214E-2</v>
+        <v>1.1907654362637E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35604,14 +35633,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="241" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35678,19 +35707,19 @@
       <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="241">
+      <c r="C7" s="244">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="242"/>
-      <c r="F7" s="241">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="242"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="208" t="s">
@@ -35717,19 +35746,19 @@
       <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="241">
+      <c r="C9" s="244">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="F9" s="241">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="242"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="208" t="s">
@@ -35756,19 +35785,19 @@
       <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="241">
+      <c r="C11" s="244">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="F11" s="241">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="242"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="208" t="s">
@@ -35795,19 +35824,19 @@
       <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="241">
+      <c r="C13" s="244">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="F13" s="241">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="242"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
@@ -35834,19 +35863,19 @@
       <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="241">
+      <c r="C15" s="244">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="242"/>
-      <c r="F15" s="241">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="242"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="208" t="s">
@@ -35873,19 +35902,19 @@
       <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="241">
+      <c r="C17" s="244">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="F17" s="241">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="242"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
@@ -35912,22 +35941,22 @@
       <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="241">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="242"/>
-      <c r="F19" s="241">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="242"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="208" t="s">
@@ -35954,22 +35983,22 @@
       <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="241">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="F21" s="241">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="242"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36017,22 +36046,22 @@
       <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="241">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="F25" s="241">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="242"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="224" t="s">
@@ -36059,22 +36088,22 @@
       <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="241">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="F27" s="241">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="242"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36101,22 +36130,22 @@
       <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="241">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="242"/>
-      <c r="F29" s="241">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="242"/>
+      <c r="G29" s="245"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36143,43 +36172,25 @@
       <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="241">
+      <c r="C31" s="244">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="F31" s="241">
+      <c r="D31" s="245"/>
+      <c r="F31" s="244">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="242"/>
+      <c r="G31" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -36188,6 +36199,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465D585F-0742-B847-B8A2-6B2037285B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1367C4-747C-F24F-B18F-CA37D53AF702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2327,10 +2297,42 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2342,36 +2344,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2381,8 +2353,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12708,7 +12678,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12728,8 +12698,10 @@
     <v>236.54</v>
     <v>164.27</v>
     <v>2.2193999999999998</v>
-    <v>0.57150000000000001</v>
-    <v>2.545E-3</v>
+    <v>0.49</v>
+    <v>2.1819999999999999E-3</v>
+    <v>-6.1499999999999999E-2</v>
+    <v>-2.7320000000000003E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12740,46 +12712,32 @@
     <v>226.94</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.718384375003</v>
+    <v>46290.840027488281</v>
     <v>0</v>
     <v>223.13290000000001</v>
-    <v>5426151150000</v>
+    <v>5424187000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
     <v>225.01</v>
-    <v>28.461600000000001</v>
+    <v>28.4513</v>
     <v>224.58</v>
-    <v>225.1515</v>
+    <v>225.07</v>
+    <v>225.0085</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>46101358</v>
+    <v>87178721</v>
     <v>126361390</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12798,7 +12756,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -12808,13 +12766,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12836,6 +12794,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12856,6 +12816,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12865,11 +12826,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12905,7 +12861,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12916,13 +12872,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13016,13 +12975,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13094,6 +13059,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13101,6 +13069,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13585,18 +13556,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="238" t="s">
+      <c r="B2" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="239"/>
-      <c r="E2" s="238" t="s">
+      <c r="C2" s="237"/>
+      <c r="E2" s="236" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="H2" s="238" t="s">
+      <c r="F2" s="237"/>
+      <c r="H2" s="236" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="239"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -13611,7 +13582,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5447540.5424999995</v>
+        <v>5445568.6499999994</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13635,7 +13606,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5381437.5424999995</v>
+        <v>5379465.6499999994</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13643,7 +13614,7 @@
       </c>
       <c r="I4" s="208">
         <f>'AVG target price'!C6</f>
-        <v>441.4166054000072</v>
+        <v>439.18110219686605</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13652,7 +13623,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>225.1515</v>
+        <v>225.07</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13674,16 +13645,16 @@
       <c r="B6" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="205" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="205" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>225.0085</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>28.464159292035397</v>
+        <v>28.453855878634638</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13691,7 +13662,7 @@
       </c>
       <c r="I6" s="208">
         <f>'AVG target price'!C8</f>
-        <v>458.54512264255123</v>
+        <v>456.30961943941008</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13700,14 +13671,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.57150000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>18.131194970855102</v>
+        <v>18.12463186827695</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13715,23 +13686,23 @@
       </c>
       <c r="I7" s="209">
         <f>'AVG target price'!C9</f>
-        <v>354.15193278752719</v>
+        <v>353.03418118595664</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-6.1499999999999999E-2</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.198496717291756E-2</v>
+        <v>2.1992928139837151E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B11</f>
@@ -13739,7 +13710,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.5729494708564109</v>
+        <v>0.56855281106303213</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13748,30 +13719,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.545E-3</v>
+        <v>2.1819999999999999E-3</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.5131900076170931E-2</v>
+        <v>3.5144621673257208E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-2.7320000000000003E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.0154123602835031E-2</v>
+        <v>1.015780050812508E-2</v>
       </c>
       <c r="H10" s="181" t="s">
         <v>397</v>
@@ -13794,7 +13765,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.243607082342334E-3</v>
+        <v>1.2440574043630873E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13851,7 +13822,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.2134466826687229E-2</v>
+        <v>1.2138860833202425E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13864,10 +13835,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="240" t="s">
+      <c r="B17" s="238" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="240"/>
+      <c r="C17" s="238"/>
       <c r="E17" s="181" t="s">
         <v>288</v>
       </c>
@@ -13940,14 +13911,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="240" t="s">
+      <c r="B25" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="240"/>
-      <c r="E25" s="238" t="s">
+      <c r="C25" s="238"/>
+      <c r="E25" s="236" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="239"/>
+      <c r="F25" s="237"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -13956,7 +13927,7 @@
       <c r="C26" s="167">
         <v>0.21</v>
       </c>
-      <c r="E26" s="182" t="e" vm="5">
+      <c r="E26" s="182" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="216" cm="1">
@@ -13996,15 +13967,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="234" t="s">
+      <c r="B33" s="235" t="s">
         <v>326</v>
       </c>
-      <c r="C33" s="234"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="234"/>
-      <c r="G33" s="234"/>
-      <c r="H33" s="234"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14023,24 +13994,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="234"/>
-      <c r="C39" s="234"/>
-      <c r="D39" s="234"/>
-      <c r="E39" s="234"/>
-      <c r="F39" s="234"/>
-      <c r="G39" s="234"/>
-      <c r="H39" s="234"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="234" t="s">
+      <c r="B42" s="235" t="s">
         <v>329</v>
       </c>
-      <c r="C42" s="234"/>
-      <c r="D42" s="234"/>
-      <c r="E42" s="234"/>
-      <c r="F42" s="234"/>
-      <c r="G42" s="234"/>
-      <c r="H42" s="234"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14087,24 +14058,24 @@
       </c>
     </row>
     <row r="51" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="234"/>
-      <c r="C51" s="234"/>
-      <c r="D51" s="234"/>
-      <c r="E51" s="234"/>
-      <c r="F51" s="234"/>
-      <c r="G51" s="234"/>
-      <c r="H51" s="234"/>
+      <c r="B51" s="235"/>
+      <c r="C51" s="235"/>
+      <c r="D51" s="235"/>
+      <c r="E51" s="235"/>
+      <c r="F51" s="235"/>
+      <c r="G51" s="235"/>
+      <c r="H51" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="234" t="s">
+      <c r="B54" s="235" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="234"/>
-      <c r="D54" s="234"/>
-      <c r="E54" s="234"/>
-      <c r="F54" s="234"/>
-      <c r="G54" s="234"/>
-      <c r="H54" s="234"/>
+      <c r="C54" s="235"/>
+      <c r="D54" s="235"/>
+      <c r="E54" s="235"/>
+      <c r="F54" s="235"/>
+      <c r="G54" s="235"/>
+      <c r="H54" s="235"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="41" t="s">
@@ -14119,28 +14090,28 @@
       </c>
     </row>
     <row r="61" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="234"/>
-      <c r="C61" s="234"/>
-      <c r="D61" s="234"/>
-      <c r="E61" s="234"/>
-      <c r="F61" s="234"/>
-      <c r="G61" s="234"/>
-      <c r="H61" s="234"/>
+      <c r="B61" s="235"/>
+      <c r="C61" s="235"/>
+      <c r="D61" s="235"/>
+      <c r="E61" s="235"/>
+      <c r="F61" s="235"/>
+      <c r="G61" s="235"/>
+      <c r="H61" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B54:H54"/>
     <mergeCell ref="B61:H61"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B51:H51"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14210,36 +14181,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="234" t="s">
+      <c r="S2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234"/>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
-      <c r="AA2" s="234" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="234"/>
-      <c r="AC2" s="234"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14250,32 +14221,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="246" t="s">
+      <c r="S4" s="245" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
-      <c r="AA4" s="247"/>
-      <c r="AB4" s="247"/>
-      <c r="AC4" s="247"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14860,33 +14831,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="233" t="s">
+      <c r="C12" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="233"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="233"/>
+      <c r="D12" s="244"/>
+      <c r="E12" s="244"/>
+      <c r="F12" s="244"/>
+      <c r="G12" s="244"/>
+      <c r="H12" s="244"/>
+      <c r="I12" s="244"/>
+      <c r="J12" s="244"/>
+      <c r="K12" s="244"/>
+      <c r="L12" s="244"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="246" t="s">
+      <c r="S12" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="247"/>
-      <c r="U12" s="247"/>
-      <c r="V12" s="247"/>
-      <c r="W12" s="247"/>
-      <c r="X12" s="247"/>
-      <c r="Y12" s="247"/>
-      <c r="Z12" s="247"/>
-      <c r="AA12" s="247"/>
-      <c r="AB12" s="247"/>
-      <c r="AC12" s="247"/>
+      <c r="T12" s="246"/>
+      <c r="U12" s="246"/>
+      <c r="V12" s="246"/>
+      <c r="W12" s="246"/>
+      <c r="X12" s="246"/>
+      <c r="Y12" s="246"/>
+      <c r="Z12" s="246"/>
+      <c r="AA12" s="246"/>
+      <c r="AB12" s="246"/>
+      <c r="AC12" s="246"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -15435,35 +15406,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="P2" s="234" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="234"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15472,31 +15443,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
-      <c r="P4" s="247" t="s">
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="P4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="247"/>
-      <c r="R4" s="247"/>
-      <c r="S4" s="247"/>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15691,32 +15662,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="233" t="s">
+      <c r="C9" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="247" t="s">
+      <c r="P9" s="246" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="247"/>
-      <c r="R9" s="247"/>
-      <c r="S9" s="247"/>
-      <c r="T9" s="247"/>
-      <c r="U9" s="247"/>
-      <c r="V9" s="247"/>
-      <c r="W9" s="247"/>
-      <c r="X9" s="247"/>
-      <c r="Y9" s="247"/>
-      <c r="Z9" s="247"/>
+      <c r="Q9" s="246"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
+      <c r="W9" s="246"/>
+      <c r="X9" s="246"/>
+      <c r="Y9" s="246"/>
+      <c r="Z9" s="246"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16192,31 +16163,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="233" t="s">
+      <c r="C17" s="244" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="233"/>
-      <c r="E17" s="233"/>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="233"/>
-      <c r="L17" s="233"/>
-      <c r="P17" s="247" t="s">
+      <c r="D17" s="244"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="244"/>
+      <c r="K17" s="244"/>
+      <c r="L17" s="244"/>
+      <c r="P17" s="246" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="247"/>
-      <c r="R17" s="247"/>
-      <c r="S17" s="247"/>
-      <c r="T17" s="247"/>
-      <c r="U17" s="247"/>
-      <c r="V17" s="247"/>
-      <c r="W17" s="247"/>
-      <c r="X17" s="247"/>
-      <c r="Y17" s="247"/>
-      <c r="Z17" s="247"/>
+      <c r="Q17" s="246"/>
+      <c r="R17" s="246"/>
+      <c r="S17" s="246"/>
+      <c r="T17" s="246"/>
+      <c r="U17" s="246"/>
+      <c r="V17" s="246"/>
+      <c r="W17" s="246"/>
+      <c r="X17" s="246"/>
+      <c r="Y17" s="246"/>
+      <c r="Z17" s="246"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16694,60 +16665,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="235"/>
-      <c r="H3" s="236" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
-      <c r="P3" s="237"/>
-      <c r="Q3" s="237"/>
-      <c r="R3" s="237"/>
-      <c r="S3" s="237"/>
-      <c r="T3" s="237"/>
-      <c r="U3" s="237"/>
-      <c r="V3" s="237"/>
-      <c r="W3" s="237"/>
-      <c r="X3" s="237"/>
-      <c r="Y3" s="237"/>
-      <c r="Z3" s="237"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="P5" s="237"/>
-      <c r="Q5" s="237"/>
-      <c r="R5" s="237"/>
-      <c r="S5" s="237"/>
-      <c r="T5" s="237"/>
-      <c r="U5" s="237"/>
-      <c r="V5" s="237"/>
-      <c r="W5" s="237"/>
-      <c r="X5" s="237"/>
-      <c r="Y5" s="237"/>
-      <c r="Z5" s="237"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -16933,30 +16904,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="233" t="s">
+      <c r="C11" s="244" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="237"/>
-      <c r="Q11" s="237"/>
-      <c r="R11" s="237"/>
-      <c r="S11" s="237"/>
-      <c r="T11" s="237"/>
-      <c r="U11" s="237"/>
-      <c r="V11" s="237"/>
-      <c r="W11" s="237"/>
-      <c r="X11" s="237"/>
-      <c r="Y11" s="237"/>
-      <c r="Z11" s="237"/>
+      <c r="P11" s="249"/>
+      <c r="Q11" s="249"/>
+      <c r="R11" s="249"/>
+      <c r="S11" s="249"/>
+      <c r="T11" s="249"/>
+      <c r="U11" s="249"/>
+      <c r="V11" s="249"/>
+      <c r="W11" s="249"/>
+      <c r="X11" s="249"/>
+      <c r="Y11" s="249"/>
+      <c r="Z11" s="249"/>
       <c r="AB11" s="111"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17198,18 +17169,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="244" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17422,23 +17393,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="237"/>
-      <c r="C25" s="237"/>
+      <c r="B25" s="249"/>
+      <c r="C25" s="249"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="233" t="s">
+      <c r="C26" s="244" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="233"/>
-      <c r="E26" s="233"/>
-      <c r="F26" s="233"/>
-      <c r="G26" s="233"/>
-      <c r="H26" s="233"/>
-      <c r="I26" s="233"/>
-      <c r="J26" s="233"/>
-      <c r="K26" s="233"/>
-      <c r="L26" s="233"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="244"/>
+      <c r="H26" s="244"/>
+      <c r="I26" s="244"/>
+      <c r="J26" s="244"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="244"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17630,18 +17601,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="233" t="s">
+      <c r="C33" s="244" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
-      <c r="I33" s="233"/>
-      <c r="J33" s="233"/>
-      <c r="K33" s="233"/>
-      <c r="L33" s="233"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="244"/>
+      <c r="J33" s="244"/>
+      <c r="K33" s="244"/>
+      <c r="L33" s="244"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17825,18 +17796,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="233" t="s">
+      <c r="C40" s="244" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="233"/>
-      <c r="E40" s="233"/>
-      <c r="F40" s="233"/>
-      <c r="G40" s="233"/>
-      <c r="H40" s="233"/>
-      <c r="I40" s="233"/>
-      <c r="J40" s="233"/>
-      <c r="K40" s="233"/>
-      <c r="L40" s="233"/>
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18100,12 +18071,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18113,6 +18078,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18150,60 +18121,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="S2" s="237"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
-      <c r="AA2" s="237"/>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="110"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="244" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
-      <c r="S4" s="237"/>
-      <c r="T4" s="237"/>
-      <c r="U4" s="237"/>
-      <c r="V4" s="237"/>
-      <c r="W4" s="237"/>
-      <c r="X4" s="237"/>
-      <c r="Y4" s="237"/>
-      <c r="Z4" s="237"/>
-      <c r="AA4" s="237"/>
-      <c r="AB4" s="237"/>
-      <c r="AC4" s="237"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="S4" s="249"/>
+      <c r="T4" s="249"/>
+      <c r="U4" s="249"/>
+      <c r="V4" s="249"/>
+      <c r="W4" s="249"/>
+      <c r="X4" s="249"/>
+      <c r="Y4" s="249"/>
+      <c r="Z4" s="249"/>
+      <c r="AA4" s="249"/>
+      <c r="AB4" s="249"/>
+      <c r="AC4" s="249"/>
       <c r="AE4" s="111"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18566,18 +18537,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="233" t="s">
+      <c r="C13" s="244" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="233"/>
-      <c r="E13" s="233"/>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="233"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="233"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="244"/>
+      <c r="H13" s="244"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="244"/>
+      <c r="L13" s="244"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18670,18 +18641,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="244" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18873,18 +18844,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="233" t="s">
+      <c r="C25" s="244" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="233"/>
-      <c r="E25" s="233"/>
-      <c r="F25" s="233"/>
-      <c r="G25" s="233"/>
-      <c r="H25" s="233"/>
-      <c r="I25" s="233"/>
-      <c r="J25" s="233"/>
-      <c r="K25" s="233"/>
-      <c r="L25" s="233"/>
+      <c r="D25" s="244"/>
+      <c r="E25" s="244"/>
+      <c r="F25" s="244"/>
+      <c r="G25" s="244"/>
+      <c r="H25" s="244"/>
+      <c r="I25" s="244"/>
+      <c r="J25" s="244"/>
+      <c r="K25" s="244"/>
+      <c r="L25" s="244"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19022,18 +18993,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="233" t="s">
+      <c r="C31" s="244" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="233"/>
-      <c r="E31" s="233"/>
-      <c r="F31" s="233"/>
-      <c r="G31" s="233"/>
-      <c r="H31" s="233"/>
-      <c r="I31" s="233"/>
-      <c r="J31" s="233"/>
-      <c r="K31" s="233"/>
-      <c r="L31" s="233"/>
+      <c r="D31" s="244"/>
+      <c r="E31" s="244"/>
+      <c r="F31" s="244"/>
+      <c r="G31" s="244"/>
+      <c r="H31" s="244"/>
+      <c r="I31" s="244"/>
+      <c r="J31" s="244"/>
+      <c r="K31" s="244"/>
+      <c r="L31" s="244"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19172,16 +19143,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19244,10 +19215,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="235" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="234"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19264,7 +19235,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>225.1515</v>
+        <v>225.07</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19273,7 +19244,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5447540.5424999995</v>
+        <v>5445568.6499999994</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19332,10 +19303,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="234"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19343,7 +19314,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.0695446449431038E-3</v>
+        <v>6.0717291404295262E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19352,7 +19323,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99393045535505686</v>
+        <v>0.99392827085957047</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19379,7 +19350,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15081325348657887</v>
+        <v>0.15081300883837587</v>
       </c>
     </row>
   </sheetData>
@@ -19424,60 +19395,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="235"/>
-      <c r="H3" s="236" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
-      <c r="P3" s="237"/>
-      <c r="Q3" s="237"/>
-      <c r="R3" s="237"/>
-      <c r="S3" s="237"/>
-      <c r="T3" s="237"/>
-      <c r="U3" s="237"/>
-      <c r="V3" s="237"/>
-      <c r="W3" s="237"/>
-      <c r="X3" s="237"/>
-      <c r="Y3" s="237"/>
-      <c r="Z3" s="237"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="P5" s="237"/>
-      <c r="Q5" s="237"/>
-      <c r="R5" s="237"/>
-      <c r="S5" s="237"/>
-      <c r="T5" s="237"/>
-      <c r="U5" s="237"/>
-      <c r="V5" s="237"/>
-      <c r="W5" s="237"/>
-      <c r="X5" s="237"/>
-      <c r="Y5" s="237"/>
-      <c r="Z5" s="237"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19723,10 +19694,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="234" t="s">
+      <c r="B13" s="235" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="234"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19746,10 +19717,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="234" t="s">
+      <c r="B18" s="235" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="234"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19815,10 +19786,10 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="251" t="s">
+      <c r="B26" s="233" t="s">
         <v>184</v>
       </c>
-      <c r="C26" s="252">
+      <c r="C26" s="234">
         <f>C24/C25</f>
         <v>205.87576455664953</v>
       </c>
@@ -19863,37 +19834,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="244" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20113,18 +20084,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="233" t="s">
+      <c r="C11" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20318,18 +20289,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="233" t="s">
+      <c r="C17" s="244" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="233"/>
-      <c r="E17" s="233"/>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="233"/>
-      <c r="L17" s="233"/>
+      <c r="D17" s="244"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="244"/>
+      <c r="K17" s="244"/>
+      <c r="L17" s="244"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20463,18 +20434,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="233" t="s">
+      <c r="C22" s="244" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="233"/>
-      <c r="E22" s="233"/>
-      <c r="F22" s="233"/>
-      <c r="G22" s="233"/>
-      <c r="H22" s="233"/>
-      <c r="I22" s="233"/>
-      <c r="J22" s="233"/>
-      <c r="K22" s="233"/>
-      <c r="L22" s="233"/>
+      <c r="D22" s="244"/>
+      <c r="E22" s="244"/>
+      <c r="F22" s="244"/>
+      <c r="G22" s="244"/>
+      <c r="H22" s="244"/>
+      <c r="I22" s="244"/>
+      <c r="J22" s="244"/>
+      <c r="K22" s="244"/>
+      <c r="L22" s="244"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20558,18 +20529,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="233" t="s">
+      <c r="C27" s="244" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="233"/>
-      <c r="E27" s="233"/>
-      <c r="F27" s="233"/>
-      <c r="G27" s="233"/>
-      <c r="H27" s="233"/>
-      <c r="I27" s="233"/>
-      <c r="J27" s="233"/>
-      <c r="K27" s="233"/>
-      <c r="L27" s="233"/>
+      <c r="D27" s="244"/>
+      <c r="E27" s="244"/>
+      <c r="F27" s="244"/>
+      <c r="G27" s="244"/>
+      <c r="H27" s="244"/>
+      <c r="I27" s="244"/>
+      <c r="J27" s="244"/>
+      <c r="K27" s="244"/>
+      <c r="L27" s="244"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -20839,10 +20810,10 @@
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="234" t="s">
+      <c r="B38" s="235" t="s">
         <v>197</v>
       </c>
-      <c r="C38" s="234"/>
+      <c r="C38" s="235"/>
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -20885,8 +20856,8 @@
         <v>407</v>
       </c>
       <c r="C43" s="24">
-        <f>C42/(1+C40)^5-G31+G32</f>
-        <v>9621660.2240634207</v>
+        <f>C42/(1+C40)^5</f>
+        <v>9567572.2240634207</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -20895,7 +20866,7 @@
       </c>
       <c r="C44" s="109">
         <f>SUM(H9:K9)+C43</f>
-        <v>10613971.767653175</v>
+        <v>10559883.767653175</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -20922,7 +20893,7 @@
       </c>
       <c r="C47" s="109">
         <f>C44+C45-C46</f>
-        <v>10680074.767653175</v>
+        <v>10625986.767653175</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -20935,19 +20906,19 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="251" t="s">
+      <c r="B49" s="233" t="s">
         <v>201</v>
       </c>
-      <c r="C49" s="252">
+      <c r="C49" s="234">
         <f>C47/C48</f>
-        <v>441.4166054000072</v>
+        <v>439.18110219686605</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="234" t="s">
+      <c r="B51" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C51" s="234"/>
+      <c r="C51" s="235"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -20994,19 +20965,19 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="251" t="s">
+      <c r="B57" s="233" t="s">
         <v>201</v>
       </c>
-      <c r="C57" s="252">
+      <c r="C57" s="234">
         <f>C56/(1+C53)^5</f>
         <v>310.77023855090073</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="234" t="s">
+      <c r="B59" s="235" t="s">
         <v>314</v>
       </c>
-      <c r="C59" s="234"/>
+      <c r="C59" s="235"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -21048,8 +21019,8 @@
         <v>407</v>
       </c>
       <c r="C64" s="24">
-        <f>C63/(1+C61)^5-G31+G32</f>
-        <v>10036084.698746772</v>
+        <f>C63/(1+C61)^5</f>
+        <v>9981996.6987467725</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -21058,7 +21029,7 @@
       </c>
       <c r="C65" s="109">
         <f>SUM(H9:K9)+C64</f>
-        <v>11028396.242336527</v>
+        <v>10974308.242336527</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21085,7 +21056,7 @@
       </c>
       <c r="C68" s="109">
         <f>C65+C66-C67</f>
-        <v>11094499.242336527</v>
+        <v>11040411.242336527</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -21098,12 +21069,12 @@
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="251" t="s">
+      <c r="B70" s="233" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="252">
+      <c r="C70" s="234">
         <f>C68/C69</f>
-        <v>458.54512264255123</v>
+        <v>456.30961943941008</v>
       </c>
     </row>
   </sheetData>
@@ -21155,10 +21126,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="235" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="234"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21176,7 +21147,7 @@
       </c>
       <c r="C6" s="134">
         <f>Multiples!C49</f>
-        <v>441.4166054000072</v>
+        <v>439.18110219686605</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21194,16 +21165,16 @@
       </c>
       <c r="C8" s="134">
         <f>Multiples!C70</f>
-        <v>458.54512264255123</v>
+        <v>456.30961943941008</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="251" t="s">
+      <c r="B9" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C9" s="252">
+      <c r="C9" s="234">
         <f>AVERAGE(C5:C8)</f>
-        <v>354.15193278752719</v>
+        <v>353.03418118595664</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21212,7 +21183,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>225.1515</v>
+        <v>225.07</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21221,7 +21192,7 @@
       </c>
       <c r="C11" s="153">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.5729494708564109</v>
+        <v>0.56855281106303213</v>
       </c>
     </row>
   </sheetData>
@@ -21277,37 +21248,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="244" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21420,18 +21391,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="233" t="s">
+      <c r="C9" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21552,18 +21523,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="233" t="s">
+      <c r="C14" s="244" t="s">
         <v>390</v>
       </c>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="233"/>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
+      <c r="D14" s="244"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="244"/>
+      <c r="G14" s="244"/>
+      <c r="H14" s="244"/>
+      <c r="I14" s="244"/>
+      <c r="J14" s="244"/>
+      <c r="K14" s="244"/>
+      <c r="L14" s="244"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21653,10 +21624,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="234" t="s">
+      <c r="B20" s="235" t="s">
         <v>392</v>
       </c>
-      <c r="C20" s="234"/>
+      <c r="C20" s="235"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21703,10 +21674,10 @@
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B26" s="251" t="s">
+      <c r="B26" s="233" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="252">
+      <c r="C26" s="234">
         <f>C23/(C24-C25)</f>
         <v>1.6842105263157894</v>
       </c>
@@ -21757,60 +21728,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="235"/>
-      <c r="H3" s="236" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
-      <c r="P3" s="237"/>
-      <c r="Q3" s="237"/>
-      <c r="R3" s="237"/>
-      <c r="S3" s="237"/>
-      <c r="T3" s="237"/>
-      <c r="U3" s="237"/>
-      <c r="V3" s="237"/>
-      <c r="W3" s="237"/>
-      <c r="X3" s="237"/>
-      <c r="Y3" s="237"/>
-      <c r="Z3" s="237"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="P5" s="237"/>
-      <c r="Q5" s="237"/>
-      <c r="R5" s="237"/>
-      <c r="S5" s="237"/>
-      <c r="T5" s="237"/>
-      <c r="U5" s="237"/>
-      <c r="V5" s="237"/>
-      <c r="W5" s="237"/>
-      <c r="X5" s="237"/>
-      <c r="Y5" s="237"/>
-      <c r="Z5" s="237"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22039,10 +22010,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="248" t="s">
+      <c r="B14" s="250" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="249"/>
+      <c r="C14" s="251"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22050,7 +22021,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>225.1515</v>
+        <v>225.07</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22069,20 +22040,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="252" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="248" t="s">
+      <c r="B19" s="250" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="249"/>
+      <c r="C19" s="251"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22116,7 +22087,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5426151.1500000004</v>
+        <v>5424187</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22143,15 +22114,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5360048.1500000004</v>
+        <v>5358084</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="248" t="s">
+      <c r="B28" s="250" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="249"/>
+      <c r="C28" s="251"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22227,16 +22198,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28811,7 +28782,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>225.1515</v>
+        <v>225.07</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -28882,7 +28853,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>225.1515</v>
+        <v>225.07</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30384,7 +30355,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>28.464159292035397</v>
+        <v>28.453855878634638</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30421,7 +30392,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.131194970855102</v>
+        <v>18.12463186827695</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30482,7 +30453,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>23.69663884812913</v>
+        <v>23.688061174579886</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30543,7 +30514,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5447540.5424999995</v>
+        <v>5445568.6499999994</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30604,7 +30575,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5381437.5424999995</v>
+        <v>5379465.6499999994</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30641,7 +30612,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>17.762337211067798</v>
+        <v>17.755828649135719</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30678,7 +30649,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>27.236890269208768</v>
+        <v>27.226909995495468</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30813,7 +30784,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>45.48562625246317</v>
+        <v>45.469161434153833</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30850,7 +30821,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>38.964877461004107</v>
+        <v>38.950599761221852</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30887,7 +30858,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.198496717291756E-2</v>
+        <v>2.1992928139837151E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30924,7 +30895,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.5131900076170931E-2</v>
+        <v>3.5144621673257208E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30961,7 +30932,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.243607082342334E-3</v>
+        <v>1.2440574043630873E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30998,7 +30969,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>1.0154123602835031E-2</v>
+        <v>1.015780050812508E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31035,7 +31006,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1397987681887914E-2</v>
+        <v>1.1402115002259683E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31538,7 +31509,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.2134466826687229E-2</v>
+        <v>1.2138860833202425E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32724,15 +32695,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="235" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="E4" s="234" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32740,7 +32711,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>225.1515</v>
+        <v>225.07</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32756,7 +32727,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5447540.5424999995</v>
+        <v>5445568.6499999994</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32776,7 +32747,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5381437.5424999995</v>
+        <v>5379465.6499999994</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32796,7 +32767,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.464159292035397</v>
+        <v>28.453855878634638</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -32816,7 +32787,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.131194970855102</v>
+        <v>18.12463186827695</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -32836,7 +32807,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>23.69663884812913</v>
+        <v>23.688061174579886</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32856,7 +32827,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.762337211067798</v>
+        <v>17.755828649135719</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32865,18 +32836,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.236890269208768</v>
+        <v>27.226909995495468</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="234"/>
-      <c r="E15" s="234" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="234"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32927,14 +32898,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="234" t="s">
+      <c r="B21" s="235" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="234"/>
-      <c r="E21" s="234" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="234"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33003,14 +32974,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="234" t="s">
+      <c r="B29" s="235" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="234"/>
-      <c r="E29" s="234" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="234"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33086,14 +33057,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="234" t="s">
+      <c r="B37" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="234"/>
-      <c r="E37" s="234" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="234"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33101,7 +33072,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.5131900076170931E-2</v>
+        <v>3.5144621673257208E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33117,7 +33088,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.198496717291756E-2</v>
+        <v>2.1992928139837151E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33133,7 +33104,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.243607082342334E-3</v>
+        <v>1.2440574043630873E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33149,7 +33120,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0154123602835031E-2</v>
+        <v>1.015780050812508E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33158,18 +33129,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1397987681887914E-2</v>
+        <v>1.1402115002259683E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="234" t="s">
+      <c r="B45" s="235" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="234"/>
-      <c r="E45" s="234" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="234"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33202,18 +33173,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.2134466826687229E-2</v>
+        <v>1.2138860833202425E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="234" t="s">
+      <c r="B51" s="235" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="234"/>
-      <c r="E51" s="234" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="234"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33382,7 +33353,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>225.1515</v>
+        <v>225.07</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33411,7 +33382,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5447540.5424999995</v>
+        <v>5445568.6499999994</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33440,7 +33411,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5381437.5424999995</v>
+        <v>5379465.6499999994</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33469,7 +33440,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.464159292035397</v>
+        <v>28.453855878634638</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33498,7 +33469,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.131194970855102</v>
+        <v>18.12463186827695</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33527,7 +33498,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>23.69663884812913</v>
+        <v>23.688061174579886</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33556,7 +33527,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.762337211067798</v>
+        <v>17.755828649135719</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33585,7 +33556,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.236890269208768</v>
+        <v>27.226909995495468</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34358,7 +34329,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.5131900076170931E-2</v>
+        <v>3.5144621673257208E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34387,7 +34358,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.198496717291756E-2</v>
+        <v>2.1992928139837151E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34416,7 +34387,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.243607082342334E-3</v>
+        <v>1.2440574043630873E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34445,7 +34416,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0154123602835031E-2</v>
+        <v>1.015780050812508E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34474,7 +34445,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1397987681887914E-2</v>
+        <v>1.1402115002259683E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34710,7 +34681,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.2134466826687229E-2</v>
+        <v>1.2138860833202425E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35222,14 +35193,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35296,19 +35267,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="241">
+      <c r="C7" s="242">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="242"/>
-      <c r="F7" s="241">
+      <c r="D7" s="243"/>
+      <c r="F7" s="242">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="242"/>
+      <c r="G7" s="243"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35335,19 +35306,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="241">
+      <c r="C9" s="242">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="F9" s="241">
+      <c r="D9" s="243"/>
+      <c r="F9" s="242">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="242"/>
+      <c r="G9" s="243"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35374,19 +35345,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="241">
+      <c r="C11" s="242">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="F11" s="241">
+      <c r="D11" s="243"/>
+      <c r="F11" s="242">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="242"/>
+      <c r="G11" s="243"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35413,19 +35384,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="241">
+      <c r="C13" s="242">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="F13" s="241">
+      <c r="D13" s="243"/>
+      <c r="F13" s="242">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="242"/>
+      <c r="G13" s="243"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35452,19 +35423,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="241">
+      <c r="C15" s="242">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="242"/>
-      <c r="F15" s="241">
+      <c r="D15" s="243"/>
+      <c r="F15" s="242">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="242"/>
+      <c r="G15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35491,19 +35462,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="241">
+      <c r="C17" s="242">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="F17" s="241">
+      <c r="D17" s="243"/>
+      <c r="F17" s="242">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="242"/>
+      <c r="G17" s="243"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35530,22 +35501,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="241">
+      <c r="C19" s="242">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="242"/>
-      <c r="F19" s="241">
+      <c r="D19" s="243"/>
+      <c r="F19" s="242">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="242"/>
+      <c r="G19" s="243"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35572,22 +35543,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="241">
+      <c r="C21" s="242">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="F21" s="241">
+      <c r="D21" s="243"/>
+      <c r="F21" s="242">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="242"/>
+      <c r="G21" s="243"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35635,22 +35606,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="241">
+      <c r="C25" s="242">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="F25" s="241">
+      <c r="D25" s="243"/>
+      <c r="F25" s="242">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="242"/>
+      <c r="G25" s="243"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -35677,22 +35648,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="241">
+      <c r="C27" s="242">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="F27" s="241">
+      <c r="D27" s="243"/>
+      <c r="F27" s="242">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="242"/>
+      <c r="G27" s="243"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35719,22 +35690,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="241">
+      <c r="C29" s="242">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="242"/>
-      <c r="F29" s="241">
+      <c r="D29" s="243"/>
+      <c r="F29" s="242">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="242"/>
+      <c r="G29" s="243"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35761,43 +35732,25 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="241">
+      <c r="C31" s="242">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="F31" s="241">
+      <c r="D31" s="243"/>
+      <c r="F31" s="242">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="242"/>
+      <c r="G31" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35806,6 +35759,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1367C4-747C-F24F-B18F-CA37D53AF702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13E8DA7-5403-4047-B6A4-884769E863BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="415">
   <si>
     <t>Ticker</t>
   </si>
@@ -1382,6 +1382,21 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales price</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
   </si>
 </sst>
 </file>
@@ -2302,6 +2317,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2326,19 +2350,10 @@
     <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12697,11 +12712,11 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>164.27</v>
-    <v>2.2193999999999998</v>
+    <v>2.2191000000000001</v>
     <v>0.49</v>
     <v>2.1819999999999999E-3</v>
-    <v>-6.1499999999999999E-2</v>
-    <v>-2.7320000000000003E-4</v>
+    <v>-7.0000000000000007E-2</v>
+    <v>-3.1099999999999997E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12712,21 +12727,21 @@
     <v>226.94</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.840027488281</v>
+    <v>46290.999978205466</v>
     <v>0</v>
     <v>223.13290000000001</v>
     <v>5424187000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>225.01</v>
-    <v>28.4513</v>
+    <v>225.13</v>
+    <v>28.389299999999999</v>
     <v>224.58</v>
     <v>225.07</v>
-    <v>225.0085</v>
+    <v>225</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>87178721</v>
+    <v>89947712</v>
     <v>126361390</v>
     <v>1998</v>
   </rv>
@@ -12749,19 +12764,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>3</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12983,9 +12998,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13556,18 +13571,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="236" t="s">
+      <c r="B2" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="237"/>
-      <c r="E2" s="236" t="s">
+      <c r="C2" s="240"/>
+      <c r="E2" s="239" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="237"/>
-      <c r="H2" s="236" t="s">
+      <c r="F2" s="240"/>
+      <c r="H2" s="239" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="237"/>
+      <c r="I2" s="240"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -13638,7 +13653,7 @@
       </c>
       <c r="I5" s="208">
         <f>'AVG target price'!C7</f>
-        <v>310.77023855090073</v>
+        <v>372.92428626108091</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13647,7 +13662,7 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>225.0085</v>
+        <v>225</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
@@ -13681,12 +13696,12 @@
         <v>18.12463186827695</v>
       </c>
       <c r="H7" s="181" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="209">
-        <f>'AVG target price'!C9</f>
-        <v>353.03418118595664</v>
+        <f>'AVG target price'!C10</f>
+        <v>375.83292964279934</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13695,7 +13710,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-6.1499999999999999E-2</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
@@ -13705,12 +13720,12 @@
         <v>2.1992928139837151E-2</v>
       </c>
       <c r="H8" s="181" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="210">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>0.56855281106303213</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>0.66984906759141316</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13735,7 +13750,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.7320000000000003E-4</v>
+        <v>-3.1099999999999997E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
@@ -13790,7 +13805,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2193999999999998</v>
+        <v>2.2191000000000001</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13835,10 +13850,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="238" t="s">
+      <c r="B17" s="241" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="238"/>
+      <c r="C17" s="241"/>
       <c r="E17" s="181" t="s">
         <v>288</v>
       </c>
@@ -13911,14 +13926,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="238" t="s">
+      <c r="B25" s="241" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="E25" s="236" t="s">
+      <c r="C25" s="241"/>
+      <c r="E25" s="239" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="237"/>
+      <c r="F25" s="240"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -13932,7 +13947,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13947,7 +13962,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14187,8 +14202,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="235"/>
@@ -14221,32 +14236,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="245" t="s">
+      <c r="S4" s="247" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
+      <c r="AA4" s="248"/>
+      <c r="AB4" s="248"/>
+      <c r="AC4" s="248"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14831,33 +14846,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="244" t="s">
+      <c r="C12" s="236" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="244"/>
-      <c r="G12" s="244"/>
-      <c r="H12" s="244"/>
-      <c r="I12" s="244"/>
-      <c r="J12" s="244"/>
-      <c r="K12" s="244"/>
-      <c r="L12" s="244"/>
+      <c r="D12" s="236"/>
+      <c r="E12" s="236"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="245" t="s">
+      <c r="S12" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="246"/>
-      <c r="U12" s="246"/>
-      <c r="V12" s="246"/>
-      <c r="W12" s="246"/>
-      <c r="X12" s="246"/>
-      <c r="Y12" s="246"/>
-      <c r="Z12" s="246"/>
-      <c r="AA12" s="246"/>
-      <c r="AB12" s="246"/>
-      <c r="AC12" s="246"/>
+      <c r="T12" s="248"/>
+      <c r="U12" s="248"/>
+      <c r="V12" s="248"/>
+      <c r="W12" s="248"/>
+      <c r="X12" s="248"/>
+      <c r="Y12" s="248"/>
+      <c r="Z12" s="248"/>
+      <c r="AA12" s="248"/>
+      <c r="AB12" s="248"/>
+      <c r="AC12" s="248"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -15412,8 +15427,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="235"/>
@@ -15443,31 +15458,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="P4" s="246" t="s">
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
+      <c r="P4" s="248" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
+      <c r="Q4" s="248"/>
+      <c r="R4" s="248"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15662,32 +15677,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="236" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="236"/>
+      <c r="E9" s="236"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="246" t="s">
+      <c r="P9" s="248" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="246"/>
-      <c r="S9" s="246"/>
-      <c r="T9" s="246"/>
-      <c r="U9" s="246"/>
-      <c r="V9" s="246"/>
-      <c r="W9" s="246"/>
-      <c r="X9" s="246"/>
-      <c r="Y9" s="246"/>
-      <c r="Z9" s="246"/>
+      <c r="Q9" s="248"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16163,31 +16178,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="236" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="244"/>
-      <c r="L17" s="244"/>
-      <c r="P17" s="246" t="s">
+      <c r="D17" s="236"/>
+      <c r="E17" s="236"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="236"/>
+      <c r="H17" s="236"/>
+      <c r="I17" s="236"/>
+      <c r="J17" s="236"/>
+      <c r="K17" s="236"/>
+      <c r="L17" s="236"/>
+      <c r="P17" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="246"/>
-      <c r="R17" s="246"/>
-      <c r="S17" s="246"/>
-      <c r="T17" s="246"/>
-      <c r="U17" s="246"/>
-      <c r="V17" s="246"/>
-      <c r="W17" s="246"/>
-      <c r="X17" s="246"/>
-      <c r="Y17" s="246"/>
-      <c r="Z17" s="246"/>
+      <c r="Q17" s="248"/>
+      <c r="R17" s="248"/>
+      <c r="S17" s="248"/>
+      <c r="T17" s="248"/>
+      <c r="U17" s="248"/>
+      <c r="V17" s="248"/>
+      <c r="W17" s="248"/>
+      <c r="X17" s="248"/>
+      <c r="Y17" s="248"/>
+      <c r="Z17" s="248"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16671,8 +16686,8 @@
       <c r="D3" s="235"/>
       <c r="E3" s="235"/>
       <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="G3" s="237"/>
+      <c r="H3" s="238" t="s">
         <v>106</v>
       </c>
       <c r="I3" s="235"/>
@@ -16696,18 +16711,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="236"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -16904,18 +16919,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="236" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="236"/>
+      <c r="E11" s="236"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
       <c r="N11" s="91"/>
       <c r="P11" s="249"/>
       <c r="Q11" s="249"/>
@@ -17169,18 +17184,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="236" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="236"/>
+      <c r="E18" s="236"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="236"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17398,18 +17413,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="244" t="s">
+      <c r="C26" s="236" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="D26" s="236"/>
+      <c r="E26" s="236"/>
+      <c r="F26" s="236"/>
+      <c r="G26" s="236"/>
+      <c r="H26" s="236"/>
+      <c r="I26" s="236"/>
+      <c r="J26" s="236"/>
+      <c r="K26" s="236"/>
+      <c r="L26" s="236"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17601,18 +17616,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="244" t="s">
+      <c r="C33" s="236" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="244"/>
-      <c r="I33" s="244"/>
-      <c r="J33" s="244"/>
-      <c r="K33" s="244"/>
-      <c r="L33" s="244"/>
+      <c r="D33" s="236"/>
+      <c r="E33" s="236"/>
+      <c r="F33" s="236"/>
+      <c r="G33" s="236"/>
+      <c r="H33" s="236"/>
+      <c r="I33" s="236"/>
+      <c r="J33" s="236"/>
+      <c r="K33" s="236"/>
+      <c r="L33" s="236"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17796,18 +17811,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="244" t="s">
+      <c r="C40" s="236" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
+      <c r="D40" s="236"/>
+      <c r="E40" s="236"/>
+      <c r="F40" s="236"/>
+      <c r="G40" s="236"/>
+      <c r="H40" s="236"/>
+      <c r="I40" s="236"/>
+      <c r="J40" s="236"/>
+      <c r="K40" s="236"/>
+      <c r="L40" s="236"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18127,8 +18142,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="235"/>
@@ -18152,18 +18167,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="236" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
       <c r="S4" s="249"/>
       <c r="T4" s="249"/>
       <c r="U4" s="249"/>
@@ -18537,18 +18552,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="236" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
-      <c r="L13" s="244"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="236"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="236"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18641,18 +18656,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="236" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="236"/>
+      <c r="E18" s="236"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="236"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18844,18 +18859,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="244" t="s">
+      <c r="C25" s="236" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
-      <c r="K25" s="244"/>
-      <c r="L25" s="244"/>
+      <c r="D25" s="236"/>
+      <c r="E25" s="236"/>
+      <c r="F25" s="236"/>
+      <c r="G25" s="236"/>
+      <c r="H25" s="236"/>
+      <c r="I25" s="236"/>
+      <c r="J25" s="236"/>
+      <c r="K25" s="236"/>
+      <c r="L25" s="236"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -18993,18 +19008,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="244" t="s">
+      <c r="C31" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
+      <c r="D31" s="236"/>
+      <c r="E31" s="236"/>
+      <c r="F31" s="236"/>
+      <c r="G31" s="236"/>
+      <c r="H31" s="236"/>
+      <c r="I31" s="236"/>
+      <c r="J31" s="236"/>
+      <c r="K31" s="236"/>
+      <c r="L31" s="236"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19262,7 +19277,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19271,7 +19286,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2193999999999998</v>
+        <v>2.2191000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19341,7 +19356,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15149299999999999</v>
+        <v>0.15169950000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19350,7 +19365,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15081300883837587</v>
+        <v>0.15101825502630839</v>
       </c>
     </row>
   </sheetData>
@@ -19401,8 +19416,8 @@
       <c r="D3" s="235"/>
       <c r="E3" s="235"/>
       <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="G3" s="237"/>
+      <c r="H3" s="238" t="s">
         <v>106</v>
       </c>
       <c r="I3" s="235"/>
@@ -19426,18 +19441,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="236" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="236"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -19812,7 +19827,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -19840,8 +19855,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="235"/>
@@ -19853,18 +19868,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="236" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20084,18 +20099,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="236" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="236"/>
+      <c r="E11" s="236"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20289,18 +20304,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="236" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="244"/>
-      <c r="L17" s="244"/>
+      <c r="D17" s="236"/>
+      <c r="E17" s="236"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="236"/>
+      <c r="H17" s="236"/>
+      <c r="I17" s="236"/>
+      <c r="J17" s="236"/>
+      <c r="K17" s="236"/>
+      <c r="L17" s="236"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20434,18 +20449,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="236" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
-      <c r="F22" s="244"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="244"/>
-      <c r="I22" s="244"/>
-      <c r="J22" s="244"/>
-      <c r="K22" s="244"/>
-      <c r="L22" s="244"/>
+      <c r="D22" s="236"/>
+      <c r="E22" s="236"/>
+      <c r="F22" s="236"/>
+      <c r="G22" s="236"/>
+      <c r="H22" s="236"/>
+      <c r="I22" s="236"/>
+      <c r="J22" s="236"/>
+      <c r="K22" s="236"/>
+      <c r="L22" s="236"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20529,18 +20544,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="244" t="s">
+      <c r="C27" s="236" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="E27" s="244"/>
-      <c r="F27" s="244"/>
-      <c r="G27" s="244"/>
-      <c r="H27" s="244"/>
-      <c r="I27" s="244"/>
-      <c r="J27" s="244"/>
-      <c r="K27" s="244"/>
-      <c r="L27" s="244"/>
+      <c r="D27" s="236"/>
+      <c r="E27" s="236"/>
+      <c r="F27" s="236"/>
+      <c r="G27" s="236"/>
+      <c r="H27" s="236"/>
+      <c r="I27" s="236"/>
+      <c r="J27" s="236"/>
+      <c r="K27" s="236"/>
+      <c r="L27" s="236"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -20804,291 +20819,427 @@
       <c r="N35" s="91"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="C36" s="148">
+        <f>C33/C6</f>
+        <v>214.74615441777513</v>
+      </c>
+      <c r="D36" s="148">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>189.14172907244011</v>
+      </c>
+      <c r="E36" s="148">
+        <f t="shared" si="14"/>
+        <v>249.57498112340366</v>
+      </c>
+      <c r="F36" s="148">
+        <f t="shared" si="14"/>
+        <v>26.841992382966659</v>
+      </c>
+      <c r="G36" s="149">
+        <f t="shared" si="14"/>
+        <v>21.054443312432273</v>
+      </c>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="138"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="138"/>
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="235" t="s">
+      <c r="N38" s="91"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="235" t="s">
         <v>197</v>
       </c>
-      <c r="C38" s="235"/>
-      <c r="N38" s="91"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="235"/>
+      <c r="N39" s="91"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>843066.5668746751</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C40" s="136">
+      <c r="C41" s="136">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="C41" s="105">
+      <c r="C42" s="105">
         <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>16861331.337493502</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>16861331.337493502</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C43" s="24">
-        <f>C42/(1+C40)^5</f>
+      <c r="C44" s="24">
+        <f>C43/(1+C41)^5</f>
         <v>9567572.2240634207</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="C44" s="109">
-        <f>SUM(H9:K9)+C43</f>
+      <c r="C45" s="109">
+        <f>SUM(H9:K9)+C44</f>
         <v>10559883.767653175</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C45" s="137">
+      <c r="C46" s="137">
         <f>Statement!AC105</f>
         <v>99369</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C46" s="137">
+      <c r="C47" s="137">
         <f>Statement!AC106</f>
         <v>33266</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C47" s="109">
-        <f>C44+C45-C46</f>
+      <c r="C48" s="109">
+        <f>C45+C46-C47</f>
         <v>10625986.767653175</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C49" s="88">
         <f>Statement!AC77</f>
         <v>24195</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="233" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="233" t="s">
         <v>201</v>
       </c>
-      <c r="C49" s="234">
-        <f>C47/C48</f>
+      <c r="C50" s="234">
+        <f>C48/C49</f>
         <v>439.18110219686605</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C51" s="235"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="235"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>1283206.3422750002</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C53" s="136">
+      <c r="C54" s="136">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="105">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="105">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>23429.712685180726</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
-        <v>547.68334529626009</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="233" t="s">
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
+        <v>657.22001435551215</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="233" t="s">
         <v>201</v>
       </c>
-      <c r="C57" s="234">
-        <f>C56/(1+C53)^5</f>
-        <v>310.77023855090073</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="235" t="s">
+      <c r="C58" s="234">
+        <f>C57/(1+C54)^5</f>
+        <v>372.92428626108091</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="235" t="s">
         <v>314</v>
       </c>
-      <c r="C59" s="235"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="235"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>586389.6287922078</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C61" s="136">
+      <c r="C62" s="136">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>375</v>
       </c>
-      <c r="C62" s="105">
+      <c r="C63" s="105">
         <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>17591688.863766234</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>17591688.863766234</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C64" s="24">
-        <f>C63/(1+C61)^5</f>
+      <c r="C65" s="24">
+        <f>C64/(1+C62)^5</f>
         <v>9981996.6987467725</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="C65" s="109">
-        <f>SUM(H9:K9)+C64</f>
+      <c r="C66" s="109">
+        <f>SUM(H9:K9)+C65</f>
         <v>10974308.242336527</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C66" s="137">
+      <c r="C67" s="137">
         <f>Statement!AC105</f>
         <v>99369</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C67" s="137">
+      <c r="C68" s="137">
         <f>Statement!AC106</f>
         <v>33266</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C68" s="109">
-        <f>C65+C66-C67</f>
+      <c r="C69" s="109">
+        <f>C66+C67-C68</f>
         <v>11040411.242336527</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C69" s="88">
+      <c r="C70" s="88">
         <f>Statement!AC77</f>
         <v>24195</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="233" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="233" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="234">
-        <f>C68/C69</f>
+      <c r="C71" s="234">
+        <f>C69/C70</f>
         <v>456.30961943941008</v>
       </c>
     </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="235" t="s">
+        <v>411</v>
+      </c>
+      <c r="C73" s="235"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>1283206.3422750002</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C75" s="136">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="C76" s="105">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>15398476.107300002</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C78" s="24">
+        <f>C77/(1+C75)^5</f>
+        <v>8737508.8804232161</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C79" s="109">
+        <f>SUM(H9:K9)+C78</f>
+        <v>9729820.4240129702</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C80" s="137">
+        <f>Statement!AC105</f>
+        <v>99369</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" s="137">
+        <f>Statement!AC106</f>
+        <v>33266</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="109">
+        <f>C79+C80-C81</f>
+        <v>9795923.4240129702</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" s="88">
+        <f>Statement!AC77</f>
+        <v>24195</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="233" t="s">
+        <v>201</v>
+      </c>
+      <c r="C84" s="234">
+        <f>C82/C83</f>
+        <v>404.87387575999048</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+  <mergeCells count="11">
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21099,7 +21250,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -21146,7 +21297,7 @@
         <v>208</v>
       </c>
       <c r="C6" s="134">
-        <f>Multiples!C49</f>
+        <f>Multiples!C50</f>
         <v>439.18110219686605</v>
       </c>
     </row>
@@ -21155,8 +21306,8 @@
         <v>209</v>
       </c>
       <c r="C7" s="134">
-        <f>Multiples!C57</f>
-        <v>310.77023855090073</v>
+        <f>Multiples!C58</f>
+        <v>372.92428626108091</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21164,35 +21315,44 @@
         <v>315</v>
       </c>
       <c r="C8" s="134">
-        <f>Multiples!C70</f>
+        <f>Multiples!C71</f>
         <v>456.30961943941008</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="233" t="s">
+      <c r="B9" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C9" s="134">
+        <f>Multiples!C84</f>
+        <v>404.87387575999048</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C9" s="234">
-        <f>AVERAGE(C5:C8)</f>
-        <v>353.03418118595664</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="234">
+        <f>AVERAGE(C5:C9)</f>
+        <v>375.83292964279934</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="134">
+      <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
         <v>225.07</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C11" s="153">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>0.56855281106303213</v>
+      <c r="C12" s="153">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>0.66984906759141316</v>
       </c>
     </row>
   </sheetData>
@@ -21254,8 +21414,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="235"/>
@@ -21267,18 +21427,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="236" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21391,18 +21551,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="236" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="236"/>
+      <c r="E9" s="236"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21523,18 +21683,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="236" t="s">
         <v>390</v>
       </c>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="244"/>
-      <c r="K14" s="244"/>
-      <c r="L14" s="244"/>
+      <c r="D14" s="236"/>
+      <c r="E14" s="236"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="236"/>
+      <c r="H14" s="236"/>
+      <c r="I14" s="236"/>
+      <c r="J14" s="236"/>
+      <c r="K14" s="236"/>
+      <c r="L14" s="236"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21734,8 +21894,8 @@
       <c r="D3" s="235"/>
       <c r="E3" s="235"/>
       <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="G3" s="237"/>
+      <c r="H3" s="238" t="s">
         <v>106</v>
       </c>
       <c r="I3" s="235"/>
@@ -21759,18 +21919,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="236" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="236"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -22198,7 +22358,6 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
@@ -22208,6 +22367,7 @@
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -35193,14 +35353,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="242" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="243"/>
+      <c r="F3" s="244" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="243"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35267,19 +35427,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="242">
+      <c r="C7" s="245">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="F7" s="242">
+      <c r="D7" s="246"/>
+      <c r="F7" s="245">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="243"/>
+      <c r="G7" s="246"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35306,19 +35466,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="242">
+      <c r="C9" s="245">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="F9" s="242">
+      <c r="D9" s="246"/>
+      <c r="F9" s="245">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="246"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35345,19 +35505,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="242">
+      <c r="C11" s="245">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="F11" s="242">
+      <c r="D11" s="246"/>
+      <c r="F11" s="245">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="243"/>
+      <c r="G11" s="246"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35384,19 +35544,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="245">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="243"/>
-      <c r="F13" s="242">
+      <c r="D13" s="246"/>
+      <c r="F13" s="245">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="243"/>
+      <c r="G13" s="246"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35423,19 +35583,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="242">
+      <c r="C15" s="245">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="F15" s="242">
+      <c r="D15" s="246"/>
+      <c r="F15" s="245">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="243"/>
+      <c r="G15" s="246"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35462,19 +35622,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="242">
+      <c r="C17" s="245">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="F17" s="242">
+      <c r="D17" s="246"/>
+      <c r="F17" s="245">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="243"/>
+      <c r="G17" s="246"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35501,22 +35661,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="242">
+      <c r="C19" s="245">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="F19" s="242">
+      <c r="D19" s="246"/>
+      <c r="F19" s="245">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="243"/>
+      <c r="G19" s="246"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35543,22 +35703,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="242">
+      <c r="C21" s="245">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="F21" s="242">
+      <c r="D21" s="246"/>
+      <c r="F21" s="245">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="243"/>
+      <c r="G21" s="246"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35606,22 +35766,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="242">
+      <c r="C25" s="245">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="243"/>
-      <c r="F25" s="242">
+      <c r="D25" s="246"/>
+      <c r="F25" s="245">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="243"/>
+      <c r="G25" s="246"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -35648,22 +35808,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="242">
+      <c r="C27" s="245">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="243"/>
-      <c r="F27" s="242">
+      <c r="D27" s="246"/>
+      <c r="F27" s="245">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="243"/>
+      <c r="G27" s="246"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35690,22 +35850,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="242">
+      <c r="C29" s="245">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="F29" s="242">
+      <c r="D29" s="246"/>
+      <c r="F29" s="245">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="243"/>
+      <c r="G29" s="246"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35732,22 +35892,22 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="242">
+      <c r="C31" s="245">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="243"/>
-      <c r="F31" s="242">
+      <c r="D31" s="246"/>
+      <c r="F31" s="245">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="243"/>
+      <c r="G31" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="26">

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13E8DA7-5403-4047-B6A4-884769E863BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4E9644-0618-0B44-AF9F-9CE1E1E2B132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="416">
   <si>
     <t>Ticker</t>
   </si>
@@ -1397,6 +1397,9 @@
   </si>
   <si>
     <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2314,18 +2317,6 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2333,6 +2324,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2350,10 +2344,19 @@
     <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12712,11 +12715,11 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>164.27</v>
-    <v>2.2191000000000001</v>
-    <v>0.49</v>
-    <v>2.1819999999999999E-3</v>
-    <v>-7.0000000000000007E-2</v>
-    <v>-3.1099999999999997E-4</v>
+    <v>2.2174</v>
+    <v>-1.65</v>
+    <v>-7.2099999999999994E-3</v>
+    <v>0.83819999999999995</v>
+    <v>3.689E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12724,25 +12727,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>226.94</v>
+    <v>232.82</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.999978205466</v>
+    <v>46294.960115948437</v>
     <v>0</v>
-    <v>223.13290000000001</v>
-    <v>5424187000000</v>
+    <v>227.02500000000001</v>
+    <v>5475761000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>225.13</v>
-    <v>28.389299999999999</v>
-    <v>224.58</v>
-    <v>225.07</v>
-    <v>225</v>
+    <v>230.97</v>
+    <v>28.930299999999999</v>
+    <v>228.86</v>
+    <v>227.21</v>
+    <v>228.04820000000001</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>89947712</v>
-    <v>126361390</v>
+    <v>101304989</v>
+    <v>128000018</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12764,19 +12767,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.15</v>
+    <v>2.8630000000000001E-3</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.62</v>
+    <v>52.13</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
-    <v>51.84</v>
+    <v>52.13</v>
+    <v>52.4</v>
+    <v>52.55</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12998,9 +13001,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13571,18 +13574,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="239" t="s">
+      <c r="B2" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="240"/>
-      <c r="E2" s="239" t="s">
+      <c r="C2" s="236"/>
+      <c r="E2" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="240"/>
-      <c r="H2" s="239" t="s">
+      <c r="F2" s="236"/>
+      <c r="H2" s="235" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="240"/>
+      <c r="I2" s="236"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -13597,7 +13600,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5445568.6499999994</v>
+        <v>5497345.9500000002</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13621,7 +13624,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5379465.6499999994</v>
+        <v>5431242.9500000002</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13638,7 +13641,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>225.07</v>
+        <v>227.21</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13662,14 +13665,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>225</v>
+        <v>228.04820000000001</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>28.453855878634638</v>
+        <v>28.724399494310997</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13686,22 +13689,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.49</v>
+        <v>-1.65</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>18.12463186827695</v>
-      </c>
-      <c r="H7" s="181" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="209">
-        <f>'AVG target price'!C10</f>
-        <v>375.83292964279934</v>
+        <v>18.296963641494674</v>
+      </c>
+      <c r="H7" s="182" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales price</v>
+      </c>
+      <c r="I7" s="208">
+        <f>'AVG target price'!C9</f>
+        <v>404.87387575999048</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13710,22 +13713,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-7.0000000000000007E-2</v>
+        <v>0.83819999999999995</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.1992928139837151E-2</v>
+        <v>2.1785785557119613E-2</v>
       </c>
       <c r="H8" s="181" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="210">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>0.66984906759141316</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="209">
+        <f>'AVG target price'!C10</f>
+        <v>375.83292964279934</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13734,14 +13737,22 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.1819999999999999E-3</v>
+        <v>-7.2099999999999994E-3</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.5144621673257208E-2</v>
+        <v>3.4813608555961446E-2</v>
+      </c>
+      <c r="H9" s="181" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="210">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>0.65412142794242911</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13750,21 +13761,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.1099999999999997E-4</v>
+        <v>3.689E-3</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.015780050812508E-2</v>
-      </c>
-      <c r="H10" s="181" t="s">
-        <v>397</v>
-      </c>
-      <c r="I10" s="209">
-        <f>DDM!C26</f>
-        <v>1.6842105263157894</v>
+        <v>1.0062128252998157E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13780,7 +13784,14 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.2440574043630873E-3</v>
+        <v>1.2323401258747416E-3</v>
+      </c>
+      <c r="H11" s="181" t="s">
+        <v>397</v>
+      </c>
+      <c r="I11" s="209">
+        <f>DDM!C26</f>
+        <v>1.6842105263157894</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13805,7 +13816,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2191000000000001</v>
+        <v>2.2174</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13814,6 +13825,13 @@
         <f>Statement!AC123</f>
         <v>0.84232522796352571</v>
       </c>
+      <c r="H13" s="181" t="s">
+        <v>415</v>
+      </c>
+      <c r="I13" s="210">
+        <f>'Reverse DCF'!C17</f>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="183" t="s">
@@ -13821,7 +13839,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>126361390</v>
+        <v>128000018</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13837,7 +13855,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.2138860833202425E-2</v>
+        <v>1.202452976422195E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13850,10 +13868,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="241" t="s">
+      <c r="B17" s="237" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="241"/>
+      <c r="C17" s="237"/>
       <c r="E17" s="181" t="s">
         <v>288</v>
       </c>
@@ -13926,14 +13944,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="241" t="s">
+      <c r="B25" s="237" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="241"/>
-      <c r="E25" s="239" t="s">
+      <c r="C25" s="237"/>
+      <c r="E25" s="235" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="240"/>
+      <c r="F25" s="236"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -13947,7 +13965,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13962,7 +13980,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13982,15 +14000,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="133" t="s">
         <v>326</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="133"/>
+      <c r="D33" s="133"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="133"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="133"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14009,24 +14027,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="133"/>
+      <c r="C39" s="133"/>
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="133" t="s">
         <v>329</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="133"/>
+      <c r="D42" s="133"/>
+      <c r="E42" s="133"/>
+      <c r="F42" s="133"/>
+      <c r="G42" s="133"/>
+      <c r="H42" s="133"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14073,24 +14091,24 @@
       </c>
     </row>
     <row r="51" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="235"/>
-      <c r="C51" s="235"/>
-      <c r="D51" s="235"/>
-      <c r="E51" s="235"/>
-      <c r="F51" s="235"/>
-      <c r="G51" s="235"/>
-      <c r="H51" s="235"/>
+      <c r="B51" s="133"/>
+      <c r="C51" s="133"/>
+      <c r="D51" s="133"/>
+      <c r="E51" s="133"/>
+      <c r="F51" s="133"/>
+      <c r="G51" s="133"/>
+      <c r="H51" s="133"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="235" t="s">
+      <c r="B54" s="133" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="235"/>
-      <c r="D54" s="235"/>
-      <c r="E54" s="235"/>
-      <c r="F54" s="235"/>
-      <c r="G54" s="235"/>
-      <c r="H54" s="235"/>
+      <c r="C54" s="133"/>
+      <c r="D54" s="133"/>
+      <c r="E54" s="133"/>
+      <c r="F54" s="133"/>
+      <c r="G54" s="133"/>
+      <c r="H54" s="133"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="41" t="s">
@@ -14105,28 +14123,22 @@
       </c>
     </row>
     <row r="61" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="235"/>
-      <c r="C61" s="235"/>
-      <c r="D61" s="235"/>
-      <c r="E61" s="235"/>
-      <c r="F61" s="235"/>
-      <c r="G61" s="235"/>
-      <c r="H61" s="235"/>
+      <c r="B61" s="133"/>
+      <c r="C61" s="133"/>
+      <c r="D61" s="133"/>
+      <c r="E61" s="133"/>
+      <c r="F61" s="133"/>
+      <c r="G61" s="133"/>
+      <c r="H61" s="133"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B51:H51"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14196,36 +14208,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14236,32 +14248,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="247" t="s">
+      <c r="S4" s="245" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="W4" s="248"/>
-      <c r="X4" s="248"/>
-      <c r="Y4" s="248"/>
-      <c r="Z4" s="248"/>
-      <c r="AA4" s="248"/>
-      <c r="AB4" s="248"/>
-      <c r="AC4" s="248"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14846,33 +14858,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="236" t="s">
+      <c r="C12" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="236"/>
-      <c r="E12" s="236"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
+      <c r="D12" s="244"/>
+      <c r="E12" s="244"/>
+      <c r="F12" s="244"/>
+      <c r="G12" s="244"/>
+      <c r="H12" s="244"/>
+      <c r="I12" s="244"/>
+      <c r="J12" s="244"/>
+      <c r="K12" s="244"/>
+      <c r="L12" s="244"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="247" t="s">
+      <c r="S12" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="248"/>
-      <c r="U12" s="248"/>
-      <c r="V12" s="248"/>
-      <c r="W12" s="248"/>
-      <c r="X12" s="248"/>
-      <c r="Y12" s="248"/>
-      <c r="Z12" s="248"/>
-      <c r="AA12" s="248"/>
-      <c r="AB12" s="248"/>
-      <c r="AC12" s="248"/>
+      <c r="T12" s="246"/>
+      <c r="U12" s="246"/>
+      <c r="V12" s="246"/>
+      <c r="W12" s="246"/>
+      <c r="X12" s="246"/>
+      <c r="Y12" s="246"/>
+      <c r="Z12" s="246"/>
+      <c r="AA12" s="246"/>
+      <c r="AB12" s="246"/>
+      <c r="AC12" s="246"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -15421,35 +15433,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="P2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15458,31 +15470,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
-      <c r="P4" s="248" t="s">
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="P4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="248"/>
-      <c r="R4" s="248"/>
-      <c r="S4" s="248"/>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="W4" s="248"/>
-      <c r="X4" s="248"/>
-      <c r="Y4" s="248"/>
-      <c r="Z4" s="248"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15677,32 +15689,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="236" t="s">
+      <c r="C9" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="248" t="s">
+      <c r="P9" s="246" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="248"/>
-      <c r="R9" s="248"/>
-      <c r="S9" s="248"/>
-      <c r="T9" s="248"/>
-      <c r="U9" s="248"/>
-      <c r="V9" s="248"/>
-      <c r="W9" s="248"/>
-      <c r="X9" s="248"/>
-      <c r="Y9" s="248"/>
-      <c r="Z9" s="248"/>
+      <c r="Q9" s="246"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
+      <c r="W9" s="246"/>
+      <c r="X9" s="246"/>
+      <c r="Y9" s="246"/>
+      <c r="Z9" s="246"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16178,31 +16190,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="236" t="s">
+      <c r="C17" s="244" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="236"/>
-      <c r="E17" s="236"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="236"/>
-      <c r="J17" s="236"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="236"/>
-      <c r="P17" s="248" t="s">
+      <c r="D17" s="244"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="244"/>
+      <c r="K17" s="244"/>
+      <c r="L17" s="244"/>
+      <c r="P17" s="246" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="248"/>
-      <c r="R17" s="248"/>
-      <c r="S17" s="248"/>
-      <c r="T17" s="248"/>
-      <c r="U17" s="248"/>
-      <c r="V17" s="248"/>
-      <c r="W17" s="248"/>
-      <c r="X17" s="248"/>
-      <c r="Y17" s="248"/>
-      <c r="Z17" s="248"/>
+      <c r="Q17" s="246"/>
+      <c r="R17" s="246"/>
+      <c r="S17" s="246"/>
+      <c r="T17" s="246"/>
+      <c r="U17" s="246"/>
+      <c r="V17" s="246"/>
+      <c r="W17" s="246"/>
+      <c r="X17" s="246"/>
+      <c r="Y17" s="246"/>
+      <c r="Z17" s="246"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16680,20 +16692,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="238" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -16711,18 +16723,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -16919,18 +16931,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="236" t="s">
+      <c r="C11" s="244" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="236"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="N11" s="91"/>
       <c r="P11" s="249"/>
       <c r="Q11" s="249"/>
@@ -17184,18 +17196,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="236" t="s">
+      <c r="C18" s="244" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="236"/>
-      <c r="E18" s="236"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="236"/>
-      <c r="J18" s="236"/>
-      <c r="K18" s="236"/>
-      <c r="L18" s="236"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17413,18 +17425,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="236" t="s">
+      <c r="C26" s="244" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="236"/>
-      <c r="E26" s="236"/>
-      <c r="F26" s="236"/>
-      <c r="G26" s="236"/>
-      <c r="H26" s="236"/>
-      <c r="I26" s="236"/>
-      <c r="J26" s="236"/>
-      <c r="K26" s="236"/>
-      <c r="L26" s="236"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="244"/>
+      <c r="H26" s="244"/>
+      <c r="I26" s="244"/>
+      <c r="J26" s="244"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="244"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17616,18 +17628,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="236" t="s">
+      <c r="C33" s="244" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="236"/>
-      <c r="E33" s="236"/>
-      <c r="F33" s="236"/>
-      <c r="G33" s="236"/>
-      <c r="H33" s="236"/>
-      <c r="I33" s="236"/>
-      <c r="J33" s="236"/>
-      <c r="K33" s="236"/>
-      <c r="L33" s="236"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="244"/>
+      <c r="J33" s="244"/>
+      <c r="K33" s="244"/>
+      <c r="L33" s="244"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17811,18 +17823,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="236" t="s">
+      <c r="C40" s="244" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="236"/>
-      <c r="E40" s="236"/>
-      <c r="F40" s="236"/>
-      <c r="G40" s="236"/>
-      <c r="H40" s="236"/>
-      <c r="I40" s="236"/>
-      <c r="J40" s="236"/>
-      <c r="K40" s="236"/>
-      <c r="L40" s="236"/>
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18136,20 +18148,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="S2" s="249"/>
       <c r="T2" s="249"/>
       <c r="U2" s="249"/>
@@ -18167,18 +18179,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="244" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
       <c r="S4" s="249"/>
       <c r="T4" s="249"/>
       <c r="U4" s="249"/>
@@ -18552,18 +18564,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="236" t="s">
+      <c r="C13" s="244" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="236"/>
-      <c r="E13" s="236"/>
-      <c r="F13" s="236"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="236"/>
-      <c r="I13" s="236"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="236"/>
-      <c r="L13" s="236"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="244"/>
+      <c r="H13" s="244"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="244"/>
+      <c r="L13" s="244"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18656,18 +18668,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="236" t="s">
+      <c r="C18" s="244" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="236"/>
-      <c r="E18" s="236"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="236"/>
-      <c r="J18" s="236"/>
-      <c r="K18" s="236"/>
-      <c r="L18" s="236"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18859,18 +18871,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="236" t="s">
+      <c r="C25" s="244" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="236"/>
-      <c r="E25" s="236"/>
-      <c r="F25" s="236"/>
-      <c r="G25" s="236"/>
-      <c r="H25" s="236"/>
-      <c r="I25" s="236"/>
-      <c r="J25" s="236"/>
-      <c r="K25" s="236"/>
-      <c r="L25" s="236"/>
+      <c r="D25" s="244"/>
+      <c r="E25" s="244"/>
+      <c r="F25" s="244"/>
+      <c r="G25" s="244"/>
+      <c r="H25" s="244"/>
+      <c r="I25" s="244"/>
+      <c r="J25" s="244"/>
+      <c r="K25" s="244"/>
+      <c r="L25" s="244"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19008,18 +19020,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="236" t="s">
+      <c r="C31" s="244" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="236"/>
-      <c r="E31" s="236"/>
-      <c r="F31" s="236"/>
-      <c r="G31" s="236"/>
-      <c r="H31" s="236"/>
-      <c r="I31" s="236"/>
-      <c r="J31" s="236"/>
-      <c r="K31" s="236"/>
-      <c r="L31" s="236"/>
+      <c r="D31" s="244"/>
+      <c r="E31" s="244"/>
+      <c r="F31" s="244"/>
+      <c r="G31" s="244"/>
+      <c r="H31" s="244"/>
+      <c r="I31" s="244"/>
+      <c r="J31" s="244"/>
+      <c r="K31" s="244"/>
+      <c r="L31" s="244"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19230,10 +19242,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="238"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19250,7 +19262,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>225.07</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19259,7 +19271,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5445568.6499999994</v>
+        <v>5497345.9500000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19277,7 +19289,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19286,7 +19298,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2191000000000001</v>
+        <v>2.2174</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19318,10 +19330,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="238" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="238"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19329,7 +19341,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.0717291404295262E-3</v>
+        <v>6.0148859295760205E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19338,7 +19350,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99392827085957047</v>
+        <v>0.993985114070424</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19356,7 +19368,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15169950000000001</v>
+        <v>0.152333</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19365,7 +19377,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15101825502630839</v>
+        <v>0.15165432237590815</v>
       </c>
     </row>
   </sheetData>
@@ -19410,20 +19422,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="238" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -19441,18 +19453,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -19709,10 +19721,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="238" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="238"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19732,10 +19744,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="238" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="238"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19849,37 +19861,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="244" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20099,18 +20111,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="236" t="s">
+      <c r="C11" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="236"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20304,18 +20316,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="236" t="s">
+      <c r="C17" s="244" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="236"/>
-      <c r="E17" s="236"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="236"/>
-      <c r="J17" s="236"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="236"/>
+      <c r="D17" s="244"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="244"/>
+      <c r="K17" s="244"/>
+      <c r="L17" s="244"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20449,18 +20461,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="236" t="s">
+      <c r="C22" s="244" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="236"/>
-      <c r="E22" s="236"/>
-      <c r="F22" s="236"/>
-      <c r="G22" s="236"/>
-      <c r="H22" s="236"/>
-      <c r="I22" s="236"/>
-      <c r="J22" s="236"/>
-      <c r="K22" s="236"/>
-      <c r="L22" s="236"/>
+      <c r="D22" s="244"/>
+      <c r="E22" s="244"/>
+      <c r="F22" s="244"/>
+      <c r="G22" s="244"/>
+      <c r="H22" s="244"/>
+      <c r="I22" s="244"/>
+      <c r="J22" s="244"/>
+      <c r="K22" s="244"/>
+      <c r="L22" s="244"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20544,18 +20556,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="236" t="s">
+      <c r="C27" s="244" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="236"/>
-      <c r="E27" s="236"/>
-      <c r="F27" s="236"/>
-      <c r="G27" s="236"/>
-      <c r="H27" s="236"/>
-      <c r="I27" s="236"/>
-      <c r="J27" s="236"/>
-      <c r="K27" s="236"/>
-      <c r="L27" s="236"/>
+      <c r="D27" s="244"/>
+      <c r="E27" s="244"/>
+      <c r="F27" s="244"/>
+      <c r="G27" s="244"/>
+      <c r="H27" s="244"/>
+      <c r="I27" s="244"/>
+      <c r="J27" s="244"/>
+      <c r="K27" s="244"/>
+      <c r="L27" s="244"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -20856,10 +20868,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="235" t="s">
+      <c r="B39" s="238" t="s">
         <v>197</v>
       </c>
-      <c r="C39" s="235"/>
+      <c r="C39" s="238"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -20961,10 +20973,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="238" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="235"/>
+      <c r="C52" s="238"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21020,10 +21032,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="235" t="s">
+      <c r="B60" s="238" t="s">
         <v>314</v>
       </c>
-      <c r="C60" s="235"/>
+      <c r="C60" s="238"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21124,10 +21136,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="235" t="s">
+      <c r="B73" s="238" t="s">
         <v>411</v>
       </c>
-      <c r="C73" s="235"/>
+      <c r="C73" s="238"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21277,10 +21289,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="238"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21343,7 +21355,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>225.07</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21352,7 +21364,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.66984906759141316</v>
+        <v>0.65412142794242911</v>
       </c>
     </row>
   </sheetData>
@@ -21408,37 +21420,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="244" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21551,18 +21563,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="236" t="s">
+      <c r="C9" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21683,18 +21695,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="236" t="s">
+      <c r="C14" s="244" t="s">
         <v>390</v>
       </c>
-      <c r="D14" s="236"/>
-      <c r="E14" s="236"/>
-      <c r="F14" s="236"/>
-      <c r="G14" s="236"/>
-      <c r="H14" s="236"/>
-      <c r="I14" s="236"/>
-      <c r="J14" s="236"/>
-      <c r="K14" s="236"/>
-      <c r="L14" s="236"/>
+      <c r="D14" s="244"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="244"/>
+      <c r="G14" s="244"/>
+      <c r="H14" s="244"/>
+      <c r="I14" s="244"/>
+      <c r="J14" s="244"/>
+      <c r="K14" s="244"/>
+      <c r="L14" s="244"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21784,10 +21796,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="235" t="s">
+      <c r="B20" s="238" t="s">
         <v>392</v>
       </c>
-      <c r="C20" s="235"/>
+      <c r="C20" s="238"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21888,20 +21900,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="238" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -21919,18 +21931,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -22181,7 +22193,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>225.07</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22247,7 +22259,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5424187</v>
+        <v>5475761</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22274,7 +22286,7 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5358084</v>
+        <v>5409658</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -28942,7 +28954,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>225.07</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29013,7 +29025,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>225.07</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30515,7 +30527,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>28.453855878634638</v>
+        <v>28.724399494310997</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30552,7 +30564,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.12463186827695</v>
+        <v>18.296963641494674</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30613,7 +30625,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>23.688061174579886</v>
+        <v>23.913290884952662</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30674,7 +30686,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5445568.6499999994</v>
+        <v>5497345.9500000002</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30735,7 +30747,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5379465.6499999994</v>
+        <v>5431242.9500000002</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30772,7 +30784,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>17.755828649135719</v>
+        <v>17.926728312137545</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30809,7 +30821,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>27.226909995495468</v>
+        <v>27.488968716310946</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30944,7 +30956,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>45.469161434153833</v>
+        <v>45.901489178718144</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30981,7 +30993,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>38.950599761221852</v>
+        <v>39.325498872068806</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31018,7 +31030,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.1992928139837151E-2</v>
+        <v>2.1785785557119613E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31055,7 +31067,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.5144621673257208E-2</v>
+        <v>3.4813608555961446E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31092,7 +31104,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.2440574043630873E-3</v>
+        <v>1.2323401258747416E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31129,7 +31141,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>1.015780050812508E-2</v>
+        <v>1.0062128252998157E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31166,7 +31178,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1402115002259683E-2</v>
+        <v>1.1294723047218812E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31669,7 +31681,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.2138860833202425E-2</v>
+        <v>1.202452976422195E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32855,15 +32867,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="238"/>
+      <c r="E4" s="238" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32871,7 +32883,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>225.07</v>
+        <v>227.21</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32887,7 +32899,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5445568.6499999994</v>
+        <v>5497345.9500000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32907,7 +32919,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5379465.6499999994</v>
+        <v>5431242.9500000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32927,7 +32939,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.453855878634638</v>
+        <v>28.724399494310997</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -32947,7 +32959,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.12463186827695</v>
+        <v>18.296963641494674</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -32967,7 +32979,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>23.688061174579886</v>
+        <v>23.913290884952662</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32987,7 +32999,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.755828649135719</v>
+        <v>17.926728312137545</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32996,18 +33008,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.226909995495468</v>
+        <v>27.488968716310946</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="238" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="238"/>
+      <c r="E15" s="238" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33058,14 +33070,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="238" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="238"/>
+      <c r="E21" s="238" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="238"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33134,14 +33146,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="238" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="238"/>
+      <c r="E29" s="238" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="238"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33217,14 +33229,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="238" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="238"/>
+      <c r="E37" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="238"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33232,7 +33244,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.5144621673257208E-2</v>
+        <v>3.4813608555961446E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33248,7 +33260,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.1992928139837151E-2</v>
+        <v>2.1785785557119613E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33264,7 +33276,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2440574043630873E-3</v>
+        <v>1.2323401258747416E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33280,7 +33292,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.015780050812508E-2</v>
+        <v>1.0062128252998157E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33289,18 +33301,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1402115002259683E-2</v>
+        <v>1.1294723047218812E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="238" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="238"/>
+      <c r="E45" s="238" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="238"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33333,18 +33345,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.2138860833202425E-2</v>
+        <v>1.202452976422195E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="238" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="238"/>
+      <c r="E51" s="238" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="238"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33513,7 +33525,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>225.07</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33542,7 +33554,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5445568.6499999994</v>
+        <v>5497345.9500000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33571,7 +33583,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5379465.6499999994</v>
+        <v>5431242.9500000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33600,7 +33612,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.453855878634638</v>
+        <v>28.724399494310997</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33629,7 +33641,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.12463186827695</v>
+        <v>18.296963641494674</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33658,7 +33670,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>23.688061174579886</v>
+        <v>23.913290884952662</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33687,7 +33699,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.755828649135719</v>
+        <v>17.926728312137545</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33716,7 +33728,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.226909995495468</v>
+        <v>27.488968716310946</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34489,7 +34501,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.5144621673257208E-2</v>
+        <v>3.4813608555961446E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34518,7 +34530,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.1992928139837151E-2</v>
+        <v>2.1785785557119613E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34547,7 +34559,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2440574043630873E-3</v>
+        <v>1.2323401258747416E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34576,7 +34588,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.015780050812508E-2</v>
+        <v>1.0062128252998157E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34605,7 +34617,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1402115002259683E-2</v>
+        <v>1.1294723047218812E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34841,7 +34853,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.2138860833202425E-2</v>
+        <v>1.202452976422195E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35353,14 +35365,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="F3" s="244" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="243"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35427,19 +35439,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="245">
+      <c r="C7" s="242">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="246"/>
-      <c r="F7" s="245">
+      <c r="D7" s="243"/>
+      <c r="F7" s="242">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="246"/>
+      <c r="G7" s="243"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35466,19 +35478,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="245">
+      <c r="C9" s="242">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="F9" s="245">
+      <c r="D9" s="243"/>
+      <c r="F9" s="242">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="246"/>
+      <c r="G9" s="243"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35505,19 +35517,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="245">
+      <c r="C11" s="242">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="246"/>
-      <c r="F11" s="245">
+      <c r="D11" s="243"/>
+      <c r="F11" s="242">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="246"/>
+      <c r="G11" s="243"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35544,19 +35556,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="245">
+      <c r="C13" s="242">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="246"/>
-      <c r="F13" s="245">
+      <c r="D13" s="243"/>
+      <c r="F13" s="242">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="246"/>
+      <c r="G13" s="243"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35583,19 +35595,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="245">
+      <c r="C15" s="242">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="246"/>
-      <c r="F15" s="245">
+      <c r="D15" s="243"/>
+      <c r="F15" s="242">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="246"/>
+      <c r="G15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35622,19 +35634,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="245">
+      <c r="C17" s="242">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="246"/>
-      <c r="F17" s="245">
+      <c r="D17" s="243"/>
+      <c r="F17" s="242">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="246"/>
+      <c r="G17" s="243"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35661,22 +35673,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="245">
+      <c r="C19" s="242">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="246"/>
-      <c r="F19" s="245">
+      <c r="D19" s="243"/>
+      <c r="F19" s="242">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="246"/>
+      <c r="G19" s="243"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35703,22 +35715,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="245">
+      <c r="C21" s="242">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="246"/>
-      <c r="F21" s="245">
+      <c r="D21" s="243"/>
+      <c r="F21" s="242">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="246"/>
+      <c r="G21" s="243"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35766,22 +35778,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="245">
+      <c r="C25" s="242">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="246"/>
-      <c r="F25" s="245">
+      <c r="D25" s="243"/>
+      <c r="F25" s="242">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="246"/>
+      <c r="G25" s="243"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -35808,22 +35820,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="245">
+      <c r="C27" s="242">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="246"/>
-      <c r="F27" s="245">
+      <c r="D27" s="243"/>
+      <c r="F27" s="242">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="246"/>
+      <c r="G27" s="243"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35850,22 +35862,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="245">
+      <c r="C29" s="242">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="246"/>
-      <c r="F29" s="245">
+      <c r="D29" s="243"/>
+      <c r="F29" s="242">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="246"/>
+      <c r="G29" s="243"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35892,22 +35904,22 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="245">
+      <c r="C31" s="242">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="246"/>
-      <c r="F31" s="245">
+      <c r="D31" s="243"/>
+      <c r="F31" s="242">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="246"/>
+      <c r="G31" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="26">

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4E9644-0618-0B44-AF9F-9CE1E1E2B132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE4CB10-C421-3F4E-82B4-25534446CF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2329,6 +2329,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2336,12 +2342,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2362,14 +2362,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12715,11 +12715,11 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>164.27</v>
-    <v>2.2174</v>
-    <v>-1.65</v>
-    <v>-7.2099999999999994E-3</v>
-    <v>0.83819999999999995</v>
-    <v>3.689E-3</v>
+    <v>2.2162000000000002</v>
+    <v>2.48</v>
+    <v>1.0859000000000001E-2</v>
+    <v>0.32819999999999999</v>
+    <v>1.4219999999999999E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12727,25 +12727,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>232.82</v>
+    <v>232.285</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46294.960115948437</v>
+    <v>46296.860987835156</v>
     <v>0</v>
-    <v>227.02500000000001</v>
-    <v>5475761000000</v>
+    <v>228.16</v>
+    <v>5563726000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>230.97</v>
-    <v>28.930299999999999</v>
-    <v>228.86</v>
-    <v>227.21</v>
-    <v>228.04820000000001</v>
+    <v>229.97499999999999</v>
+    <v>29.183299999999999</v>
+    <v>228.38</v>
+    <v>230.86</v>
+    <v>231.18819999999999</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>101304989</v>
-    <v>128000018</v>
+    <v>97450913</v>
+    <v>126629251</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12767,19 +12767,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.93</v>
+    <v>53.06</v>
     <v>39.47</v>
-    <v>0.15</v>
-    <v>2.8630000000000001E-3</v>
+    <v>0.38</v>
+    <v>7.2309999999999996E-3</v>
     <v>US</v>
-    <v>52.93</v>
+    <v>53.06</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.13</v>
+    <v>52.05</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.13</v>
-    <v>52.4</v>
+    <v>52.43</v>
     <v>52.55</v>
+    <v>52.93</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5497345.9500000002</v>
+        <v>5585657.7000000002</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13624,7 +13624,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5431242.9500000002</v>
+        <v>5519554.7000000002</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>227.21</v>
+        <v>230.86</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="I5" s="208">
         <f>'AVG target price'!C7</f>
-        <v>372.92428626108091</v>
+        <v>367.96964961579448</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13665,14 +13665,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>228.04820000000001</v>
+        <v>231.18819999999999</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>28.724399494310997</v>
+        <v>29.185840707964601</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13689,14 +13689,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.65</v>
+        <v>2.48</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>18.296963641494674</v>
+        <v>18.590894002356677</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13713,14 +13713,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.83819999999999995</v>
+        <v>0.32819999999999999</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.1785785557119613E-2</v>
+        <v>2.1441342529815242E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="I8" s="209">
         <f>'AVG target price'!C10</f>
-        <v>375.83292964279934</v>
+        <v>374.84200231374206</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13737,14 +13737,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-7.2099999999999994E-3</v>
+        <v>1.0859000000000001E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.4813608555961446E-2</v>
+        <v>3.4263189812007273E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.65412142794242911</v>
+        <v>0.6236766971919866</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13761,14 +13761,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.689E-3</v>
+        <v>1.4219999999999999E-3</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.0062128252998157E-2</v>
+        <v>9.9030414985866386E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13784,14 +13784,14 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.2323401258747416E-3</v>
+        <v>1.2128562765312311E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
       </c>
       <c r="I11" s="209">
         <f>DDM!C26</f>
-        <v>1.6842105263157894</v>
+        <v>1.6326530612244898</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2174</v>
+        <v>2.2162000000000002</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>128000018</v>
+        <v>126629251</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.202452976422195E-2</v>
+        <v>1.1834416562976997E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.55</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2929999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13996,7 +13996,7 @@
         <v>387</v>
       </c>
       <c r="C29" s="218">
-        <v>0.12</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -18098,6 +18098,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18105,12 +18111,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19170,16 +19170,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>227.21</v>
+        <v>230.86</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5497345.9500000002</v>
+        <v>5585657.7000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2929999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2174</v>
+        <v>2.2162000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.0148859295760205E-3</v>
+        <v>5.9203509027894435E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.993985114070424</v>
+        <v>0.99407964909721058</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.152333</v>
+        <v>0.15265899999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15165432237590815</v>
+        <v>0.15198905901219126</v>
       </c>
     </row>
   </sheetData>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="C54" s="136">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C58" s="234">
         <f>C57/(1+C54)^5</f>
-        <v>372.92428626108091</v>
+        <v>367.96964961579448</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21241,17 +21241,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21319,7 +21319,7 @@
       </c>
       <c r="C7" s="134">
         <f>Multiples!C58</f>
-        <v>372.92428626108091</v>
+        <v>367.96964961579448</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21346,7 +21346,7 @@
       </c>
       <c r="C10" s="234">
         <f>AVERAGE(C5:C9)</f>
-        <v>375.83292964279934</v>
+        <v>374.84200231374206</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>227.21</v>
+        <v>230.86</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.65412142794242911</v>
+        <v>0.6236766971919866</v>
       </c>
     </row>
   </sheetData>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="C24" s="136">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="C26" s="234">
         <f>C23/(C24-C25)</f>
-        <v>1.6842105263157894</v>
+        <v>1.6326530612244898</v>
       </c>
     </row>
   </sheetData>
@@ -22182,10 +22182,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="250" t="s">
+      <c r="B14" s="251" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="251"/>
+      <c r="C14" s="252"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>227.21</v>
+        <v>230.86</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22212,20 +22212,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="252" t="s">
+      <c r="E17" s="250" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="250" t="s">
+      <c r="B19" s="251" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="251"/>
+      <c r="C19" s="252"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5475761</v>
+        <v>5563726</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22286,15 +22286,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5409658</v>
+        <v>5497623</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="250" t="s">
+      <c r="B28" s="251" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="251"/>
+      <c r="C28" s="252"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22370,16 +22370,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28954,7 +28954,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>227.21</v>
+        <v>230.86</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>227.21</v>
+        <v>230.86</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30527,7 +30527,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>28.724399494310997</v>
+        <v>29.185840707964601</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30564,7 +30564,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.296963641494674</v>
+        <v>18.590894002356677</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30625,7 +30625,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>23.913290884952662</v>
+        <v>24.297444362924924</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5497345.9500000002</v>
+        <v>5585657.7000000002</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30747,7 +30747,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5431242.9500000002</v>
+        <v>5519554.7000000002</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30784,7 +30784,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>17.926728312137545</v>
+        <v>18.218216055107948</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30821,7 +30821,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>27.488968716310946</v>
+        <v>27.93593802985135</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30956,7 +30956,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>45.901489178718144</v>
+        <v>46.638870612204002</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30993,7 +30993,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>39.325498872068806</v>
+        <v>39.964929598513372</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31030,7 +31030,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.1785785557119613E-2</v>
+        <v>2.1441342529815242E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31067,7 +31067,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.4813608555961446E-2</v>
+        <v>3.4263189812007273E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31104,7 +31104,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.2323401258747416E-3</v>
+        <v>1.2128562765312311E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31141,7 +31141,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>1.0062128252998157E-2</v>
+        <v>9.9030414985866386E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31178,7 +31178,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1294723047218812E-2</v>
+        <v>1.111614841704317E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31681,7 +31681,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.202452976422195E-2</v>
+        <v>1.1834416562976997E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>227.21</v>
+        <v>230.86</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5497345.9500000002</v>
+        <v>5585657.7000000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5431242.9500000002</v>
+        <v>5519554.7000000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.724399494310997</v>
+        <v>29.185840707964601</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -32959,7 +32959,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.296963641494674</v>
+        <v>18.590894002356677</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -32979,7 +32979,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>23.913290884952662</v>
+        <v>24.297444362924924</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32999,7 +32999,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.926728312137545</v>
+        <v>18.218216055107948</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33008,7 +33008,7 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.488968716310946</v>
+        <v>27.93593802985135</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.4813608555961446E-2</v>
+        <v>3.4263189812007273E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33260,7 +33260,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.1785785557119613E-2</v>
+        <v>2.1441342529815242E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2323401258747416E-3</v>
+        <v>1.2128562765312311E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33292,7 +33292,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0062128252998157E-2</v>
+        <v>9.9030414985866386E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33301,7 +33301,7 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1294723047218812E-2</v>
+        <v>1.111614841704317E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33345,7 +33345,7 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.202452976422195E-2</v>
+        <v>1.1834416562976997E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33525,7 +33525,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>227.21</v>
+        <v>230.86</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5497345.9500000002</v>
+        <v>5585657.7000000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33583,7 +33583,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5431242.9500000002</v>
+        <v>5519554.7000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.724399494310997</v>
+        <v>29.185840707964601</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.296963641494674</v>
+        <v>18.590894002356677</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33670,7 +33670,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>23.913290884952662</v>
+        <v>24.297444362924924</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33699,7 +33699,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.926728312137545</v>
+        <v>18.218216055107948</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.488968716310946</v>
+        <v>27.93593802985135</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34501,7 +34501,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.4813608555961446E-2</v>
+        <v>3.4263189812007273E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.1785785557119613E-2</v>
+        <v>2.1441342529815242E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34559,7 +34559,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2323401258747416E-3</v>
+        <v>1.2128562765312311E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34588,7 +34588,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0062128252998157E-2</v>
+        <v>9.9030414985866386E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34617,7 +34617,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1294723047218812E-2</v>
+        <v>1.111614841704317E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34853,7 +34853,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.202452976422195E-2</v>
+        <v>1.1834416562976997E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35365,14 +35365,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="241" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35439,19 +35439,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="242">
+      <c r="C7" s="239">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="F7" s="242">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="243"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35478,19 +35478,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="242">
+      <c r="C9" s="239">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="F9" s="242">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35517,19 +35517,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="242">
+      <c r="C11" s="239">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="F11" s="242">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="243"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35556,19 +35556,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="239">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="243"/>
-      <c r="F13" s="242">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="243"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35595,19 +35595,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="242">
+      <c r="C15" s="239">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="F15" s="242">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="243"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35634,19 +35634,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="242">
+      <c r="C17" s="239">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="F17" s="242">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="243"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35673,22 +35673,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="242">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="F19" s="242">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="243"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35715,22 +35715,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="242">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="F21" s="242">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="243"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35778,22 +35778,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="242">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="243"/>
-      <c r="F25" s="242">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="243"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -35820,22 +35820,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="242">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="243"/>
-      <c r="F27" s="242">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="243"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35862,22 +35862,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="242">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="F29" s="242">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="243"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35904,25 +35904,43 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="242">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="243"/>
-      <c r="F31" s="242">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="243"/>
+      <c r="G31" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35931,24 +35949,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE4CB10-C421-3F4E-82B4-25534446CF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B6AA81-AF5A-434F-B5D0-FFD0399E9193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2329,12 +2329,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2342,6 +2336,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2362,14 +2362,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12713,13 +12713,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>236.54</v>
+    <v>240.09829999999999</v>
     <v>164.27</v>
-    <v>2.2162000000000002</v>
-    <v>2.48</v>
-    <v>1.0859000000000001E-2</v>
-    <v>0.32819999999999999</v>
-    <v>1.4219999999999999E-3</v>
+    <v>2.1888999999999998</v>
+    <v>4.95</v>
+    <v>2.1158E-2</v>
+    <v>0.53669999999999995</v>
+    <v>2.2470000000000003E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12727,25 +12727,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>232.285</v>
+    <v>240.09829999999999</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46296.860987835156</v>
+    <v>46300.892718032032</v>
     <v>0</v>
-    <v>228.16</v>
-    <v>5563726000000</v>
+    <v>235.15</v>
+    <v>5757490000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>229.97499999999999</v>
-    <v>29.183299999999999</v>
-    <v>228.38</v>
-    <v>230.86</v>
-    <v>231.18819999999999</v>
+    <v>236.09</v>
+    <v>30.1996</v>
+    <v>233.95</v>
+    <v>238.9</v>
+    <v>239.4367</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>97450913</v>
-    <v>126629251</v>
+    <v>126499605</v>
+    <v>116827227</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12767,19 +12767,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.06</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.2309999999999996E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>53.06</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.05</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.43</v>
-    <v>52.55</v>
-    <v>52.93</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5585657.7000000002</v>
+        <v>5780185.5</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13624,7 +13624,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5519554.7000000002</v>
+        <v>5714082.5</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>230.86</v>
+        <v>238.9</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13665,14 +13665,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>231.18819999999999</v>
+        <v>239.4367</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>29.185840707964601</v>
+        <v>30.20227560050569</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13689,14 +13689,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>2.48</v>
+        <v>4.95</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>18.590894002356677</v>
+        <v>19.238346084912976</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13713,14 +13713,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.32819999999999999</v>
+        <v>0.53669999999999995</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.1441342529815242E-2</v>
+        <v>2.0719750257150053E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13737,14 +13737,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.0859000000000001E-2</v>
+        <v>2.1158E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.4263189812007273E-2</v>
+        <v>3.311008790288824E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.6236766971919866</v>
+        <v>0.56903307791436608</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13761,14 +13761,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.4219999999999999E-3</v>
+        <v>2.2470000000000003E-3</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>9.9030414985866386E-3</v>
+        <v>9.5697620777049457E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13777,14 +13777,14 @@
       </c>
       <c r="C11" s="206" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>236.54</v>
+        <v>240.09829999999999</v>
       </c>
       <c r="E11" s="183" t="s">
         <v>281</v>
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.2128562765312311E-3</v>
+        <v>1.1720385098367518E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2162000000000002</v>
+        <v>2.1888999999999998</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>126629251</v>
+        <v>116827227</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.1834416562976997E-2</v>
+        <v>1.1436138165461992E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.93</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>5.2929999999999998E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18098,12 +18098,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18111,6 +18105,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19170,16 +19170,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>230.86</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5585657.7000000002</v>
+        <v>5780185.5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>5.2929999999999998E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2162000000000002</v>
+        <v>2.1888999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.9203509027894435E-3</v>
+        <v>5.7222460701701902E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99407964909721058</v>
+        <v>0.99427775392982976</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15265899999999999</v>
+        <v>0.1512705</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15198905901219126</v>
+        <v>0.15063092169561404</v>
       </c>
     </row>
   </sheetData>
@@ -21241,17 +21241,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>230.86</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.6236766971919866</v>
+        <v>0.56903307791436608</v>
       </c>
     </row>
   </sheetData>
@@ -22182,10 +22182,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="251" t="s">
+      <c r="B14" s="250" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="252"/>
+      <c r="C14" s="251"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>230.86</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22212,20 +22212,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="252" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="251" t="s">
+      <c r="B19" s="250" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="252"/>
+      <c r="C19" s="251"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5563726</v>
+        <v>5757490</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22286,15 +22286,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5497623</v>
+        <v>5691387</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="251" t="s">
+      <c r="B28" s="250" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="251"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22370,16 +22370,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28954,7 +28954,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>230.86</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>230.86</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30527,7 +30527,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>29.185840707964601</v>
+        <v>30.20227560050569</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30564,7 +30564,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.590894002356677</v>
+        <v>19.238346084912976</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30625,7 +30625,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.297444362924924</v>
+        <v>25.14363448974601</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5585657.7000000002</v>
+        <v>5780185.5</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30747,7 +30747,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5519554.7000000002</v>
+        <v>5714082.5</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30784,7 +30784,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>18.218216055107948</v>
+        <v>18.860287686198919</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30821,7 +30821,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>27.93593802985135</v>
+        <v>28.920495093101998</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30918,8 +30918,8 @@
       <c r="Z160" s="49"/>
       <c r="AA160" s="49"/>
       <c r="AC160" s="64">
-        <f>AC107+AC52+AC108+AC54+AC56+AC57</f>
-        <v>138109.9567908489</v>
+        <f>AC107+AC52+AC108+AC54+AC56+AC57+AC55</f>
+        <v>121461.9567908489</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -30956,7 +30956,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>46.638870612204002</v>
+        <v>48.263129988978321</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30993,7 +30993,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>39.964929598513372</v>
+        <v>47.044215744353188</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31030,7 +31030,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.1441342529815242E-2</v>
+        <v>2.0719750257150053E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31067,7 +31067,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.4263189812007273E-2</v>
+        <v>3.311008790288824E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31104,7 +31104,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.2128562765312311E-3</v>
+        <v>1.1720385098367518E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31141,7 +31141,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>9.9030414985866386E-3</v>
+        <v>9.5697620777049457E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31178,7 +31178,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.111614841704317E-2</v>
+        <v>1.0742042794301325E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31215,7 +31215,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="153">
         <f>AC160/AC5</f>
-        <v>0.45585507689185656</v>
+        <v>0.40090556060471172</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31681,7 +31681,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.1834416562976997E-2</v>
+        <v>1.1436138165461992E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>230.86</v>
+        <v>238.9</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5585657.7000000002</v>
+        <v>5780185.5</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5519554.7000000002</v>
+        <v>5714082.5</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>29.185840707964601</v>
+        <v>30.20227560050569</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -32959,7 +32959,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.590894002356677</v>
+        <v>19.238346084912976</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -32979,7 +32979,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>24.297444362924924</v>
+        <v>25.14363448974601</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32999,7 +32999,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>18.218216055107948</v>
+        <v>18.860287686198919</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33008,7 +33008,7 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.93593802985135</v>
+        <v>28.920495093101998</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.4263189812007273E-2</v>
+        <v>3.311008790288824E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33260,7 +33260,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.1441342529815242E-2</v>
+        <v>2.0719750257150053E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2128562765312311E-3</v>
+        <v>1.1720385098367518E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33292,7 +33292,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>9.9030414985866386E-3</v>
+        <v>9.5697620777049457E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33301,7 +33301,7 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.111614841704317E-2</v>
+        <v>1.0742042794301325E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33345,7 +33345,7 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.1834416562976997E-2</v>
+        <v>1.1436138165461992E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33525,7 +33525,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>230.86</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5585657.7000000002</v>
+        <v>5780185.5</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33583,7 +33583,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5519554.7000000002</v>
+        <v>5714082.5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>29.185840707964601</v>
+        <v>30.20227560050569</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.590894002356677</v>
+        <v>19.238346084912976</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33670,7 +33670,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>24.297444362924924</v>
+        <v>25.14363448974601</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33699,7 +33699,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>18.218216055107948</v>
+        <v>18.860287686198919</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.93593802985135</v>
+        <v>28.920495093101998</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34501,7 +34501,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.4263189812007273E-2</v>
+        <v>3.311008790288824E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.1441342529815242E-2</v>
+        <v>2.0719750257150053E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34559,7 +34559,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2128562765312311E-3</v>
+        <v>1.1720385098367518E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34588,7 +34588,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>9.9030414985866386E-3</v>
+        <v>9.5697620777049457E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34617,7 +34617,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.111614841704317E-2</v>
+        <v>1.0742042794301325E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34853,7 +34853,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.1834416562976997E-2</v>
+        <v>1.1436138165461992E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35365,14 +35365,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35439,19 +35439,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="242">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="243"/>
+      <c r="F7" s="242">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="243"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35478,19 +35478,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="242">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="243"/>
+      <c r="F9" s="242">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="243"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35517,19 +35517,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="242">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="243"/>
+      <c r="F11" s="242">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="243"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35556,19 +35556,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="242">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="243"/>
+      <c r="F13" s="242">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="243"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35595,19 +35595,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="242">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="243"/>
+      <c r="F15" s="242">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35634,19 +35634,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="242">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="243"/>
+      <c r="F17" s="242">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="243"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35673,22 +35673,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="242">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="243"/>
+      <c r="F19" s="242">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="243"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35715,22 +35715,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="242">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="243"/>
+      <c r="F21" s="242">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="243"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35778,22 +35778,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="242">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="243"/>
+      <c r="F25" s="242">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="243"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -35820,22 +35820,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="242">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="243"/>
+      <c r="F27" s="242">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="243"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35862,22 +35862,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="242">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="243"/>
+      <c r="F29" s="242">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="243"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35904,43 +35904,25 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="242">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="243"/>
+      <c r="F31" s="242">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35949,6 +35931,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B6AA81-AF5A-434F-B5D0-FFD0399E9193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A183321F-5CE3-3E4A-9ADA-7F6916BDF2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2329,6 +2329,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2336,12 +2342,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2362,14 +2362,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12713,13 +12713,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>240.09829999999999</v>
+    <v>243.37</v>
     <v>164.27</v>
-    <v>2.1888999999999998</v>
-    <v>4.95</v>
-    <v>2.1158E-2</v>
-    <v>0.53669999999999995</v>
-    <v>2.2470000000000003E-3</v>
+    <v>2.1823000000000001</v>
+    <v>-1.2</v>
+    <v>-5.2070000000000007E-3</v>
+    <v>3.8199999999999998E-2</v>
+    <v>1.6660000000000001E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12727,25 +12727,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>240.09829999999999</v>
+    <v>233.92</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46300.892718032032</v>
+    <v>46304.99999582109</v>
     <v>0</v>
-    <v>235.15</v>
-    <v>5757490000000</v>
+    <v>229.11</v>
+    <v>5525648000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>236.09</v>
-    <v>30.1996</v>
-    <v>233.95</v>
-    <v>238.9</v>
-    <v>239.4367</v>
+    <v>233.83500000000001</v>
+    <v>29.135100000000001</v>
+    <v>230.48</v>
+    <v>229.28</v>
+    <v>229.31819999999999</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>126499605</v>
-    <v>116827227</v>
+    <v>84645559</v>
+    <v>110533758</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12767,19 +12767,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13001,9 +13001,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5780185.5</v>
+        <v>5547429.5999999996</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13624,7 +13624,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5714082.5</v>
+        <v>5481326.5999999996</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>238.9</v>
+        <v>229.28</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13665,14 +13665,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>239.4367</v>
+        <v>229.31819999999999</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>30.20227560050569</v>
+        <v>28.986093552465235</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13689,14 +13689,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>4.95</v>
+        <v>-1.2</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>19.238346084912976</v>
+        <v>18.463658394093123</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13713,14 +13713,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.53669999999999995</v>
+        <v>3.8199999999999998E-2</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.0719750257150053E-2</v>
+        <v>2.1589097768811703E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13737,14 +13737,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.1158E-2</v>
+        <v>-5.2070000000000007E-3</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.311008790288824E-2</v>
+        <v>3.4499302163293791E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.56903307791436608</v>
+        <v>0.63486567652539272</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13761,14 +13761,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>2.2470000000000003E-3</v>
+        <v>1.6660000000000001E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>9.5697620777049457E-3</v>
+        <v>9.9712847189624542E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13777,14 +13777,14 @@
       </c>
       <c r="C11" s="206" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>240.09829999999999</v>
+        <v>243.37</v>
       </c>
       <c r="E11" s="183" t="s">
         <v>281</v>
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.1720385098367518E-3</v>
+        <v>1.2212142358688069E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1888999999999998</v>
+        <v>2.1823000000000001</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>116827227</v>
+        <v>110533758</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.1436138165461992E-2</v>
+        <v>1.1915969154435057E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18098,6 +18098,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18105,12 +18111,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19170,16 +19170,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>238.9</v>
+        <v>229.28</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5780185.5</v>
+        <v>5547429.5999999996</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.1888999999999998</v>
+        <v>2.1823000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.7222460701701902E-3</v>
+        <v>5.9609056620110231E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99427775392982976</v>
+        <v>0.99403909433798898</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1512705</v>
+        <v>0.15064349999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15063092169561404</v>
+        <v>0.14998098408155427</v>
       </c>
     </row>
   </sheetData>
@@ -21241,17 +21241,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>238.9</v>
+        <v>229.28</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.56903307791436608</v>
+        <v>0.63486567652539272</v>
       </c>
     </row>
   </sheetData>
@@ -22182,10 +22182,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="250" t="s">
+      <c r="B14" s="251" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="251"/>
+      <c r="C14" s="252"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>238.9</v>
+        <v>229.28</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22212,20 +22212,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="252" t="s">
+      <c r="E17" s="250" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="250" t="s">
+      <c r="B19" s="251" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="251"/>
+      <c r="C19" s="252"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5757490</v>
+        <v>5525648</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22286,15 +22286,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5691387</v>
+        <v>5459545</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="250" t="s">
+      <c r="B28" s="251" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="251"/>
+      <c r="C28" s="252"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22370,16 +22370,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28954,7 +28954,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>238.9</v>
+        <v>229.28</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>238.9</v>
+        <v>229.28</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30527,7 +30527,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>30.20227560050569</v>
+        <v>28.986093552465235</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30564,7 +30564,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>19.238346084912976</v>
+        <v>18.463658394093123</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30625,7 +30625,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>25.14363448974601</v>
+        <v>24.13115326835063</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5780185.5</v>
+        <v>5547429.5999999996</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30747,7 +30747,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5714082.5</v>
+        <v>5481326.5999999996</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30784,7 +30784,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>18.860287686198919</v>
+        <v>18.092037799246786</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30821,7 +30821,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>28.920495093101998</v>
+        <v>27.742455422894132</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30956,7 +30956,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>48.263129988978321</v>
+        <v>46.31967536154437</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30993,7 +30993,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>47.044215744353188</v>
+        <v>45.127929310726948</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31030,7 +31030,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.0719750257150053E-2</v>
+        <v>2.1589097768811703E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31067,7 +31067,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.311008790288824E-2</v>
+        <v>3.4499302163293791E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31104,7 +31104,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.1720385098367518E-3</v>
+        <v>1.2212142358688069E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31141,7 +31141,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>9.5697620777049457E-3</v>
+        <v>9.9712847189624542E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31178,7 +31178,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.0742042794301325E-2</v>
+        <v>1.1192751323964526E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31681,7 +31681,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.1436138165461992E-2</v>
+        <v>1.1915969154435057E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>238.9</v>
+        <v>229.28</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5780185.5</v>
+        <v>5547429.5999999996</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5714082.5</v>
+        <v>5481326.5999999996</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>30.20227560050569</v>
+        <v>28.986093552465235</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -32959,7 +32959,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>19.238346084912976</v>
+        <v>18.463658394093123</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -32979,7 +32979,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>25.14363448974601</v>
+        <v>24.13115326835063</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32999,7 +32999,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>18.860287686198919</v>
+        <v>18.092037799246786</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33008,7 +33008,7 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>28.920495093101998</v>
+        <v>27.742455422894132</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.311008790288824E-2</v>
+        <v>3.4499302163293791E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33260,7 +33260,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.0719750257150053E-2</v>
+        <v>2.1589097768811703E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.1720385098367518E-3</v>
+        <v>1.2212142358688069E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33292,7 +33292,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>9.5697620777049457E-3</v>
+        <v>9.9712847189624542E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33301,7 +33301,7 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.0742042794301325E-2</v>
+        <v>1.1192751323964526E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33345,7 +33345,7 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.1436138165461992E-2</v>
+        <v>1.1915969154435057E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33525,7 +33525,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>238.9</v>
+        <v>229.28</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5780185.5</v>
+        <v>5547429.5999999996</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33583,7 +33583,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5714082.5</v>
+        <v>5481326.5999999996</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>30.20227560050569</v>
+        <v>28.986093552465235</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>19.238346084912976</v>
+        <v>18.463658394093123</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33670,7 +33670,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>25.14363448974601</v>
+        <v>24.13115326835063</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33699,7 +33699,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>18.860287686198919</v>
+        <v>18.092037799246786</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>28.920495093101998</v>
+        <v>27.742455422894132</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34501,7 +34501,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.311008790288824E-2</v>
+        <v>3.4499302163293791E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.0719750257150053E-2</v>
+        <v>2.1589097768811703E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34559,7 +34559,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.1720385098367518E-3</v>
+        <v>1.2212142358688069E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34588,7 +34588,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>9.5697620777049457E-3</v>
+        <v>9.9712847189624542E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34617,7 +34617,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.0742042794301325E-2</v>
+        <v>1.1192751323964526E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34853,7 +34853,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.1436138165461992E-2</v>
+        <v>1.1915969154435057E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35365,14 +35365,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="241" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35439,19 +35439,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="242">
+      <c r="C7" s="239">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="F7" s="242">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="243"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35478,19 +35478,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="242">
+      <c r="C9" s="239">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="F9" s="242">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35517,19 +35517,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="242">
+      <c r="C11" s="239">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="F11" s="242">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="243"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35556,19 +35556,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="239">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="243"/>
-      <c r="F13" s="242">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="243"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35595,19 +35595,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="242">
+      <c r="C15" s="239">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="F15" s="242">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="243"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35634,19 +35634,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="242">
+      <c r="C17" s="239">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="F17" s="242">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="243"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35673,22 +35673,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="242">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="F19" s="242">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="243"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35715,22 +35715,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="242">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="F21" s="242">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="243"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35778,22 +35778,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="242">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="243"/>
-      <c r="F25" s="242">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="243"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -35820,22 +35820,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="242">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="243"/>
-      <c r="F27" s="242">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="243"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35862,22 +35862,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="242">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="F29" s="242">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="243"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35904,25 +35904,43 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="242">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="243"/>
-      <c r="F31" s="242">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="243"/>
+      <c r="G31" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35931,24 +35949,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A183321F-5CE3-3E4A-9ADA-7F6916BDF2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812D1582-2025-2842-81ED-B651809E5BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="424">
   <si>
     <t>Ticker</t>
   </si>
@@ -1400,6 +1400,30 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1440,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1582,6 +1606,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1999,11 +2031,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2317,6 +2350,14 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2329,12 +2370,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2342,6 +2377,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2362,17 +2403,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -12716,10 +12758,10 @@
     <v>243.37</v>
     <v>164.27</v>
     <v>2.1823000000000001</v>
-    <v>-1.2</v>
-    <v>-5.2070000000000007E-3</v>
-    <v>3.8199999999999998E-2</v>
-    <v>1.6660000000000001E-4</v>
+    <v>-2.96</v>
+    <v>-1.291E-2</v>
+    <v>-8.1199999999999994E-2</v>
+    <v>-3.5880000000000005E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12727,25 +12769,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>233.92</v>
+    <v>228.86</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46304.99999582109</v>
+    <v>46307.862072546093</v>
     <v>0</v>
-    <v>229.11</v>
-    <v>5525648000000</v>
+    <v>224.9</v>
+    <v>5454312000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>233.83500000000001</v>
-    <v>29.135100000000001</v>
-    <v>230.48</v>
+    <v>228.73</v>
+    <v>28.609400000000001</v>
     <v>229.28</v>
-    <v>229.31819999999999</v>
+    <v>226.32</v>
+    <v>226.2388</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>84645559</v>
-    <v>110533758</v>
+    <v>69740922</v>
+    <v>108532316</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -13001,9 +13043,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13557,7 +13599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I61"/>
+  <dimension ref="B1:K61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13569,25 +13611,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="235" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="235" t="s">
+      <c r="C2" s="240"/>
+      <c r="E2" s="239" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="H2" s="235" t="s">
+      <c r="F2" s="240"/>
+      <c r="H2" s="239" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="236"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="240"/>
+      <c r="K2" s="133" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
         <v>11</v>
       </c>
@@ -13600,7 +13647,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5547429.5999999996</v>
+        <v>5475812.3999999994</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13610,8 +13657,11 @@
         <f>'AVG target price'!C5</f>
         <v>205.87576455664953</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K3" s="237" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="182" t="s">
         <v>0</v>
       </c>
@@ -13624,7 +13674,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5481326.5999999996</v>
+        <v>5409709.3999999994</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13634,14 +13684,17 @@
         <f>'AVG target price'!C6</f>
         <v>439.18110219686605</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K4" s="237" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="182" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>229.28</v>
+        <v>226.32</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13658,21 +13711,24 @@
         <f>'AVG target price'!C7</f>
         <v>367.96964961579448</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="182" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>229.31819999999999</v>
+        <v>226.2388</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>28.986093552465235</v>
+        <v>28.611883691529709</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13682,21 +13738,24 @@
         <f>'AVG target price'!C8</f>
         <v>456.30961943941008</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K6" s="238" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="182" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.2</v>
+        <v>-2.96</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>18.463658394093123</v>
+        <v>18.225292950763937</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13707,20 +13766,20 @@
         <v>404.87387575999048</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="182" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>3.8199999999999998E-2</v>
+        <v>-8.1199999999999994E-2</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.1589097768811703E-2</v>
+        <v>2.1871457831535646E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13731,20 +13790,20 @@
         <v>374.84200231374206</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="182" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-5.2070000000000007E-3</v>
+        <v>-1.291E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.4499302163293791E-2</v>
+        <v>3.4950512548603749E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13752,26 +13811,26 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.63486567652539272</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.65624780096209823</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="182" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.6660000000000001E-4</v>
+        <v>-3.5880000000000005E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>9.9712847189624542E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1.0101697421189959E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="182" t="s">
         <v>7</v>
       </c>
@@ -13784,7 +13843,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.2212142358688069E-3</v>
+        <v>1.2371862849063274E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
@@ -13794,7 +13853,7 @@
         <v>1.6326530612244898</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="182" t="s">
         <v>8</v>
       </c>
@@ -13810,7 +13869,7 @@
         <v>0.60223497527101955</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="182" t="s">
         <v>9</v>
       </c>
@@ -13833,13 +13892,13 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="183" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>110533758</v>
+        <v>108532316</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13849,16 +13908,16 @@
         <v>1.0183873919662139</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="182" t="s">
         <v>282</v>
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.1915969154435057E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1.207181604687553E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="183" t="s">
         <v>287</v>
       </c>
@@ -13866,12 +13925,16 @@
         <f>Statement!AC177</f>
         <v>2.742863070539419</v>
       </c>
+      <c r="H16" s="239" t="s">
+        <v>416</v>
+      </c>
+      <c r="I16" s="240"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="241" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="237"/>
+      <c r="C17" s="241"/>
       <c r="E17" s="181" t="s">
         <v>288</v>
       </c>
@@ -13879,6 +13942,13 @@
         <f>Statement!AC173</f>
         <v>3.9553626782393055E-2</v>
       </c>
+      <c r="H17" s="182" t="s">
+        <v>157</v>
+      </c>
+      <c r="I17" s="235">
+        <f>DCF!C15</f>
+        <v>0.12</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="181" t="s">
@@ -13894,7 +13964,13 @@
         <f>Statement!AC146</f>
         <v>154.53760182273862</v>
       </c>
-      <c r="I18" s="50"/>
+      <c r="H18" s="183" t="s">
+        <v>417</v>
+      </c>
+      <c r="I18" s="236">
+        <f>Multiples!C54</f>
+        <v>0.123</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="181" t="s">
@@ -13944,14 +14020,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="241" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="237"/>
-      <c r="E25" s="235" t="s">
+      <c r="C25" s="241"/>
+      <c r="E25" s="239" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="236"/>
+      <c r="F25" s="240"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -14132,13 +14208,14 @@
       <c r="H61" s="133"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14151,6 +14228,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{10489DD8-00F1-4B4C-88E5-8DC4CFDEF80F}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{B6EFC4C8-9B6F-6946-AC56-6D30B37EC39E}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{D64C6099-5F2B-E843-99EC-F53B32B11DC6}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{74B4AB1E-2742-2441-B9AD-D802B27B47CF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14160,18 +14243,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="19" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="133" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>103</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{2887DF58-DFFB-114A-8990-41F77DA26F54}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{0AD1E0BC-6275-0D4A-8036-A67BC50CAD73}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{C57FB289-D17F-D34E-8088-5B146C03C9F9}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{731F71B8-75A4-BD4C-95AB-3063A9FCA837}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{CFE7E2D2-F819-0448-8CA3-51B7B205F47B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14208,36 +14330,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="238" t="s">
+      <c r="S2" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14248,32 +14370,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="245" t="s">
+      <c r="S4" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
+      <c r="AA4" s="250"/>
+      <c r="AB4" s="250"/>
+      <c r="AC4" s="250"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14858,33 +14980,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="244" t="s">
+      <c r="C12" s="248" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="244"/>
-      <c r="G12" s="244"/>
-      <c r="H12" s="244"/>
-      <c r="I12" s="244"/>
-      <c r="J12" s="244"/>
-      <c r="K12" s="244"/>
-      <c r="L12" s="244"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="248"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="248"/>
+      <c r="I12" s="248"/>
+      <c r="J12" s="248"/>
+      <c r="K12" s="248"/>
+      <c r="L12" s="248"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="245" t="s">
+      <c r="S12" s="249" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="246"/>
-      <c r="U12" s="246"/>
-      <c r="V12" s="246"/>
-      <c r="W12" s="246"/>
-      <c r="X12" s="246"/>
-      <c r="Y12" s="246"/>
-      <c r="Z12" s="246"/>
-      <c r="AA12" s="246"/>
-      <c r="AB12" s="246"/>
-      <c r="AC12" s="246"/>
+      <c r="T12" s="250"/>
+      <c r="U12" s="250"/>
+      <c r="V12" s="250"/>
+      <c r="W12" s="250"/>
+      <c r="X12" s="250"/>
+      <c r="Y12" s="250"/>
+      <c r="Z12" s="250"/>
+      <c r="AA12" s="250"/>
+      <c r="AB12" s="250"/>
+      <c r="AC12" s="250"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -15433,35 +15555,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="P2" s="238" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15470,31 +15592,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="P4" s="246" t="s">
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="P4" s="250" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
+      <c r="Q4" s="250"/>
+      <c r="R4" s="250"/>
+      <c r="S4" s="250"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15689,32 +15811,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="246" t="s">
+      <c r="P9" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="246"/>
-      <c r="S9" s="246"/>
-      <c r="T9" s="246"/>
-      <c r="U9" s="246"/>
-      <c r="V9" s="246"/>
-      <c r="W9" s="246"/>
-      <c r="X9" s="246"/>
-      <c r="Y9" s="246"/>
-      <c r="Z9" s="246"/>
+      <c r="Q9" s="250"/>
+      <c r="R9" s="250"/>
+      <c r="S9" s="250"/>
+      <c r="T9" s="250"/>
+      <c r="U9" s="250"/>
+      <c r="V9" s="250"/>
+      <c r="W9" s="250"/>
+      <c r="X9" s="250"/>
+      <c r="Y9" s="250"/>
+      <c r="Z9" s="250"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16190,31 +16312,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="244"/>
-      <c r="L17" s="244"/>
-      <c r="P17" s="246" t="s">
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
+      <c r="P17" s="250" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="246"/>
-      <c r="R17" s="246"/>
-      <c r="S17" s="246"/>
-      <c r="T17" s="246"/>
-      <c r="U17" s="246"/>
-      <c r="V17" s="246"/>
-      <c r="W17" s="246"/>
-      <c r="X17" s="246"/>
-      <c r="Y17" s="246"/>
-      <c r="Z17" s="246"/>
+      <c r="Q17" s="250"/>
+      <c r="R17" s="250"/>
+      <c r="S17" s="250"/>
+      <c r="T17" s="250"/>
+      <c r="U17" s="250"/>
+      <c r="V17" s="250"/>
+      <c r="W17" s="250"/>
+      <c r="X17" s="250"/>
+      <c r="Y17" s="250"/>
+      <c r="Z17" s="250"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16692,60 +16814,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -16931,30 +17053,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="248" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="249"/>
-      <c r="Q11" s="249"/>
-      <c r="R11" s="249"/>
-      <c r="S11" s="249"/>
-      <c r="T11" s="249"/>
-      <c r="U11" s="249"/>
-      <c r="V11" s="249"/>
-      <c r="W11" s="249"/>
-      <c r="X11" s="249"/>
-      <c r="Y11" s="249"/>
-      <c r="Z11" s="249"/>
+      <c r="P11" s="253"/>
+      <c r="Q11" s="253"/>
+      <c r="R11" s="253"/>
+      <c r="S11" s="253"/>
+      <c r="T11" s="253"/>
+      <c r="U11" s="253"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="253"/>
+      <c r="X11" s="253"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
       <c r="AB11" s="111"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17196,18 +17318,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="248" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17420,23 +17542,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="249"/>
-      <c r="C25" s="249"/>
+      <c r="B25" s="253"/>
+      <c r="C25" s="253"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="244" t="s">
+      <c r="C26" s="248" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="248"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="248"/>
+      <c r="I26" s="248"/>
+      <c r="J26" s="248"/>
+      <c r="K26" s="248"/>
+      <c r="L26" s="248"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17628,18 +17750,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="244" t="s">
+      <c r="C33" s="248" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="244"/>
-      <c r="I33" s="244"/>
-      <c r="J33" s="244"/>
-      <c r="K33" s="244"/>
-      <c r="L33" s="244"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="248"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="248"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17823,18 +17945,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="244" t="s">
+      <c r="C40" s="248" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
+      <c r="D40" s="248"/>
+      <c r="E40" s="248"/>
+      <c r="F40" s="248"/>
+      <c r="G40" s="248"/>
+      <c r="H40" s="248"/>
+      <c r="I40" s="248"/>
+      <c r="J40" s="248"/>
+      <c r="K40" s="248"/>
+      <c r="L40" s="248"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18098,12 +18220,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18111,6 +18227,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18148,60 +18270,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249"/>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
+      <c r="AA2" s="253"/>
+      <c r="AB2" s="253"/>
+      <c r="AC2" s="253"/>
       <c r="AE2" s="110"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="S4" s="249"/>
-      <c r="T4" s="249"/>
-      <c r="U4" s="249"/>
-      <c r="V4" s="249"/>
-      <c r="W4" s="249"/>
-      <c r="X4" s="249"/>
-      <c r="Y4" s="249"/>
-      <c r="Z4" s="249"/>
-      <c r="AA4" s="249"/>
-      <c r="AB4" s="249"/>
-      <c r="AC4" s="249"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="111"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18564,18 +18686,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="248" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
-      <c r="L13" s="244"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="248"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="248"/>
+      <c r="I13" s="248"/>
+      <c r="J13" s="248"/>
+      <c r="K13" s="248"/>
+      <c r="L13" s="248"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18668,18 +18790,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="248" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18871,18 +18993,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="244" t="s">
+      <c r="C25" s="248" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
-      <c r="K25" s="244"/>
-      <c r="L25" s="244"/>
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="248"/>
+      <c r="I25" s="248"/>
+      <c r="J25" s="248"/>
+      <c r="K25" s="248"/>
+      <c r="L25" s="248"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19020,18 +19142,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="244" t="s">
+      <c r="C31" s="248" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19170,16 +19292,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19193,18 +19315,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="133" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>156</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{3DB6C82D-D023-5C41-84B0-D0C0BFB77DAE}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{C51B6CDC-BAD8-E74E-815A-542865D3D37E}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{F55B46DC-4611-F143-96F9-CD1D252B05B5}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{28737E29-2602-0445-963A-C4E24F8943AB}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{6BEC8394-147C-6142-9C26-606A441DF628}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19242,10 +19403,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19262,7 +19423,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>229.28</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19271,7 +19432,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5547429.5999999996</v>
+        <v>5475812.3999999994</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19330,10 +19491,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="242" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="238"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19341,7 +19502,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.9609056620110231E-3</v>
+        <v>6.038396549230449E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19350,7 +19511,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99403909433798898</v>
+        <v>0.99396160345076956</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19377,7 +19538,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14998098408155427</v>
+        <v>0.14997237147313058</v>
       </c>
     </row>
   </sheetData>
@@ -19422,60 +19583,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19721,10 +19882,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="238" t="s">
+      <c r="B13" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="238"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19744,10 +19905,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="238" t="s">
+      <c r="B18" s="242" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="238"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19861,37 +20022,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20111,18 +20272,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="248" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20316,18 +20477,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="248" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="244"/>
-      <c r="L17" s="244"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20461,18 +20622,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="248" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
-      <c r="F22" s="244"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="244"/>
-      <c r="I22" s="244"/>
-      <c r="J22" s="244"/>
-      <c r="K22" s="244"/>
-      <c r="L22" s="244"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="248"/>
+      <c r="G22" s="248"/>
+      <c r="H22" s="248"/>
+      <c r="I22" s="248"/>
+      <c r="J22" s="248"/>
+      <c r="K22" s="248"/>
+      <c r="L22" s="248"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20556,18 +20717,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="244" t="s">
+      <c r="C27" s="248" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="E27" s="244"/>
-      <c r="F27" s="244"/>
-      <c r="G27" s="244"/>
-      <c r="H27" s="244"/>
-      <c r="I27" s="244"/>
-      <c r="J27" s="244"/>
-      <c r="K27" s="244"/>
-      <c r="L27" s="244"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="248"/>
+      <c r="I27" s="248"/>
+      <c r="J27" s="248"/>
+      <c r="K27" s="248"/>
+      <c r="L27" s="248"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -20868,10 +21029,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="238" t="s">
+      <c r="B39" s="242" t="s">
         <v>197</v>
       </c>
-      <c r="C39" s="238"/>
+      <c r="C39" s="242"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -20973,10 +21134,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="238" t="s">
+      <c r="B52" s="242" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="238"/>
+      <c r="C52" s="242"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21032,10 +21193,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="238" t="s">
+      <c r="B60" s="242" t="s">
         <v>314</v>
       </c>
-      <c r="C60" s="238"/>
+      <c r="C60" s="242"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21136,10 +21297,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="238" t="s">
+      <c r="B73" s="242" t="s">
         <v>411</v>
       </c>
-      <c r="C73" s="238"/>
+      <c r="C73" s="242"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21241,17 +21402,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21289,10 +21450,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21355,7 +21516,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>229.28</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21364,7 +21525,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.63486567652539272</v>
+        <v>0.65624780096209823</v>
       </c>
     </row>
   </sheetData>
@@ -21380,18 +21541,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18.83203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="133" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{1A710FAA-9B12-454D-95BA-030D666701CD}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{790DB574-6F94-C941-8EC7-3F7F3C78D4D5}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{6737C960-2701-B84D-B6E8-1D3D3189B23C}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{6168D43E-330E-D84F-8381-FF98592C62D3}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{28FBCAAD-1B8D-9B4A-8CBF-65FB96D9E7B8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21420,37 +21620,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21563,18 +21763,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="248" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21695,18 +21895,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="248" t="s">
         <v>390</v>
       </c>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="244"/>
-      <c r="K14" s="244"/>
-      <c r="L14" s="244"/>
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="248"/>
+      <c r="G14" s="248"/>
+      <c r="H14" s="248"/>
+      <c r="I14" s="248"/>
+      <c r="J14" s="248"/>
+      <c r="K14" s="248"/>
+      <c r="L14" s="248"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21796,10 +21996,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="238" t="s">
+      <c r="B20" s="242" t="s">
         <v>392</v>
       </c>
-      <c r="C20" s="238"/>
+      <c r="C20" s="242"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21900,60 +22100,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22182,10 +22382,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="251" t="s">
+      <c r="B14" s="254" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="252"/>
+      <c r="C14" s="255"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22193,7 +22393,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>229.28</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22212,20 +22412,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="256" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="256"/>
+      <c r="G17" s="256"/>
+      <c r="H17" s="256"/>
+      <c r="I17" s="256"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="251" t="s">
+      <c r="B19" s="254" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="252"/>
+      <c r="C19" s="255"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22259,7 +22459,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5525648</v>
+        <v>5454312</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22286,15 +22486,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5459545</v>
+        <v>5388209</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="251" t="s">
+      <c r="B28" s="254" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="255"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22370,16 +22570,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28954,7 +29154,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>229.28</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29025,7 +29225,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>229.28</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30527,7 +30727,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>28.986093552465235</v>
+        <v>28.611883691529709</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30564,7 +30764,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.463658394093123</v>
+        <v>18.225292950763937</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30625,7 +30825,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.13115326835063</v>
+        <v>23.819620584844358</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30686,7 +30886,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5547429.5999999996</v>
+        <v>5475812.3999999994</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30747,7 +30947,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5481326.5999999996</v>
+        <v>5409709.3999999994</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30784,7 +30984,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>18.092037799246786</v>
+        <v>17.855653218646129</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30821,7 +31021,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>27.742455422894132</v>
+        <v>27.379981678214786</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30956,7 +31156,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>46.31967536154437</v>
+        <v>45.721689322333916</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30993,7 +31193,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>45.127929310726948</v>
+        <v>44.538302715765028</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31030,7 +31230,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.1589097768811703E-2</v>
+        <v>2.1871457831535646E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31067,7 +31267,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.4499302163293791E-2</v>
+        <v>3.4950512548603749E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31104,7 +31304,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.2212142358688069E-3</v>
+        <v>1.2371862849063274E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31141,7 +31341,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>9.9712847189624542E-3</v>
+        <v>1.0101697421189959E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31178,7 +31378,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1192751323964526E-2</v>
+        <v>1.1339139375921646E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31681,7 +31881,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.1915969154435057E-2</v>
+        <v>1.207181604687553E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32832,18 +33032,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="133" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>224</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{69D6E76D-7A34-E44C-8C04-715DC0C65111}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{E80532D9-627B-024C-B694-F903E60B2428}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{8DF49614-04B4-EF4D-9C99-832506CCA3F7}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{4A98CDA9-19D6-9047-964C-AE40FE137305}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{2F72496E-E032-D544-9FC9-4FC0E19A0D9E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -32867,15 +33106,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="E4" s="238" t="s">
+      <c r="C4" s="242"/>
+      <c r="E4" s="242" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32883,7 +33122,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>229.28</v>
+        <v>226.32</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32899,7 +33138,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5547429.5999999996</v>
+        <v>5475812.3999999994</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32919,7 +33158,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5481326.5999999996</v>
+        <v>5409709.3999999994</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32939,7 +33178,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.986093552465235</v>
+        <v>28.611883691529709</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -32959,7 +33198,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.463658394093123</v>
+        <v>18.225292950763937</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -32979,7 +33218,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>24.13115326835063</v>
+        <v>23.819620584844358</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32999,7 +33238,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>18.092037799246786</v>
+        <v>17.855653218646129</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33008,18 +33247,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.742455422894132</v>
+        <v>27.379981678214786</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="242" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="238"/>
-      <c r="E15" s="238" t="s">
+      <c r="C15" s="242"/>
+      <c r="E15" s="242" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="238"/>
+      <c r="F15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33070,14 +33309,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="238" t="s">
+      <c r="B21" s="242" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="238"/>
-      <c r="E21" s="238" t="s">
+      <c r="C21" s="242"/>
+      <c r="E21" s="242" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="238"/>
+      <c r="F21" s="242"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33146,14 +33385,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="242" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="238"/>
-      <c r="E29" s="238" t="s">
+      <c r="C29" s="242"/>
+      <c r="E29" s="242" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="238"/>
+      <c r="F29" s="242"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33229,14 +33468,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="242" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="238"/>
-      <c r="E37" s="238" t="s">
+      <c r="C37" s="242"/>
+      <c r="E37" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="238"/>
+      <c r="F37" s="242"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33244,7 +33483,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.4499302163293791E-2</v>
+        <v>3.4950512548603749E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33260,7 +33499,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.1589097768811703E-2</v>
+        <v>2.1871457831535646E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33276,7 +33515,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2212142358688069E-3</v>
+        <v>1.2371862849063274E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33292,7 +33531,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>9.9712847189624542E-3</v>
+        <v>1.0101697421189959E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33301,18 +33540,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1192751323964526E-2</v>
+        <v>1.1339139375921646E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="238" t="s">
+      <c r="B45" s="242" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="238"/>
-      <c r="E45" s="238" t="s">
+      <c r="C45" s="242"/>
+      <c r="E45" s="242" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="238"/>
+      <c r="F45" s="242"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33345,18 +33584,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.1915969154435057E-2</v>
+        <v>1.207181604687553E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="238" t="s">
+      <c r="B51" s="242" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="238"/>
-      <c r="E51" s="238" t="s">
+      <c r="C51" s="242"/>
+      <c r="E51" s="242" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="238"/>
+      <c r="F51" s="242"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33525,7 +33764,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>229.28</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33554,7 +33793,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5547429.5999999996</v>
+        <v>5475812.3999999994</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33583,7 +33822,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5481326.5999999996</v>
+        <v>5409709.3999999994</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33612,7 +33851,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.986093552465235</v>
+        <v>28.611883691529709</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33641,7 +33880,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.463658394093123</v>
+        <v>18.225292950763937</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33670,7 +33909,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>24.13115326835063</v>
+        <v>23.819620584844358</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33699,7 +33938,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>18.092037799246786</v>
+        <v>17.855653218646129</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33728,7 +33967,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.742455422894132</v>
+        <v>27.379981678214786</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34501,7 +34740,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.4499302163293791E-2</v>
+        <v>3.4950512548603749E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34530,7 +34769,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.1589097768811703E-2</v>
+        <v>2.1871457831535646E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34559,7 +34798,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2212142358688069E-3</v>
+        <v>1.2371862849063274E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34588,7 +34827,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>9.9712847189624542E-3</v>
+        <v>1.0101697421189959E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34617,7 +34856,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1192751323964526E-2</v>
+        <v>1.1339139375921646E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34853,7 +35092,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.1915969154435057E-2</v>
+        <v>1.207181604687553E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35365,14 +35604,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35439,19 +35678,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="246">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35478,19 +35717,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="246">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35517,19 +35756,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="246">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35556,19 +35795,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="246">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35595,19 +35834,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="246">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35634,19 +35873,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="246">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35673,22 +35912,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35715,22 +35954,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35778,22 +36017,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -35820,22 +36059,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35862,22 +36101,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="247"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35904,43 +36143,25 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="246">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="247"/>
+      <c r="F31" s="246">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35949,6 +36170,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812D1582-2025-2842-81ED-B651809E5BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DB43AB-EEED-BE47-8146-BA3E9EB55EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -12757,11 +12757,11 @@
     <v>Powered by Refinitiv</v>
     <v>243.37</v>
     <v>164.27</v>
-    <v>2.1823000000000001</v>
-    <v>-2.96</v>
-    <v>-1.291E-2</v>
-    <v>-8.1199999999999994E-2</v>
-    <v>-3.5880000000000005E-4</v>
+    <v>2.1894</v>
+    <v>-4.07</v>
+    <v>-1.8391000000000001E-2</v>
+    <v>0.19</v>
+    <v>8.7460000000000001E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12769,25 +12769,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>228.86</v>
+    <v>218.4692</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46307.862072546093</v>
+    <v>46310.906180010934</v>
     <v>0</v>
-    <v>224.9</v>
-    <v>5454312000000</v>
+    <v>212.85</v>
+    <v>5235243000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>228.73</v>
-    <v>28.609400000000001</v>
-    <v>229.28</v>
-    <v>226.32</v>
-    <v>226.2388</v>
+    <v>215.3</v>
+    <v>27.4603</v>
+    <v>221.3</v>
+    <v>217.23</v>
+    <v>217.42</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>69740922</v>
-    <v>108532316</v>
+    <v>126632343</v>
+    <v>105819669</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12811,17 +12811,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-5.1749999999999999E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>53.29</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.34</v>
+    <v>51.77</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.96</v>
+    <v>52.17</v>
+    <v>51.9</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5475812.3999999994</v>
+        <v>5255879.8499999996</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5409709.3999999994</v>
+        <v>5189776.8499999996</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>226.32</v>
+        <v>217.23</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="I5" s="208">
         <f>'AVG target price'!C7</f>
-        <v>367.96964961579448</v>
+        <v>372.92428626108091</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>421</v>
@@ -13721,14 +13721,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>226.2388</v>
+        <v>217.42</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>28.611883691529709</v>
+        <v>27.46270543615676</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13748,14 +13748,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.96</v>
+        <v>-4.07</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>18.225292950763937</v>
+        <v>17.493285558918569</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13772,14 +13772,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-8.1199999999999994E-2</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.1871457831535646E-2</v>
+        <v>2.2786670056774608E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13787,7 +13787,7 @@
       </c>
       <c r="I8" s="209">
         <f>'AVG target price'!C10</f>
-        <v>374.84200231374206</v>
+        <v>375.83292964279934</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13796,14 +13796,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.291E-2</v>
+        <v>-1.8391000000000001E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.4950512548603749E-2</v>
+        <v>3.6413018459697098E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.65624780096209823</v>
+        <v>0.73011522185149091</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13820,14 +13820,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.5880000000000005E-4</v>
+        <v>8.7460000000000001E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.0101697421189959E-2</v>
+        <v>1.0524403445029286E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13843,14 +13843,14 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.2371862849063274E-3</v>
+        <v>1.2889564056529947E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
       </c>
       <c r="I11" s="209">
         <f>DDM!C26</f>
-        <v>1.6326530612244898</v>
+        <v>1.6842105263157894</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1823000000000001</v>
+        <v>2.1894</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>108532316</v>
+        <v>105819669</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.207181604687553E-2</v>
+        <v>1.2576961781194447E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="I18" s="236">
         <f>Multiples!C54</f>
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14072,7 +14072,7 @@
         <v>387</v>
       </c>
       <c r="C29" s="218">
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>226.32</v>
+        <v>217.23</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5475812.3999999994</v>
+        <v>5255879.8499999996</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.1823000000000001</v>
+        <v>2.1894</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.038396549230449E-3</v>
+        <v>6.2894843408411588E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99396160345076956</v>
+        <v>0.9937105156591588</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19529,7 +19529,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15064349999999999</v>
+        <v>0.150423</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19538,7 +19538,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14997237147313058</v>
+        <v>0.14972535152846089</v>
       </c>
     </row>
   </sheetData>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C54" s="136">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C58" s="234">
         <f>C57/(1+C54)^5</f>
-        <v>367.96964961579448</v>
+        <v>372.92428626108091</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="C7" s="134">
         <f>Multiples!C58</f>
-        <v>367.96964961579448</v>
+        <v>372.92428626108091</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="C10" s="234">
         <f>AVERAGE(C5:C9)</f>
-        <v>374.84200231374206</v>
+        <v>375.83292964279934</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>226.32</v>
+        <v>217.23</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.65624780096209823</v>
+        <v>0.73011522185149091</v>
       </c>
     </row>
   </sheetData>
@@ -22034,7 +22034,7 @@
       </c>
       <c r="C24" s="136">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22051,7 +22051,7 @@
       </c>
       <c r="C26" s="234">
         <f>C23/(C24-C25)</f>
-        <v>1.6326530612244898</v>
+        <v>1.6842105263157894</v>
       </c>
     </row>
   </sheetData>
@@ -22393,7 +22393,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>226.32</v>
+        <v>217.23</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5454312</v>
+        <v>5235243</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22486,7 +22486,7 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5388209</v>
+        <v>5169140</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>226.32</v>
+        <v>217.23</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29225,7 +29225,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>226.32</v>
+        <v>217.23</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30727,7 +30727,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>28.611883691529709</v>
+        <v>27.46270543615676</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30764,7 +30764,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.225292950763937</v>
+        <v>17.493285558918569</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30825,7 +30825,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>23.819620584844358</v>
+        <v>22.862920553401111</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30886,7 +30886,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5475812.3999999994</v>
+        <v>5255879.8499999996</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30947,7 +30947,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5409709.3999999994</v>
+        <v>5189776.8499999996</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30984,7 +30984,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>17.855653218646129</v>
+        <v>17.129728949166417</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31021,7 +31021,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>27.379981678214786</v>
+        <v>26.266844401479911</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31156,7 +31156,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>45.721689322333916</v>
+        <v>43.885306519488324</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31193,7 +31193,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>44.538302715765028</v>
+        <v>42.727591314344807</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31230,7 +31230,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.1871457831535646E-2</v>
+        <v>2.2786670056774608E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31267,7 +31267,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.4950512548603749E-2</v>
+        <v>3.6413018459697098E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31304,7 +31304,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.2371862849063274E-3</v>
+        <v>1.2889564056529947E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31341,7 +31341,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>1.0101697421189959E-2</v>
+        <v>1.0524403445029286E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31378,7 +31378,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1339139375921646E-2</v>
+        <v>1.1813626219024015E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31881,7 +31881,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.207181604687553E-2</v>
+        <v>1.2576961781194447E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -33122,7 +33122,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>226.32</v>
+        <v>217.23</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -33138,7 +33138,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5475812.3999999994</v>
+        <v>5255879.8499999996</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5409709.3999999994</v>
+        <v>5189776.8499999996</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33178,7 +33178,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.611883691529709</v>
+        <v>27.46270543615676</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.225292950763937</v>
+        <v>17.493285558918569</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33218,7 +33218,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>23.819620584844358</v>
+        <v>22.862920553401111</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33238,7 +33238,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.855653218646129</v>
+        <v>17.129728949166417</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33247,7 +33247,7 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.379981678214786</v>
+        <v>26.266844401479911</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33483,7 +33483,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.4950512548603749E-2</v>
+        <v>3.6413018459697098E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33499,7 +33499,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.1871457831535646E-2</v>
+        <v>2.2786670056774608E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33515,7 +33515,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2371862849063274E-3</v>
+        <v>1.2889564056529947E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33531,7 +33531,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0101697421189959E-2</v>
+        <v>1.0524403445029286E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33540,7 +33540,7 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1339139375921646E-2</v>
+        <v>1.1813626219024015E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33584,7 +33584,7 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.207181604687553E-2</v>
+        <v>1.2576961781194447E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33764,7 +33764,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>226.32</v>
+        <v>217.23</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5475812.3999999994</v>
+        <v>5255879.8499999996</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5409709.3999999994</v>
+        <v>5189776.8499999996</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33851,7 +33851,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>28.611883691529709</v>
+        <v>27.46270543615676</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33880,7 +33880,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>18.225292950763937</v>
+        <v>17.493285558918569</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33909,7 +33909,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>23.819620584844358</v>
+        <v>22.862920553401111</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33938,7 +33938,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.855653218646129</v>
+        <v>17.129728949166417</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33967,7 +33967,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>27.379981678214786</v>
+        <v>26.266844401479911</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34740,7 +34740,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.4950512548603749E-2</v>
+        <v>3.6413018459697098E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.1871457831535646E-2</v>
+        <v>2.2786670056774608E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34798,7 +34798,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2371862849063274E-3</v>
+        <v>1.2889564056529947E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34827,7 +34827,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0101697421189959E-2</v>
+        <v>1.0524403445029286E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34856,7 +34856,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1339139375921646E-2</v>
+        <v>1.1813626219024015E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35092,7 +35092,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.207181604687553E-2</v>
+        <v>1.2576961781194447E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DB43AB-EEED-BE47-8146-BA3E9EB55EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07630F35-54A3-5847-A737-45816951F3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,19 +161,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="425">
   <si>
     <t>Ticker</t>
   </si>
@@ -1424,6 +1454,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2069,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2370,6 +2403,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2377,12 +2416,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2403,15 +2436,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12738,7 +12774,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12757,11 +12793,9 @@
     <v>Powered by Refinitiv</v>
     <v>243.37</v>
     <v>164.27</v>
-    <v>2.1894</v>
-    <v>-4.07</v>
-    <v>-1.8391000000000001E-2</v>
-    <v>0.19</v>
-    <v>8.7460000000000001E-4</v>
+    <v>2.1920999999999999</v>
+    <v>-0.02</v>
+    <v>-9.2130000000000001E-5</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12769,35 +12803,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>218.4692</v>
+    <v>218.46</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46310.906180010934</v>
+    <v>46315.72310350625</v>
     <v>0</v>
-    <v>212.85</v>
-    <v>5235243000000</v>
+    <v>212.77</v>
+    <v>5231387000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>215.3</v>
-    <v>27.4603</v>
-    <v>221.3</v>
-    <v>217.23</v>
-    <v>217.42</v>
+    <v>216</v>
+    <v>27.44</v>
+    <v>217.09</v>
+    <v>217.07</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>126632343</v>
-    <v>105819669</v>
+    <v>47336829</v>
+    <v>106616857</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12811,28 +12859,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-0.27</v>
-    <v>-5.1749999999999999E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>53.29</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>51.77</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.96</v>
-    <v>52.17</v>
-    <v>51.9</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12854,8 +12902,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12876,7 +12922,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12886,6 +12931,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12921,7 +12971,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12932,16 +12982,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13035,19 +13082,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13119,9 +13160,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13129,9 +13167,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13609,7 +13644,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -13647,7 +13682,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5255879.8499999996</v>
+        <v>5252008.6499999994</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13674,7 +13709,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5189776.8499999996</v>
+        <v>5185905.6499999994</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13694,7 +13729,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>217.23</v>
+        <v>217.07</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13719,16 +13754,16 @@
       <c r="B6" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="205" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>217.42</v>
+      <c r="C6" s="205" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>27.46270543615676</v>
+        <v>27.442477876106192</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13748,14 +13783,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.07</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>17.493285558918569</v>
+        <v>17.480400940360234</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13770,16 +13805,16 @@
       <c r="B8" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.19</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.2786670056774608E-2</v>
+        <v>2.2803465870148559E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13796,14 +13831,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.8391000000000001E-2</v>
+        <v>-9.2130000000000001E-5</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.6413018459697098E-2</v>
+        <v>3.6439858110287007E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13811,23 +13846,23 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.73011522185149091</v>
+        <v>0.73139047147371516</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>8.7460000000000001E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.0524403445029286E-2</v>
+        <v>1.0532160871441064E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13843,7 +13878,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.2889564056529947E-3</v>
+        <v>1.2899064817800711E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
@@ -13875,7 +13910,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1894</v>
+        <v>2.1920999999999999</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13884,10 +13919,10 @@
         <f>Statement!AC123</f>
         <v>0.84232522796352571</v>
       </c>
-      <c r="H13" s="181" t="s">
+      <c r="H13" s="259" t="s">
         <v>415</v>
       </c>
-      <c r="I13" s="210">
+      <c r="I13" s="257">
         <f>'Reverse DCF'!C17</f>
         <v>0.5</v>
       </c>
@@ -13898,7 +13933,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>105819669</v>
+        <v>106616857</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13907,6 +13942,13 @@
         <f>Statement!AC142</f>
         <v>1.0183873919662139</v>
       </c>
+      <c r="H14" s="183" t="s">
+        <v>424</v>
+      </c>
+      <c r="I14" s="258">
+        <f>'Reverse DCF'!C16</f>
+        <v>228.84689448777979</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="182" t="s">
@@ -13914,7 +13956,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.2576961781194447E-2</v>
+        <v>1.258623212663597E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14036,12 +14078,12 @@
       <c r="C26" s="167">
         <v>0.21</v>
       </c>
-      <c r="E26" s="182" t="e" vm="2">
+      <c r="E26" s="182" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.9</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14056,7 +14098,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18220,6 +18262,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18227,12 +18275,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19292,16 +19334,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19423,7 +19465,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>217.23</v>
+        <v>217.07</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19432,7 +19474,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5255879.8499999996</v>
+        <v>5252008.6499999994</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19450,7 +19492,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19459,7 +19501,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.1894</v>
+        <v>2.1920999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19502,7 +19544,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.2894843408411588E-3</v>
+        <v>6.2940910743399126E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19511,7 +19553,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9937105156591588</v>
+        <v>0.99370590892566013</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19529,7 +19571,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.150423</v>
+        <v>0.15000449999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19538,7 +19580,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14972535152846089</v>
+        <v>0.14930897461287559</v>
       </c>
     </row>
   </sheetData>
@@ -21402,17 +21444,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21516,7 +21558,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>217.23</v>
+        <v>217.07</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21525,7 +21567,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.73011522185149091</v>
+        <v>0.73139047147371516</v>
       </c>
     </row>
   </sheetData>
@@ -22382,10 +22424,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="254" t="s">
+      <c r="B14" s="255" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="255"/>
+      <c r="C14" s="256"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22393,7 +22435,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>217.23</v>
+        <v>217.07</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22412,20 +22454,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="256" t="s">
+      <c r="E17" s="254" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="256"/>
-      <c r="G17" s="256"/>
-      <c r="H17" s="256"/>
-      <c r="I17" s="256"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="254" t="s">
+      <c r="B19" s="255" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="255"/>
+      <c r="C19" s="256"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22459,7 +22501,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5235243</v>
+        <v>5231387</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22486,15 +22528,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5169140</v>
+        <v>5165284</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="255" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="255"/>
+      <c r="C28" s="256"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22570,16 +22612,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29154,7 +29196,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>217.23</v>
+        <v>217.07</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29225,7 +29267,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>217.23</v>
+        <v>217.07</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30727,7 +30769,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>27.46270543615676</v>
+        <v>27.442477876106192</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30764,7 +30806,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>17.493285558918569</v>
+        <v>17.480400940360234</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30825,7 +30867,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>22.862920553401111</v>
+        <v>22.846080948887259</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30886,7 +30928,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5255879.8499999996</v>
+        <v>5252008.6499999994</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30947,7 +30989,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5189776.8499999996</v>
+        <v>5185905.6499999994</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30984,7 +31026,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>17.129728949166417</v>
+        <v>17.116951404269081</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31021,7 +31063,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>26.266844401479911</v>
+        <v>26.247251226091841</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31156,7 +31198,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>43.885306519488324</v>
+        <v>43.852982949801273</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31193,7 +31235,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>42.727591314344807</v>
+        <v>42.695719606509023</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31230,7 +31272,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.2786670056774608E-2</v>
+        <v>2.2803465870148559E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31267,7 +31309,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.6413018459697098E-2</v>
+        <v>3.6439858110287007E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31304,7 +31346,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.2889564056529947E-3</v>
+        <v>1.2899064817800711E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31341,7 +31383,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>1.0524403445029286E-2</v>
+        <v>1.0532160871441064E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31378,7 +31420,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1813626219024015E-2</v>
+        <v>1.1822333917900156E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31881,7 +31923,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.2576961781194447E-2</v>
+        <v>1.258623212663597E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -33122,7 +33164,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>217.23</v>
+        <v>217.07</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -33138,7 +33180,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5255879.8499999996</v>
+        <v>5252008.6499999994</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33158,7 +33200,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5189776.8499999996</v>
+        <v>5185905.6499999994</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33178,7 +33220,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>27.46270543615676</v>
+        <v>27.442477876106192</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33198,7 +33240,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>17.493285558918569</v>
+        <v>17.480400940360234</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33218,7 +33260,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>22.862920553401111</v>
+        <v>22.846080948887259</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33238,7 +33280,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.129728949166417</v>
+        <v>17.116951404269081</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33247,7 +33289,7 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>26.266844401479911</v>
+        <v>26.247251226091841</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33483,7 +33525,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.6413018459697098E-2</v>
+        <v>3.6439858110287007E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33499,7 +33541,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.2786670056774608E-2</v>
+        <v>2.2803465870148559E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33515,7 +33557,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2889564056529947E-3</v>
+        <v>1.2899064817800711E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33531,7 +33573,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0524403445029286E-2</v>
+        <v>1.0532160871441064E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33540,7 +33582,7 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1813626219024015E-2</v>
+        <v>1.1822333917900156E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33584,7 +33626,7 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.2576961781194447E-2</v>
+        <v>1.258623212663597E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33764,7 +33806,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>217.23</v>
+        <v>217.07</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33793,7 +33835,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5255879.8499999996</v>
+        <v>5252008.6499999994</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33822,7 +33864,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5189776.8499999996</v>
+        <v>5185905.6499999994</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33851,7 +33893,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>27.46270543615676</v>
+        <v>27.442477876106192</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33880,7 +33922,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>17.493285558918569</v>
+        <v>17.480400940360234</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33909,7 +33951,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>22.862920553401111</v>
+        <v>22.846080948887259</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33938,7 +33980,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.129728949166417</v>
+        <v>17.116951404269081</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33967,7 +34009,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>26.266844401479911</v>
+        <v>26.247251226091841</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34740,7 +34782,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.6413018459697098E-2</v>
+        <v>3.6439858110287007E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34769,7 +34811,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.2786670056774608E-2</v>
+        <v>2.2803465870148559E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34798,7 +34840,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2889564056529947E-3</v>
+        <v>1.2899064817800711E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34827,7 +34869,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0524403445029286E-2</v>
+        <v>1.0532160871441064E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34856,7 +34898,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1813626219024015E-2</v>
+        <v>1.1822333917900156E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35092,7 +35134,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.2576961781194447E-2</v>
+        <v>1.258623212663597E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35604,14 +35646,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="245" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="246"/>
+      <c r="F3" s="247" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="246"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35678,19 +35720,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="243">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="244"/>
+      <c r="F7" s="243">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="244"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35717,19 +35759,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="243">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="244"/>
+      <c r="F9" s="243">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="244"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35756,19 +35798,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="243">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="244"/>
+      <c r="F11" s="243">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="244"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35795,19 +35837,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="243">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="244"/>
+      <c r="F13" s="243">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="244"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35834,19 +35876,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="243">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="244"/>
+      <c r="F15" s="243">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="244"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35873,19 +35915,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="243">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="244"/>
+      <c r="F17" s="243">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="244"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35912,22 +35954,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="243">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="244"/>
+      <c r="F19" s="243">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="244"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35954,22 +35996,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="243">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="244"/>
+      <c r="F21" s="243">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="244"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36017,22 +36059,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="243">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="244"/>
+      <c r="F25" s="243">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="244"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -36059,22 +36101,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="243">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="244"/>
+      <c r="F27" s="243">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="244"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36101,22 +36143,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="246">
+      <c r="C29" s="243">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="247"/>
-      <c r="F29" s="246">
+      <c r="D29" s="244"/>
+      <c r="F29" s="243">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="247"/>
+      <c r="G29" s="244"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36143,25 +36185,43 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="246">
+      <c r="C31" s="243">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="247"/>
-      <c r="F31" s="246">
+      <c r="D31" s="244"/>
+      <c r="F31" s="243">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="247"/>
+      <c r="G31" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -36170,24 +36230,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07630F35-54A3-5847-A737-45816951F3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E67464-8BDE-5E4E-A37E-2366D603D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2391,6 +2361,9 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2445,9 +2418,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12774,7 +12744,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12793,9 +12763,11 @@
     <v>Powered by Refinitiv</v>
     <v>243.37</v>
     <v>164.27</v>
-    <v>2.1920999999999999</v>
-    <v>-0.02</v>
-    <v>-9.2130000000000001E-5</v>
+    <v>2.1957</v>
+    <v>-1.25</v>
+    <v>-5.8899999999999994E-3</v>
+    <v>0.1555</v>
+    <v>7.3709999999999997E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12803,49 +12775,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>218.46</v>
+    <v>213.85</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46315.72310350625</v>
+    <v>46318.955257638285</v>
     <v>0</v>
-    <v>212.77</v>
-    <v>5231387000000</v>
+    <v>210.18</v>
+    <v>5084136000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>216</v>
-    <v>27.44</v>
-    <v>217.09</v>
-    <v>217.07</v>
+    <v>210.99</v>
+    <v>26.825600000000001</v>
+    <v>212.21</v>
+    <v>210.96</v>
+    <v>211.1155</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>47336829</v>
-    <v>106616857</v>
+    <v>80064334</v>
+    <v>107148374</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12859,28 +12817,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>6</v>
-    <v>50.9</v>
+    <v>3</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12902,6 +12860,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12922,6 +12882,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12931,11 +12892,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12971,7 +12927,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12982,13 +12938,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13082,13 +13041,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13160,6 +13125,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13167,6 +13135,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13653,18 +13624,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="239" t="s">
+      <c r="B2" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="240"/>
-      <c r="E2" s="239" t="s">
+      <c r="C2" s="243"/>
+      <c r="E2" s="242" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="240"/>
-      <c r="H2" s="239" t="s">
+      <c r="F2" s="243"/>
+      <c r="H2" s="242" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="240"/>
+      <c r="I2" s="243"/>
       <c r="K2" s="133" t="s">
         <v>418</v>
       </c>
@@ -13682,7 +13653,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5252008.6499999994</v>
+        <v>5104177.2</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13709,7 +13680,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5185905.6499999994</v>
+        <v>5038074.2</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13729,7 +13700,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>217.07</v>
+        <v>210.96</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13754,16 +13725,16 @@
       <c r="B6" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="205" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="205" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>211.1155</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>27.442477876106192</v>
+        <v>26.670037926675096</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13783,14 +13754,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.02</v>
+        <v>-1.25</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>17.480400940360234</v>
+        <v>16.98836956916384</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13805,16 +13776,16 @@
       <c r="B8" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.1555</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.2803465870148559E-2</v>
+        <v>2.3463918925071801E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13831,14 +13802,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-9.2130000000000001E-5</v>
+        <v>-5.8899999999999994E-3</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.6439858110287007E-2</v>
+        <v>3.7495259764884339E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13846,23 +13817,23 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.73139047147371516</v>
+        <v>0.78153645071482425</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>7.3709999999999997E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.0532160871441064E-2</v>
+        <v>1.083720212534941E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13878,7 +13849,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.2899064817800711E-3</v>
+        <v>1.3272658323852863E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
@@ -13910,7 +13881,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1920999999999999</v>
+        <v>2.1957</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13919,10 +13890,10 @@
         <f>Statement!AC123</f>
         <v>0.84232522796352571</v>
       </c>
-      <c r="H13" s="259" t="s">
+      <c r="H13" s="241" t="s">
         <v>415</v>
       </c>
-      <c r="I13" s="257">
+      <c r="I13" s="239">
         <f>'Reverse DCF'!C17</f>
         <v>0.5</v>
       </c>
@@ -13933,7 +13904,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>106616857</v>
+        <v>107148374</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13945,7 +13916,7 @@
       <c r="H14" s="183" t="s">
         <v>424</v>
       </c>
-      <c r="I14" s="258">
+      <c r="I14" s="240">
         <f>'Reverse DCF'!C16</f>
         <v>228.84689448777979</v>
       </c>
@@ -13956,7 +13927,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.258623212663597E-2</v>
+        <v>1.2950765110584326E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13967,16 +13938,16 @@
         <f>Statement!AC177</f>
         <v>2.742863070539419</v>
       </c>
-      <c r="H16" s="239" t="s">
+      <c r="H16" s="242" t="s">
         <v>416</v>
       </c>
-      <c r="I16" s="240"/>
+      <c r="I16" s="243"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="241" t="s">
+      <c r="B17" s="244" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="241"/>
+      <c r="C17" s="244"/>
       <c r="E17" s="181" t="s">
         <v>288</v>
       </c>
@@ -14062,14 +14033,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="241" t="s">
+      <c r="B25" s="244" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="241"/>
-      <c r="E25" s="239" t="s">
+      <c r="C25" s="244"/>
+      <c r="E25" s="242" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="240"/>
+      <c r="F25" s="243"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -14078,12 +14049,12 @@
       <c r="C26" s="167">
         <v>0.21</v>
       </c>
-      <c r="E26" s="182" t="e" vm="5">
+      <c r="E26" s="182" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14098,7 +14069,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14372,36 +14343,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
+      <c r="AA2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="245"/>
+      <c r="AC2" s="245"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14412,32 +14383,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="249" t="s">
+      <c r="S4" s="252" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
-      <c r="AA4" s="250"/>
-      <c r="AB4" s="250"/>
-      <c r="AC4" s="250"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15022,33 +14993,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="248" t="s">
+      <c r="C12" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="248"/>
-      <c r="L12" s="248"/>
+      <c r="D12" s="251"/>
+      <c r="E12" s="251"/>
+      <c r="F12" s="251"/>
+      <c r="G12" s="251"/>
+      <c r="H12" s="251"/>
+      <c r="I12" s="251"/>
+      <c r="J12" s="251"/>
+      <c r="K12" s="251"/>
+      <c r="L12" s="251"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="249" t="s">
+      <c r="S12" s="252" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="250"/>
-      <c r="U12" s="250"/>
-      <c r="V12" s="250"/>
-      <c r="W12" s="250"/>
-      <c r="X12" s="250"/>
-      <c r="Y12" s="250"/>
-      <c r="Z12" s="250"/>
-      <c r="AA12" s="250"/>
-      <c r="AB12" s="250"/>
-      <c r="AC12" s="250"/>
+      <c r="T12" s="253"/>
+      <c r="U12" s="253"/>
+      <c r="V12" s="253"/>
+      <c r="W12" s="253"/>
+      <c r="X12" s="253"/>
+      <c r="Y12" s="253"/>
+      <c r="Z12" s="253"/>
+      <c r="AA12" s="253"/>
+      <c r="AB12" s="253"/>
+      <c r="AC12" s="253"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -15597,35 +15568,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="P2" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="245"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15634,31 +15605,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="P4" s="250" t="s">
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="P4" s="253" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="250"/>
-      <c r="R4" s="250"/>
-      <c r="S4" s="250"/>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
+      <c r="Q4" s="253"/>
+      <c r="R4" s="253"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15853,32 +15824,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="251" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="250" t="s">
+      <c r="P9" s="253" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="250"/>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
+      <c r="T9" s="253"/>
+      <c r="U9" s="253"/>
+      <c r="V9" s="253"/>
+      <c r="W9" s="253"/>
+      <c r="X9" s="253"/>
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16354,31 +16325,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="248" t="s">
+      <c r="C17" s="251" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
-      <c r="P17" s="250" t="s">
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
+      <c r="P17" s="253" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="250"/>
-      <c r="R17" s="250"/>
-      <c r="S17" s="250"/>
-      <c r="T17" s="250"/>
-      <c r="U17" s="250"/>
-      <c r="V17" s="250"/>
-      <c r="W17" s="250"/>
-      <c r="X17" s="250"/>
-      <c r="Y17" s="250"/>
-      <c r="Z17" s="250"/>
+      <c r="Q17" s="253"/>
+      <c r="R17" s="253"/>
+      <c r="S17" s="253"/>
+      <c r="T17" s="253"/>
+      <c r="U17" s="253"/>
+      <c r="V17" s="253"/>
+      <c r="W17" s="253"/>
+      <c r="X17" s="253"/>
+      <c r="Y17" s="253"/>
+      <c r="Z17" s="253"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16856,60 +16827,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17095,30 +17066,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="251" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="253"/>
-      <c r="Q11" s="253"/>
-      <c r="R11" s="253"/>
-      <c r="S11" s="253"/>
-      <c r="T11" s="253"/>
-      <c r="U11" s="253"/>
-      <c r="V11" s="253"/>
-      <c r="W11" s="253"/>
-      <c r="X11" s="253"/>
-      <c r="Y11" s="253"/>
-      <c r="Z11" s="253"/>
+      <c r="P11" s="256"/>
+      <c r="Q11" s="256"/>
+      <c r="R11" s="256"/>
+      <c r="S11" s="256"/>
+      <c r="T11" s="256"/>
+      <c r="U11" s="256"/>
+      <c r="V11" s="256"/>
+      <c r="W11" s="256"/>
+      <c r="X11" s="256"/>
+      <c r="Y11" s="256"/>
+      <c r="Z11" s="256"/>
       <c r="AB11" s="111"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17360,18 +17331,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="251" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17584,23 +17555,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="253"/>
-      <c r="C25" s="253"/>
+      <c r="B25" s="256"/>
+      <c r="C25" s="256"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="248" t="s">
+      <c r="C26" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="248"/>
-      <c r="G26" s="248"/>
-      <c r="H26" s="248"/>
-      <c r="I26" s="248"/>
-      <c r="J26" s="248"/>
-      <c r="K26" s="248"/>
-      <c r="L26" s="248"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17792,18 +17763,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="248" t="s">
+      <c r="C33" s="251" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="248"/>
-      <c r="H33" s="248"/>
-      <c r="I33" s="248"/>
-      <c r="J33" s="248"/>
-      <c r="K33" s="248"/>
-      <c r="L33" s="248"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
+      <c r="I33" s="251"/>
+      <c r="J33" s="251"/>
+      <c r="K33" s="251"/>
+      <c r="L33" s="251"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17987,18 +17958,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="248" t="s">
+      <c r="C40" s="251" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="248"/>
-      <c r="E40" s="248"/>
-      <c r="F40" s="248"/>
-      <c r="G40" s="248"/>
-      <c r="H40" s="248"/>
-      <c r="I40" s="248"/>
-      <c r="J40" s="248"/>
-      <c r="K40" s="248"/>
-      <c r="L40" s="248"/>
+      <c r="D40" s="251"/>
+      <c r="E40" s="251"/>
+      <c r="F40" s="251"/>
+      <c r="G40" s="251"/>
+      <c r="H40" s="251"/>
+      <c r="I40" s="251"/>
+      <c r="J40" s="251"/>
+      <c r="K40" s="251"/>
+      <c r="L40" s="251"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18312,60 +18283,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
-      <c r="AA2" s="253"/>
-      <c r="AB2" s="253"/>
-      <c r="AC2" s="253"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256"/>
+      <c r="AB2" s="256"/>
+      <c r="AC2" s="256"/>
       <c r="AE2" s="110"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="S4" s="256"/>
+      <c r="T4" s="256"/>
+      <c r="U4" s="256"/>
+      <c r="V4" s="256"/>
+      <c r="W4" s="256"/>
+      <c r="X4" s="256"/>
+      <c r="Y4" s="256"/>
+      <c r="Z4" s="256"/>
+      <c r="AA4" s="256"/>
+      <c r="AB4" s="256"/>
+      <c r="AC4" s="256"/>
       <c r="AE4" s="111"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18728,18 +18699,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="248" t="s">
+      <c r="C13" s="251" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="248"/>
-      <c r="J13" s="248"/>
-      <c r="K13" s="248"/>
-      <c r="L13" s="248"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="251"/>
+      <c r="K13" s="251"/>
+      <c r="L13" s="251"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18832,18 +18803,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="251" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19035,18 +19006,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="248" t="s">
+      <c r="C25" s="251" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="248"/>
-      <c r="I25" s="248"/>
-      <c r="J25" s="248"/>
-      <c r="K25" s="248"/>
-      <c r="L25" s="248"/>
+      <c r="D25" s="251"/>
+      <c r="E25" s="251"/>
+      <c r="F25" s="251"/>
+      <c r="G25" s="251"/>
+      <c r="H25" s="251"/>
+      <c r="I25" s="251"/>
+      <c r="J25" s="251"/>
+      <c r="K25" s="251"/>
+      <c r="L25" s="251"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19184,18 +19155,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="248" t="s">
+      <c r="C31" s="251" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="251"/>
+      <c r="G31" s="251"/>
+      <c r="H31" s="251"/>
+      <c r="I31" s="251"/>
+      <c r="J31" s="251"/>
+      <c r="K31" s="251"/>
+      <c r="L31" s="251"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19445,10 +19416,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="245"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19465,7 +19436,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>217.07</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19474,7 +19445,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5252008.6499999994</v>
+        <v>5104177.2</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19492,7 +19463,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19501,7 +19472,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.1920999999999999</v>
+        <v>2.1957</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19533,10 +19504,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="245" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="245"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19544,7 +19515,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.2940910743399126E-3</v>
+        <v>6.4752054095702704E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19553,7 +19524,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99370590892566013</v>
+        <v>0.99352479459042975</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19571,7 +19542,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15000449999999999</v>
+        <v>0.14833649999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19580,7 +19551,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14930897461287559</v>
+        <v>0.14763176130644129</v>
       </c>
     </row>
   </sheetData>
@@ -19625,60 +19596,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19924,10 +19895,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="245" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="245"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19947,10 +19918,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="245"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20064,37 +20035,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20314,18 +20285,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20519,18 +20490,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="248" t="s">
+      <c r="C17" s="251" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20664,18 +20635,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="248" t="s">
+      <c r="C22" s="251" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
-      <c r="J22" s="248"/>
-      <c r="K22" s="248"/>
-      <c r="L22" s="248"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="251"/>
+      <c r="F22" s="251"/>
+      <c r="G22" s="251"/>
+      <c r="H22" s="251"/>
+      <c r="I22" s="251"/>
+      <c r="J22" s="251"/>
+      <c r="K22" s="251"/>
+      <c r="L22" s="251"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20759,18 +20730,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="248" t="s">
+      <c r="C27" s="251" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="E27" s="248"/>
-      <c r="F27" s="248"/>
-      <c r="G27" s="248"/>
-      <c r="H27" s="248"/>
-      <c r="I27" s="248"/>
-      <c r="J27" s="248"/>
-      <c r="K27" s="248"/>
-      <c r="L27" s="248"/>
+      <c r="D27" s="251"/>
+      <c r="E27" s="251"/>
+      <c r="F27" s="251"/>
+      <c r="G27" s="251"/>
+      <c r="H27" s="251"/>
+      <c r="I27" s="251"/>
+      <c r="J27" s="251"/>
+      <c r="K27" s="251"/>
+      <c r="L27" s="251"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21071,10 +21042,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="242" t="s">
+      <c r="B39" s="245" t="s">
         <v>197</v>
       </c>
-      <c r="C39" s="242"/>
+      <c r="C39" s="245"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21176,10 +21147,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="245" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="242"/>
+      <c r="C52" s="245"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21235,10 +21206,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="242" t="s">
+      <c r="B60" s="245" t="s">
         <v>314</v>
       </c>
-      <c r="C60" s="242"/>
+      <c r="C60" s="245"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21339,10 +21310,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="242" t="s">
+      <c r="B73" s="245" t="s">
         <v>411</v>
       </c>
-      <c r="C73" s="242"/>
+      <c r="C73" s="245"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21492,10 +21463,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="245"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21558,7 +21529,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>217.07</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21567,7 +21538,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.73139047147371516</v>
+        <v>0.78153645071482425</v>
       </c>
     </row>
   </sheetData>
@@ -21662,37 +21633,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21805,18 +21776,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="251" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21937,18 +21908,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="248" t="s">
+      <c r="C14" s="251" t="s">
         <v>390</v>
       </c>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="248"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="248"/>
-      <c r="I14" s="248"/>
-      <c r="J14" s="248"/>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="251"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="251"/>
+      <c r="J14" s="251"/>
+      <c r="K14" s="251"/>
+      <c r="L14" s="251"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22038,10 +22009,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="242" t="s">
+      <c r="B20" s="245" t="s">
         <v>392</v>
       </c>
-      <c r="C20" s="242"/>
+      <c r="C20" s="245"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22142,60 +22113,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22424,10 +22395,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="258" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="256"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22435,7 +22406,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>217.07</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22454,20 +22425,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="254" t="s">
+      <c r="E17" s="257" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="254"/>
-      <c r="G17" s="254"/>
-      <c r="H17" s="254"/>
-      <c r="I17" s="254"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="258" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="256"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22501,7 +22472,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5231387</v>
+        <v>5084136</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22528,15 +22499,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5165284</v>
+        <v>5018033</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="255" t="s">
+      <c r="B28" s="258" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="256"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -29196,7 +29167,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>217.07</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29267,7 +29238,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>217.07</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30769,7 +30740,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>27.442477876106192</v>
+        <v>26.670037926675096</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30806,7 +30777,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>17.480400940360234</v>
+        <v>16.98836956916384</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30867,7 +30838,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>22.846080948887259</v>
+        <v>22.203018551514518</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30928,7 +30899,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5252008.6499999994</v>
+        <v>5104177.2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30989,7 +30960,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5185905.6499999994</v>
+        <v>5038074.2</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31026,7 +30997,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>17.116951404269081</v>
+        <v>16.62900890850219</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31063,7 +31034,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>26.247251226091841</v>
+        <v>25.499036840959821</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31198,7 +31169,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>43.852982949801273</v>
+        <v>42.618626632377008</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31235,7 +31206,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>42.695719606509023</v>
+        <v>41.478618763530207</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31272,7 +31243,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.2803465870148559E-2</v>
+        <v>2.3463918925071801E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31309,7 +31280,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.6439858110287007E-2</v>
+        <v>3.7495259764884339E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31346,7 +31317,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.2899064817800711E-3</v>
+        <v>1.3272658323852863E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31383,7 +31354,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>1.0532160871441064E-2</v>
+        <v>1.083720212534941E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31420,7 +31391,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1822333917900156E-2</v>
+        <v>1.2164742242882947E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31923,7 +31894,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.258623212663597E-2</v>
+        <v>1.2950765110584326E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -33148,15 +33119,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="242"/>
-      <c r="E4" s="242" t="s">
+      <c r="C4" s="245"/>
+      <c r="E4" s="245" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33164,7 +33135,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>217.07</v>
+        <v>210.96</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -33180,7 +33151,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5252008.6499999994</v>
+        <v>5104177.2</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33200,7 +33171,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5185905.6499999994</v>
+        <v>5038074.2</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33220,7 +33191,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>27.442477876106192</v>
+        <v>26.670037926675096</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33240,7 +33211,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>17.480400940360234</v>
+        <v>16.98836956916384</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33260,7 +33231,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>22.846080948887259</v>
+        <v>22.203018551514518</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33280,7 +33251,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.116951404269081</v>
+        <v>16.62900890850219</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33289,18 +33260,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>26.247251226091841</v>
+        <v>25.499036840959821</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="245" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="242"/>
-      <c r="E15" s="242" t="s">
+      <c r="C15" s="245"/>
+      <c r="E15" s="245" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="242"/>
+      <c r="F15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33351,14 +33322,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="242" t="s">
+      <c r="B21" s="245" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="242"/>
-      <c r="E21" s="242" t="s">
+      <c r="C21" s="245"/>
+      <c r="E21" s="245" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="242"/>
+      <c r="F21" s="245"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33427,14 +33398,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="242" t="s">
+      <c r="B29" s="245" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="242"/>
-      <c r="E29" s="242" t="s">
+      <c r="C29" s="245"/>
+      <c r="E29" s="245" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="242"/>
+      <c r="F29" s="245"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33510,14 +33481,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="245" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="242"/>
-      <c r="E37" s="242" t="s">
+      <c r="C37" s="245"/>
+      <c r="E37" s="245" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="242"/>
+      <c r="F37" s="245"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33525,7 +33496,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.6439858110287007E-2</v>
+        <v>3.7495259764884339E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33541,7 +33512,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.2803465870148559E-2</v>
+        <v>2.3463918925071801E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33557,7 +33528,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2899064817800711E-3</v>
+        <v>1.3272658323852863E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33573,7 +33544,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0532160871441064E-2</v>
+        <v>1.083720212534941E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33582,18 +33553,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1822333917900156E-2</v>
+        <v>1.2164742242882947E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="242" t="s">
+      <c r="B45" s="245" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="242"/>
-      <c r="E45" s="242" t="s">
+      <c r="C45" s="245"/>
+      <c r="E45" s="245" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="242"/>
+      <c r="F45" s="245"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33626,18 +33597,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.258623212663597E-2</v>
+        <v>1.2950765110584326E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="242" t="s">
+      <c r="B51" s="245" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="242"/>
-      <c r="E51" s="242" t="s">
+      <c r="C51" s="245"/>
+      <c r="E51" s="245" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="242"/>
+      <c r="F51" s="245"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33806,7 +33777,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>217.07</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33835,7 +33806,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5252008.6499999994</v>
+        <v>5104177.2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33864,7 +33835,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5185905.6499999994</v>
+        <v>5038074.2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33893,7 +33864,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>27.442477876106192</v>
+        <v>26.670037926675096</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33922,7 +33893,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>17.480400940360234</v>
+        <v>16.98836956916384</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33951,7 +33922,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>22.846080948887259</v>
+        <v>22.203018551514518</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33980,7 +33951,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.116951404269081</v>
+        <v>16.62900890850219</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34009,7 +33980,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>26.247251226091841</v>
+        <v>25.499036840959821</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34782,7 +34753,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.6439858110287007E-2</v>
+        <v>3.7495259764884339E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34811,7 +34782,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.2803465870148559E-2</v>
+        <v>2.3463918925071801E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34840,7 +34811,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2899064817800711E-3</v>
+        <v>1.3272658323852863E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34869,7 +34840,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0532160871441064E-2</v>
+        <v>1.083720212534941E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34898,7 +34869,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1822333917900156E-2</v>
+        <v>1.2164742242882947E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35134,7 +35105,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.258623212663597E-2</v>
+        <v>1.2950765110584326E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35646,14 +35617,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="248" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="F3" s="247" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="246"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35720,19 +35691,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="243">
+      <c r="C7" s="246">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="244"/>
-      <c r="F7" s="243">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="244"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35759,19 +35730,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="243">
+      <c r="C9" s="246">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="F9" s="243">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="244"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35798,19 +35769,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="243">
+      <c r="C11" s="246">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="F11" s="243">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="244"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35837,19 +35808,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="243">
+      <c r="C13" s="246">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="F13" s="243">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="244"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35876,19 +35847,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="243">
+      <c r="C15" s="246">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="244"/>
-      <c r="F15" s="243">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="244"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35915,19 +35886,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="243">
+      <c r="C17" s="246">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="F17" s="243">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="244"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35954,22 +35925,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="243">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="244"/>
-      <c r="F19" s="243">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="244"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35996,22 +35967,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="243">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="F21" s="243">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="244"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36059,22 +36030,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="243">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="F25" s="243">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="244"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -36101,22 +36072,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="243">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="F27" s="243">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="244"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36143,22 +36114,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="243">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="244"/>
-      <c r="F29" s="243">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="244"/>
+      <c r="G29" s="247"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36185,22 +36156,22 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="243">
+      <c r="C31" s="246">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="F31" s="243">
+      <c r="D31" s="247"/>
+      <c r="F31" s="246">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="244"/>
+      <c r="G31" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="26">

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E67464-8BDE-5E4E-A37E-2366D603D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0C5DD0-201A-2046-AF3D-82FBC6794BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2376,12 +2376,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2389,6 +2383,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2409,14 +2409,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12763,11 +12763,11 @@
     <v>Powered by Refinitiv</v>
     <v>243.37</v>
     <v>164.27</v>
-    <v>2.1957</v>
-    <v>-1.25</v>
-    <v>-5.8899999999999994E-3</v>
-    <v>0.1555</v>
-    <v>7.3709999999999997E-4</v>
+    <v>2.1993999999999998</v>
+    <v>5.04</v>
+    <v>2.3890999999999999E-2</v>
+    <v>0.14000000000000001</v>
+    <v>6.4810000000000009E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12775,25 +12775,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>213.85</v>
+    <v>217.75</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46318.955257638285</v>
+    <v>46321.85384879609</v>
     <v>0</v>
-    <v>210.18</v>
-    <v>5084136000000</v>
+    <v>212.61</v>
+    <v>5205600000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>210.99</v>
-    <v>26.825600000000001</v>
-    <v>212.21</v>
+    <v>213.10499999999999</v>
+    <v>27.3048</v>
     <v>210.96</v>
-    <v>211.1155</v>
+    <v>216</v>
+    <v>216.14</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>80064334</v>
-    <v>107148374</v>
+    <v>89951744</v>
+    <v>102744467</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12817,17 +12817,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5104177.2</v>
+        <v>5226120</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5038074.2</v>
+        <v>5160017</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13700,7 +13700,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>210.96</v>
+        <v>216</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13727,14 +13727,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>211.1155</v>
+        <v>216.14</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>26.670037926675096</v>
+        <v>27.307206068268016</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13754,14 +13754,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.25</v>
+        <v>5.04</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>16.98836956916384</v>
+        <v>17.394235053751373</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13778,14 +13778,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.1555</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.3463918925071801E-2</v>
+        <v>2.2916427483486792E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13802,14 +13802,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-5.8899999999999994E-3</v>
+        <v>2.3890999999999999E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.7495259764884339E-2</v>
+        <v>3.6620370370370373E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.78153645071482425</v>
+        <v>0.73996726686481173</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13826,14 +13826,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>7.3709999999999997E-4</v>
+        <v>6.4810000000000009E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.083720212534941E-2</v>
+        <v>1.0584334075757923E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.3272658323852863E-3</v>
+        <v>1.2962962962962965E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1957</v>
+        <v>2.1993999999999998</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>107148374</v>
+        <v>102744467</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.2950765110584326E-2</v>
+        <v>1.2648580591337359E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18233,12 +18233,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18246,6 +18240,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19305,16 +19305,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19445,7 +19445,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5104177.2</v>
+        <v>5226120</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.1957</v>
+        <v>2.1993999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.4752054095702704E-3</v>
+        <v>6.3250729267636946E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99352479459042975</v>
+        <v>0.99367492707323635</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14833649999999998</v>
+        <v>0.14885299999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14763176130644129</v>
+        <v>0.14816133430023959</v>
       </c>
     </row>
   </sheetData>
@@ -21415,17 +21415,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.78153645071482425</v>
+        <v>0.73996726686481173</v>
       </c>
     </row>
   </sheetData>
@@ -22395,10 +22395,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="257" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="258"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22425,20 +22425,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="259" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="257" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="258"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22472,7 +22472,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5084136</v>
+        <v>5205600</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22499,15 +22499,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5018033</v>
+        <v>5139497</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="257" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="258"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22583,16 +22583,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29167,7 +29167,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>216</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29238,7 +29238,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>210.96</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30740,7 +30740,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>26.670037926675096</v>
+        <v>27.307206068268016</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30777,7 +30777,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>16.98836956916384</v>
+        <v>17.394235053751373</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>22.203018551514518</v>
+        <v>22.733466093700873</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30899,7 +30899,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5104177.2</v>
+        <v>5226120</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30960,7 +30960,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5038074.2</v>
+        <v>5160017</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30997,7 +30997,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>16.62900890850219</v>
+        <v>17.031501572768171</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31034,7 +31034,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>25.499036840959821</v>
+        <v>26.116221865684107</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31169,7 +31169,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>42.618626632377008</v>
+        <v>43.636819077519121</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31206,7 +31206,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>41.478618763530207</v>
+        <v>42.482577560357257</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31243,7 +31243,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.3463918925071801E-2</v>
+        <v>2.2916427483486792E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31280,7 +31280,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.7495259764884339E-2</v>
+        <v>3.6620370370370373E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31317,7 +31317,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.3272658323852863E-3</v>
+        <v>1.2962962962962965E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31354,7 +31354,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>1.083720212534941E-2</v>
+        <v>1.0584334075757923E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31391,7 +31391,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.2164742242882947E-2</v>
+        <v>1.1880898257215678E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31894,7 +31894,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.2950765110584326E-2</v>
+        <v>1.2648580591337359E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -33135,7 +33135,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>216</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -33151,7 +33151,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5104177.2</v>
+        <v>5226120</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5038074.2</v>
+        <v>5160017</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33191,7 +33191,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>26.670037926675096</v>
+        <v>27.307206068268016</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33211,7 +33211,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>16.98836956916384</v>
+        <v>17.394235053751373</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33231,7 +33231,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>22.203018551514518</v>
+        <v>22.733466093700873</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33251,7 +33251,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>16.62900890850219</v>
+        <v>17.031501572768171</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33260,7 +33260,7 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>25.499036840959821</v>
+        <v>26.116221865684107</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33496,7 +33496,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.7495259764884339E-2</v>
+        <v>3.6620370370370373E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33512,7 +33512,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.3463918925071801E-2</v>
+        <v>2.2916427483486792E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.3272658323852863E-3</v>
+        <v>1.2962962962962965E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.083720212534941E-2</v>
+        <v>1.0584334075757923E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33553,7 +33553,7 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.2164742242882947E-2</v>
+        <v>1.1880898257215678E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.2950765110584326E-2</v>
+        <v>1.2648580591337359E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33777,7 +33777,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>210.96</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33806,7 +33806,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5104177.2</v>
+        <v>5226120</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33835,7 +33835,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5038074.2</v>
+        <v>5160017</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33864,7 +33864,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>26.670037926675096</v>
+        <v>27.307206068268016</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33893,7 +33893,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>16.98836956916384</v>
+        <v>17.394235053751373</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33922,7 +33922,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>22.203018551514518</v>
+        <v>22.733466093700873</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33951,7 +33951,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>16.62900890850219</v>
+        <v>17.031501572768171</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33980,7 +33980,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>25.499036840959821</v>
+        <v>26.116221865684107</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34753,7 +34753,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.7495259764884339E-2</v>
+        <v>3.6620370370370373E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34782,7 +34782,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.3463918925071801E-2</v>
+        <v>2.2916427483486792E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34811,7 +34811,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.3272658323852863E-3</v>
+        <v>1.2962962962962965E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.083720212534941E-2</v>
+        <v>1.0584334075757923E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34869,7 +34869,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.2164742242882947E-2</v>
+        <v>1.1880898257215678E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35105,7 +35105,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.2950765110584326E-2</v>
+        <v>1.2648580591337359E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35617,14 +35617,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="246" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="F3" s="250" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="249"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35691,19 +35691,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="249">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="250"/>
+      <c r="F7" s="249">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35730,19 +35730,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="249">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="250"/>
+      <c r="F9" s="249">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="250"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35769,19 +35769,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="249">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="250"/>
+      <c r="F11" s="249">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="250"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35808,19 +35808,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="249">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="250"/>
+      <c r="F13" s="249">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="250"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35847,19 +35847,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="249">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="250"/>
+      <c r="F15" s="249">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="250"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35886,19 +35886,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="249">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="250"/>
+      <c r="F17" s="249">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="250"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35925,22 +35925,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="249">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="250"/>
+      <c r="F19" s="249">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="250"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35967,22 +35967,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="249">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="250"/>
+      <c r="F21" s="249">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="250"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36030,22 +36030,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="249">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="250"/>
+      <c r="F25" s="249">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="250"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -36072,22 +36072,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="249">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="250"/>
+      <c r="F27" s="249">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="250"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36114,22 +36114,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="246">
+      <c r="C29" s="249">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="247"/>
-      <c r="F29" s="246">
+      <c r="D29" s="250"/>
+      <c r="F29" s="249">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="247"/>
+      <c r="G29" s="250"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36156,43 +36156,25 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="246">
+      <c r="C31" s="249">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="247"/>
-      <c r="F31" s="246">
+      <c r="D31" s="250"/>
+      <c r="F31" s="249">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="247"/>
+      <c r="G31" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -36201,6 +36183,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0C5DD0-201A-2046-AF3D-82FBC6794BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57263A2-72AB-0349-8F08-F12FFAC05895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="429">
   <si>
     <t>Ticker</t>
   </si>
@@ -1427,6 +1427,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2376,6 +2388,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2383,12 +2401,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2409,14 +2421,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12763,11 +12775,11 @@
     <v>Powered by Refinitiv</v>
     <v>243.37</v>
     <v>164.27</v>
-    <v>2.1993999999999998</v>
-    <v>5.04</v>
-    <v>2.3890999999999999E-2</v>
-    <v>0.14000000000000001</v>
-    <v>6.4810000000000009E-4</v>
+    <v>2.1934999999999998</v>
+    <v>1.94</v>
+    <v>8.9809999999999994E-3</v>
+    <v>-0.49</v>
+    <v>-2.248E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12775,25 +12787,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>217.75</v>
+    <v>219.19</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46321.85384879609</v>
+    <v>46322.896050161718</v>
     <v>0</v>
-    <v>212.61</v>
-    <v>5205600000000</v>
+    <v>215.53</v>
+    <v>5252354000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>213.10499999999999</v>
-    <v>27.3048</v>
-    <v>210.96</v>
+    <v>218.31</v>
+    <v>27.55</v>
     <v>216</v>
-    <v>216.14</v>
+    <v>217.94</v>
+    <v>217.45</v>
     <v>24100000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>89951744</v>
-    <v>102744467</v>
+    <v>84383179</v>
+    <v>101985396</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12817,17 +12829,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.55</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
+    <v>50.03</v>
     <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13653,7 +13665,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC155</f>
-        <v>5226120</v>
+        <v>5273058.3</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -13680,7 +13692,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC156</f>
-        <v>5160017</v>
+        <v>5206955.3</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -13700,7 +13712,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>216</v>
+        <v>217.94</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>235</v>
@@ -13727,14 +13739,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>216.14</v>
+        <v>217.45</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC152</f>
-        <v>27.307206068268016</v>
+        <v>27.552465233881161</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -13754,14 +13766,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>5.04</v>
+        <v>1.94</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>17.394235053751373</v>
+        <v>17.550461053771176</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13778,14 +13790,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.14000000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC163</f>
-        <v>2.2916427483486792E-2</v>
+        <v>2.2712436158727849E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B10</f>
@@ -13802,14 +13814,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.3890999999999999E-2</v>
+        <v>8.9809999999999994E-3</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC164</f>
-        <v>3.6620370370370373E-2</v>
+        <v>3.6294392952188677E-2</v>
       </c>
       <c r="H9" s="181" t="str">
         <f>'AVG target price'!B12</f>
@@ -13817,7 +13829,7 @@
       </c>
       <c r="I9" s="210">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.73996726686481173</v>
+        <v>0.72447889163439183</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13826,14 +13838,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>6.4810000000000009E-4</v>
+        <v>-2.248E-3</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.0584334075757923E-2</v>
+        <v>1.0490117281654178E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13849,7 +13861,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>1.2962962962962965E-3</v>
+        <v>1.284757272643847E-3</v>
       </c>
       <c r="H11" s="181" t="s">
         <v>397</v>
@@ -13881,7 +13893,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1993999999999998</v>
+        <v>2.1934999999999998</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>96</v>
@@ -13904,7 +13916,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>102744467</v>
+        <v>101985396</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>97</v>
@@ -13927,7 +13939,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC178</f>
-        <v>1.2648580591337359E-2</v>
+        <v>1.2535988839721344E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14054,7 +14066,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14069,7 +14081,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18233,6 +18245,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18240,12 +18258,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19305,16 +19317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19436,7 +19448,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>216</v>
+        <v>217.94</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19445,7 +19457,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5226120</v>
+        <v>5273058.3</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19463,7 +19475,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19472,7 +19484,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.1993999999999998</v>
+        <v>2.1934999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19515,7 +19527,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.3250729267636946E-3</v>
+        <v>6.2691230537869694E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19524,7 +19536,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99367492707323635</v>
+        <v>0.99373087694621298</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19542,7 +19554,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14885299999999999</v>
+        <v>0.14856749999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19551,7 +19563,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14816133430023959</v>
+        <v>0.14788374242133107</v>
       </c>
     </row>
   </sheetData>
@@ -21415,17 +21427,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21529,7 +21541,7 @@
       </c>
       <c r="C11" s="134">
         <f ca="1">Overview!C5</f>
-        <v>216</v>
+        <v>217.94</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21538,7 +21550,7 @@
       </c>
       <c r="C12" s="153">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.73996726686481173</v>
+        <v>0.72447889163439183</v>
       </c>
     </row>
   </sheetData>
@@ -22395,10 +22407,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="257" t="s">
+      <c r="B14" s="258" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="258"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22406,7 +22418,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>216</v>
+        <v>217.94</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22425,20 +22437,20 @@
       <c r="C17" s="157">
         <v>0.5</v>
       </c>
-      <c r="E17" s="259" t="s">
+      <c r="E17" s="257" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="257" t="s">
+      <c r="B19" s="258" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="258"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22472,7 +22484,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>5205600</v>
+        <v>5252354</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22499,15 +22511,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>5139497</v>
+        <v>5186251</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="257" t="s">
+      <c r="B28" s="258" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="258"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22583,16 +22595,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29167,7 +29179,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>216</v>
+        <v>217.94</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29238,7 +29250,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>216</v>
+        <v>217.94</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30740,7 +30752,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>27.307206068268016</v>
+        <v>27.552465233881161</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30777,7 +30789,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>17.394235053751373</v>
+        <v>17.550461053771176</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30838,7 +30850,7 @@
       </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>22.733466093700873</v>
+        <v>22.937646298431332</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30899,7 +30911,7 @@
       </c>
       <c r="AC155" s="142">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5226120</v>
+        <v>5273058.3</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30960,7 +30972,7 @@
       </c>
       <c r="AC156" s="142">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5160017</v>
+        <v>5206955.3</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30997,7 +31009,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="180">
         <f ca="1">AC156/AC5</f>
-        <v>17.031501572768171</v>
+        <v>17.186429304648328</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31034,7 +31046,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="180">
         <f ca="1">AC156/AC11</f>
-        <v>26.116221865684107</v>
+        <v>26.353789117264487</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31169,7 +31181,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="168">AC155/AC159</f>
-        <v>43.636819077519121</v>
+        <v>44.028742359974615</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31206,7 +31218,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="168"/>
-        <v>42.482577560357257</v>
+        <v>42.869022017866079</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31243,7 +31255,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="171">AC159/AC155</f>
-        <v>2.2916427483486792E-2</v>
+        <v>2.2712436158727849E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31280,7 +31292,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.6620370370370373E-2</v>
+        <v>3.6294392952188677E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31317,7 +31329,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">AC81/AC115</f>
-        <v>1.2962962962962965E-3</v>
+        <v>1.284757272643847E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31354,7 +31366,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="153">
         <f ca="1">-AC62/AC155</f>
-        <v>1.0584334075757923E-2</v>
+        <v>1.0490117281654178E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31391,7 +31403,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="153">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>1.1880898257215678E-2</v>
+        <v>1.1775140054871003E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31894,7 +31906,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="153">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.2648580591337359E-2</v>
+        <v>1.2535988839721344E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -33102,7 +33114,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -33135,7 +33147,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>216</v>
+        <v>217.94</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -33151,7 +33163,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5226120</v>
+        <v>5273058.3</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33171,7 +33183,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5160017</v>
+        <v>5206955.3</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33191,7 +33203,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>27.307206068268016</v>
+        <v>27.552465233881161</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33211,7 +33223,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>17.394235053751373</v>
+        <v>17.550461053771176</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33231,7 +33243,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>22.733466093700873</v>
+        <v>22.937646298431332</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33251,7 +33263,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.031501572768171</v>
+        <v>17.186429304648328</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33260,7 +33272,7 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>26.116221865684107</v>
+        <v>26.353789117264487</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33496,7 +33508,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.6620370370370373E-2</v>
+        <v>3.6294392952188677E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33512,7 +33524,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC163</f>
-        <v>2.2916427483486792E-2</v>
+        <v>2.2712436158727849E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33528,7 +33540,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2962962962962965E-3</v>
+        <v>1.284757272643847E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33544,7 +33556,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0584334075757923E-2</v>
+        <v>1.0490117281654178E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33553,7 +33565,7 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1880898257215678E-2</v>
+        <v>1.1775140054871003E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33597,7 +33609,7 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC178</f>
-        <v>1.2648580591337359E-2</v>
+        <v>1.2535988839721344E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33651,8 +33663,51 @@
         <v>1.9948467588825602</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="245" t="s">
+        <v>425</v>
+      </c>
+      <c r="C57" s="245"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C58" s="171">
+        <f ca="1">Statement!AC161</f>
+        <v>44.028742359974615</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C59" s="171">
+        <f ca="1">Statement!AC162</f>
+        <v>42.869022017866079</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="C60" s="172">
+        <f>Statement!AC168</f>
+        <v>0.40090556060471172</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="C61" s="172">
+        <f>Statement!AC169</f>
+        <v>0.39530116942657501</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -33677,7 +33732,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I95"/>
+  <dimension ref="B1:I101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -33777,7 +33832,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>216</v>
+        <v>217.94</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33806,7 +33861,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>5226120</v>
+        <v>5273058.3</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33835,7 +33890,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC156</f>
-        <v>5160017</v>
+        <v>5206955.3</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33864,7 +33919,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC152</f>
-        <v>27.307206068268016</v>
+        <v>27.552465233881161</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33893,7 +33948,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>17.394235053751373</v>
+        <v>17.550461053771176</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33922,7 +33977,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>22.733466093700873</v>
+        <v>22.937646298431332</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33951,7 +34006,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC157</f>
-        <v>17.031501572768171</v>
+        <v>17.186429304648328</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33980,7 +34035,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC158</f>
-        <v>26.116221865684107</v>
+        <v>26.353789117264487</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34753,7 +34808,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC164</f>
-        <v>3.6620370370370373E-2</v>
+        <v>3.6294392952188677E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34782,7 +34837,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC163</f>
-        <v>2.2916427483486792E-2</v>
+        <v>2.2712436158727849E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34811,7 +34866,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC165</f>
-        <v>1.2962962962962965E-3</v>
+        <v>1.284757272643847E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34840,7 +34895,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.0584334075757923E-2</v>
+        <v>1.0490117281654178E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34869,7 +34924,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC167</f>
-        <v>1.1880898257215678E-2</v>
+        <v>1.1775140054871003E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35105,7 +35160,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.2648580591337359E-2</v>
+        <v>1.2535988839721344E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35442,157 +35497,284 @@
       </c>
       <c r="I85" s="194"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C88" s="171">
+        <f>Statement!M161</f>
+        <v>95.00515665796344</v>
+      </c>
+      <c r="D88" s="171">
+        <f>Statement!N161</f>
+        <v>461.29572338489538</v>
+      </c>
+      <c r="E88" s="171">
+        <f>Statement!O161</f>
+        <v>65.653012099522826</v>
+      </c>
+      <c r="F88" s="171">
+        <f>Statement!P161</f>
+        <v>62.645954451493331</v>
+      </c>
+      <c r="G88" s="171">
+        <f>Statement!Q161</f>
+        <v>50.830322848598954</v>
+      </c>
+      <c r="I88" s="171">
+        <f ca="1">Statement!AC161</f>
+        <v>44.028742359974615</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C89" s="171">
+        <f>Statement!M162</f>
+        <v>85.552901846404438</v>
+      </c>
+      <c r="D89" s="171">
+        <f>Statement!N162</f>
+        <v>292.02604166666669</v>
+      </c>
+      <c r="E89" s="171">
+        <f>Statement!O162</f>
+        <v>59.253144937486333</v>
+      </c>
+      <c r="F89" s="171">
+        <f>Statement!P162</f>
+        <v>58.114897258120507</v>
+      </c>
+      <c r="G89" s="171">
+        <f>Statement!Q162</f>
+        <v>49.56625962229554</v>
+      </c>
+      <c r="I89" s="171">
+        <f ca="1">Statement!AC162</f>
+        <v>42.869022017866079</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="C90" s="172">
+        <f>Statement!M168</f>
+        <v>0.24838741111758303</v>
+      </c>
+      <c r="D90" s="172">
+        <f>Statement!N168</f>
+        <v>6.4061689033884484E-2</v>
+      </c>
+      <c r="E90" s="172">
+        <f>Statement!O168</f>
+        <v>0.42238462291779383</v>
+      </c>
+      <c r="F90" s="172">
+        <f>Statement!P168</f>
+        <v>0.45896309457389761</v>
+      </c>
+      <c r="G90" s="172">
+        <f>Statement!Q168</f>
+        <v>0.42373919358213857</v>
+      </c>
+      <c r="I90" s="172">
+        <f>Statement!AC168</f>
+        <v>0.40090556060471172</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="C91" s="172">
+        <f>Statement!M169</f>
+        <v>0.22768819201902354</v>
+      </c>
+      <c r="D91" s="172">
+        <f>Statement!N169</f>
+        <v>4.0742937643656857E-2</v>
+      </c>
+      <c r="E91" s="172">
+        <f>Statement!O169</f>
+        <v>0.38527953776960705</v>
+      </c>
+      <c r="F91" s="172">
+        <f>Statement!P169</f>
+        <v>0.43001754829612943</v>
+      </c>
+      <c r="G91" s="172">
+        <f>Statement!Q169</f>
+        <v>0.41812927784827125</v>
+      </c>
+      <c r="I91" s="172">
+        <f>Statement!AC169</f>
+        <v>0.39530116942657501</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C94" s="172">
+        <f>Statement!M203</f>
+        <v>-1</v>
+      </c>
+      <c r="D94" s="172">
+        <f>Statement!N203</f>
+        <v>-2.5062656641604009E-3</v>
+      </c>
+      <c r="E94" s="172">
+        <f>Statement!O203</f>
+        <v>-7.537688442211055E-3</v>
+      </c>
+      <c r="F94" s="172">
+        <f>Statement!P203</f>
+        <v>1.1113924050632911</v>
+      </c>
+      <c r="G94" s="172">
+        <f>Statement!Q203</f>
+        <v>0.16786570743405277</v>
+      </c>
+      <c r="I94" s="194"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="220" t="s">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="220" t="s">
         <v>359</v>
       </c>
-      <c r="C89" s="172">
+      <c r="C98" s="172">
         <f>Statement!M196</f>
         <v>0</v>
       </c>
-      <c r="D89" s="172">
+      <c r="D98" s="172">
         <f>Statement!N196</f>
         <v>0</v>
       </c>
-      <c r="E89" s="172">
+      <c r="E98" s="172">
         <f>Statement!O196</f>
         <v>0</v>
       </c>
-      <c r="F89" s="172">
+      <c r="F98" s="172">
         <f>Statement!P196</f>
         <v>1</v>
       </c>
-      <c r="G89" s="172">
+      <c r="G98" s="172">
         <f>Statement!Q196</f>
         <v>0.96364041936203437</v>
       </c>
-      <c r="I89" s="194"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="220" t="s">
+      <c r="I98" s="194"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="220" t="s">
         <v>360</v>
       </c>
-      <c r="C90" s="172">
+      <c r="C99" s="172">
         <f>Statement!M197</f>
         <v>0</v>
       </c>
-      <c r="D90" s="172">
+      <c r="D99" s="172">
         <f>Statement!N197</f>
         <v>0</v>
       </c>
-      <c r="E90" s="172">
+      <c r="E99" s="172">
         <f>Statement!O197</f>
         <v>0</v>
       </c>
-      <c r="F90" s="172">
+      <c r="F99" s="172">
         <f>Statement!P197</f>
         <v>1</v>
       </c>
-      <c r="G90" s="172">
+      <c r="G99" s="172">
         <f>Statement!Q197</f>
         <v>0.43510343704186349</v>
       </c>
-      <c r="I90" s="194"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="20" t="s">
+      <c r="I99" s="194"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="s">
         <v>361</v>
       </c>
-      <c r="C91" s="172">
+      <c r="C100" s="172">
         <f>Statement!M198</f>
         <v>0</v>
       </c>
-      <c r="D91" s="172">
+      <c r="D100" s="172">
         <f>Statement!N198</f>
         <v>0</v>
       </c>
-      <c r="E91" s="172">
+      <c r="E100" s="172">
         <f>Statement!O198</f>
         <v>0</v>
       </c>
-      <c r="F91" s="172">
+      <c r="F100" s="172">
         <f>Statement!P198</f>
         <v>1</v>
       </c>
-      <c r="G91" s="172">
+      <c r="G100" s="172">
         <f>Statement!Q198</f>
         <v>0.68194919521469621</v>
       </c>
-      <c r="I91" s="194"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B92" s="20" t="s">
+      <c r="I100" s="194"/>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B101" s="20" t="s">
         <v>362</v>
       </c>
-      <c r="C92" s="172">
+      <c r="C101" s="172">
         <f>Statement!M199</f>
         <v>0</v>
       </c>
-      <c r="D92" s="172">
+      <c r="D101" s="172">
         <f>Statement!N199</f>
         <v>0</v>
       </c>
-      <c r="E92" s="172">
+      <c r="E101" s="172">
         <f>Statement!O199</f>
         <v>0</v>
       </c>
-      <c r="F92" s="172">
+      <c r="F101" s="172">
         <f>Statement!P199</f>
         <v>1</v>
       </c>
-      <c r="G92" s="172">
+      <c r="G101" s="172">
         <f>Statement!Q199</f>
         <v>0.4500032656260205</v>
       </c>
-      <c r="I92" s="194"/>
-    </row>
-    <row r="94" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="C94" s="14"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
-      <c r="I94" s="14"/>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B95" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C95" s="172">
-        <f>Statement!M202</f>
-        <v>0</v>
-      </c>
-      <c r="D95" s="172">
-        <f>Statement!N203</f>
-        <v>-2.5062656641604009E-3</v>
-      </c>
-      <c r="E95" s="172">
-        <f>Statement!O203</f>
-        <v>-7.537688442211055E-3</v>
-      </c>
-      <c r="F95" s="172">
-        <f>Statement!P203</f>
-        <v>1.1113924050632911</v>
-      </c>
-      <c r="G95" s="172">
-        <f>Statement!Q203</f>
-        <v>0.16786570743405277</v>
-      </c>
-      <c r="I95" s="194"/>
+      <c r="I101" s="194"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35617,14 +35799,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="248" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35691,19 +35873,19 @@
       <c r="B7" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="249">
+      <c r="C7" s="246">
         <f>Statement!AA88</f>
         <v>0.17896220057587453</v>
       </c>
-      <c r="D7" s="250"/>
-      <c r="F7" s="249">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>1.0585114348672529</v>
       </c>
-      <c r="G7" s="250"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -35730,19 +35912,19 @@
       <c r="B9" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="249">
+      <c r="C9" s="246">
         <f>Statement!AA89</f>
         <v>0.17699677387818946</v>
       </c>
-      <c r="D9" s="250"/>
-      <c r="F9" s="249">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.86803723816912337</v>
       </c>
-      <c r="G9" s="250"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -35769,19 +35951,19 @@
       <c r="B11" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="249">
+      <c r="C11" s="246">
         <f>Statement!AA90</f>
         <v>0.17961966741337868</v>
       </c>
-      <c r="D11" s="250"/>
-      <c r="F11" s="249">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.1310371311257497</v>
       </c>
-      <c r="G11" s="250"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -35808,19 +35990,19 @@
       <c r="B13" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="249">
+      <c r="C13" s="246">
         <f>Statement!AA93</f>
         <v>0.10326728775751214</v>
       </c>
-      <c r="D13" s="250"/>
-      <c r="F13" s="249">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.55329761684832812</v>
       </c>
-      <c r="G13" s="250"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -35847,19 +36029,19 @@
       <c r="B15" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="249">
+      <c r="C15" s="246">
         <f>Statement!AA94</f>
         <v>0.19048864315600716</v>
       </c>
-      <c r="D15" s="250"/>
-      <c r="F15" s="249">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.240998593530239</v>
       </c>
-      <c r="G15" s="250"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -35886,19 +36068,19 @@
       <c r="B17" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="249">
+      <c r="C17" s="246">
         <f>Statement!AA96</f>
         <v>2.3439241439618664E-2</v>
       </c>
-      <c r="D17" s="250"/>
-      <c r="F17" s="249">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2590265687684505</v>
       </c>
-      <c r="G17" s="250"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -35925,22 +36107,22 @@
       <c r="B19" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.3458652781763769E-3</v>
       </c>
-      <c r="D19" s="250"/>
-      <c r="F19" s="249">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.0068481982716452E-2</v>
       </c>
-      <c r="G19" s="250"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -35967,22 +36149,22 @@
       <c r="B21" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="249">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>2.9288702928870224E-2</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="F21" s="249">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.2777777777777777</v>
       </c>
-      <c r="G21" s="250"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36030,22 +36212,22 @@
       <c r="B25" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="249">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.28627637381499377</v>
       </c>
-      <c r="D25" s="250"/>
-      <c r="F25" s="249">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.0395260226939664</v>
       </c>
-      <c r="G25" s="250"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="220" t="s">
@@ -36072,22 +36254,22 @@
       <c r="B27" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="249">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>7.8550980549535812E-2</v>
       </c>
-      <c r="D27" s="250"/>
-      <c r="F27" s="249">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.3420089467263114</v>
       </c>
-      <c r="G27" s="250"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36114,22 +36296,22 @@
       <c r="B29" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="249">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18309278898546102</v>
       </c>
-      <c r="D29" s="250"/>
-      <c r="F29" s="249">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>1.166220556745182</v>
       </c>
-      <c r="G29" s="250"/>
+      <c r="G29" s="247"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36156,25 +36338,43 @@
       <c r="B31" s="203" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="249">
+      <c r="C31" s="246">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.13016172083529595</v>
       </c>
-      <c r="D31" s="250"/>
-      <c r="F31" s="249">
+      <c r="D31" s="247"/>
+      <c r="F31" s="246">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.27465911103240659</v>
       </c>
-      <c r="G31" s="250"/>
+      <c r="G31" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -36183,24 +36383,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
